--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cobertura'!$A$1:$E$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cobertura'!$A$1:$E$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Personas'!$A$1:$H$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Escenas'!$A$1:$Q$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Noticias'!$A$1:$K$14</definedName>
@@ -590,7 +590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 06:50 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 07:00 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -30334,7 +30334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -30379,22 +30379,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>«ana_lengua»: la niña de los Cuthbert tiene una lengua, pero buen corazón</t>
+          <t>Ana en camisón en la tienda de Lawson</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:ana_lengua» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena con «si: ana:camison» (o la hora), y «ve:quien» o «en: quien=tl»</t>
         </is>
       </c>
     </row>
@@ -30406,76 +30406,76 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>«ana_ofendio_lynde»: la niña de los Cuthbert le dijo vieja chismosa a la Sra. Lynde</t>
+          <t>Ana en camisón en la escuela</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:ana_ofendio_lynde» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena con «si: ana:camison» (o la hora), y «ve:quien» o «en: quien=es»</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón en la casa del Sr. Harrison</t>
+          <t>«ana_lengua»: la niña de los Cuthbert tiene una lengua, pero buen corazón</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona a ella (solo se cuenta)</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:camison» (o la hora) y «en: …=hh»</t>
+          <t>una escena o una frase con «sabe:quien:ana_lengua» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón en la tienda de Lawson</t>
+          <t>«ana_ofendio_lynde»: la niña de los Cuthbert le dijo vieja chismosa a la Sra. Lynde</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona a ella (solo se cuenta)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:camison» (o la hora) y «en: …=tl»</t>
+          <t>una escena o una frase con «sabe:quien:ana_ofendio_lynde» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -30487,22 +30487,22 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón en la escuela</t>
+          <t>Ana en camisón en La Cuesta del Huerto</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:camison» (o la hora) y «en: …=es»</t>
+          <t>una escena con «si: ana:camison» (o la hora), y «ve:quien» o «en: quien=os»</t>
         </is>
       </c>
     </row>
@@ -30514,22 +30514,22 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón en la iglesia</t>
+          <t>Ana en camisón en la casa del Sr. Harrison</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:camison» (o la hora) y «en: …=ig»</t>
+          <t>una escena con «si: ana:camison» (o la hora), y «ve:quien» o «en: quien=hh»</t>
         </is>
       </c>
     </row>
@@ -30541,7 +30541,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -30551,12 +30551,12 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:camison» (o la hora) y «en: …=cp»</t>
+          <t>una escena con «si: ana:camison» (o la hora), y «ve:quien» o «en: quien=cp»</t>
         </is>
       </c>
     </row>
@@ -30568,22 +30568,22 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón en afuera (los caminos, la aldea)</t>
+          <t>Ana sin sombrero en Tejas Verdes</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: Marilla, Matthew, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:camison» (o la hora) y «en: …=out»</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=gg»</t>
         </is>
       </c>
     </row>
@@ -30595,22 +30595,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Ana sin sombrero en afuera (los caminos, la aldea)</t>
+          <t>Ana sin sombrero en La Cuesta del Huerto</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:sin_sombrero» (o la hora) y «en: …=out»</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=os»</t>
         </is>
       </c>
     </row>
@@ -30622,22 +30622,22 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Ana sin sombrero en la iglesia</t>
+          <t>Ana sin sombrero en la Hondonada (Sra. Lynde)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: Thomas Lynde, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:sin_sombrero» (o la hora) y «en: …=ig»</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=rl»</t>
         </is>
       </c>
     </row>
@@ -30649,22 +30649,22 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Ana sin sombrero en la escuela</t>
+          <t>Ana sin sombrero en la casa del Sr. Harrison</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>una escena con «si: ana:sin_sombrero» (o la hora) y «en: …=es»</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=hh»</t>
         </is>
       </c>
     </row>
@@ -30676,22 +30676,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en afuera (los caminos, la aldea)</t>
+          <t>Ana sin sombrero en la tienda de Lawson</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>una escena de noche (hora:21-26) en out</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=tl»</t>
         </is>
       </c>
     </row>
@@ -30703,22 +30703,22 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Quién la ve en camisón</t>
+          <t>Ana sin sombrero en la escuela</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>no reaccionan: Matthew, Diana, el Sr. Harrison, el Sr. Shearer</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>una escena «si: ana:camison, ve:quien» para cada uno</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=es»</t>
         </is>
       </c>
     </row>
@@ -30730,22 +30730,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Frases</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Gertie Pye</t>
+          <t>Ana sin sombrero en la iglesia</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Bell, el reverendo Allan, la Sra. Allan, la Sra. Lynde, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>frases para esos momentos (hoja «Huecos»)</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=ig»</t>
         </is>
       </c>
     </row>
@@ -30757,22 +30757,22 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Frases</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Jane Andrews</t>
+          <t>Ana sin sombrero en la casa parroquial</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>frases para esos momentos (hoja «Huecos»)</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=cp»</t>
         </is>
       </c>
     </row>
@@ -30784,22 +30784,22 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Frases</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Charlie Sloane</t>
+          <t>Ana sin sombrero en la aldea (afuera)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison, el Sr. Lawson, la Sra. Barry, la Sra. Lynde, la Sra. Pye, v0)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>frases para esos momentos (hoja «Huecos»)</t>
+          <t>una escena con «si: ana:sin_sombrero» (o la hora), y «ve:quien» o «en: quien=out»</t>
         </is>
       </c>
     </row>
@@ -30811,22 +30811,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Frases</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Cecily King</t>
+          <t>Quién ve a Ana en camisón y no dice nada</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>Mary Joe, Matthew, Thomas Lynde, el Sr. Barry, el Sr. Bell, el Sr. Harrison, el Sr. Lawson, el Sr. Phillips, el reverendo Allan, la Sra. Allan, la Sra. Barry, la Sra. Pye, la Srta. Stacy, v0</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>frases para esos momentos (hoja «Huecos»)</t>
+          <t>una escena «si: ana:camison, ve:quien» (o una frase con [ana:camison])</t>
         </is>
       </c>
     </row>
@@ -30843,12 +30843,12 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Minnie May Barry</t>
+          <t>Gertie Pye</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -30870,12 +30870,12 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
+          <t>Jane Andrews</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -30897,12 +30897,12 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>la Srta. Josephine Barry</t>
+          <t>Charlie Sloane</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 45 (sin conocerla), Día 45 (conociéndola)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -30919,22 +30919,22 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Metas</t>
+          <t>Frases</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>«perdon_barry»</t>
+          <t>Cecily King</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
+          <t>frases para esos momentos (hoja «Huecos»)</t>
         </is>
       </c>
     </row>
@@ -30946,22 +30946,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Metas</t>
+          <t>Frases</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>«carta»</t>
+          <t>Minnie May Barry</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
+          <t>frases para esos momentos (hoja «Huecos»)</t>
         </is>
       </c>
     </row>
@@ -30973,22 +30973,22 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Metas</t>
+          <t>Frases</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>«sala»</t>
+          <t>Carrie Sloane</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
+          <t>frases para esos momentos (hoja «Huecos»)</t>
         </is>
       </c>
     </row>
@@ -31000,22 +31000,22 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Metas</t>
+          <t>Frases</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>«sombrero»</t>
+          <t>la Srta. Josephine Barry</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
+          <t>no tiene qué decir: Día 45 (sin conocerla), Día 45 (conociéndola)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
+          <t>frases para esos momentos (hoja «Huecos»)</t>
         </is>
       </c>
     </row>
@@ -31032,7 +31032,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>«tinte»</t>
+          <t>«perdon_barry»</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>«pelo_corto»</t>
+          <t>«carta»</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -31086,7 +31086,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>«techo»</t>
+          <t>«sala»</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -31103,108 +31103,108 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>media</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Metas</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en La Cuesta del Huerto (los Barry)</t>
+          <t>«sombrero»</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>una escena de noche (hora:21-26) en os</t>
+          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>media</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Metas</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la Hondonada (la Sra. Lynde)</t>
+          <t>«tinte»</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>una escena de noche (hora:21-26) en rl</t>
+          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>media</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Ana y los lugares</t>
+          <t>Metas</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la casa del Sr. Harrison</t>
+          <t>«pelo_corto»</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>ninguna escena reacciona</t>
+          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>una escena de noche (hora:21-26) en hh</t>
+          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>media</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Metas</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>«huerfano»: los Cuthbert van a traer un niño del orfanato</t>
+          <t>«techo»</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:huerfano» (alguien que se entera y hace o dice algo)</t>
+          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
         </is>
       </c>
     </row>
@@ -31216,22 +31216,22 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>«cerdo_pye»: a los Pye se les escapó otra vez el cerdo</t>
+          <t>Ana de noche en Tejas Verdes</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: Marilla, Matthew, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:cerdo_pye» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31243,22 +31243,22 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>«maestra_plumas»: la maestra nueva usa sombrero con plumas</t>
+          <t>Ana de noche en La Cuesta del Huerto</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:maestra_plumas» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31270,22 +31270,22 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>«loro_harrison»: el loro del Sr. Harrison dice cosas terribles</t>
+          <t>Ana de noche en la Hondonada (Sra. Lynde)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: Thomas Lynde, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:loro_harrison» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31297,22 +31297,22 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>«rastrillo_matthew»: Matthew Cuthbert compró un rastrillo en invierno</t>
+          <t>Ana de noche en la casa del Sr. Harrison</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:rastrillo_matthew» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31324,22 +31324,22 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>«ana_lengua»</t>
+          <t>Ana de noche en la tienda de Lawson</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>es de Ana y no tiene versión exagerada</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>una línea «exagerada:» (los chismosos la agrandan)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31351,22 +31351,22 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>«pastor_nuevo»: llegó un pastor nuevo, el Sr. Allan, con su esposa</t>
+          <t>Ana de noche en la escuela</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:pastor_nuevo» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31378,22 +31378,22 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>«tia_josephine»: la tía Josephine de los Barry vino de Charlottetown</t>
+          <t>Ana de noche en la iglesia</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Bell, el reverendo Allan, la Sra. Allan, la Sra. Lynde, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:tia_josephine» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31405,22 +31405,22 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>«se_va_phillips»: el Sr. Phillips se va de la escuela de Avonlea</t>
+          <t>Ana de noche en la casa parroquial</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:se_va_phillips» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31432,22 +31432,22 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Llegadas</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Prissy Andrews se va</t>
+          <t>Ana de noche en la aldea (afuera)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison, el Sr. Lawson, la Sra. Barry, la Sra. Lynde, la Sra. Pye, v0)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>una noticia o una escena con «hecho:se_fue_prissy»</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -31459,22 +31459,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Llegadas</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>el buhonero llega (de visita)</t>
+          <t>Ana en camisón: ella misma no lo nota</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota (solo queda en el diario)</t>
+          <t>en Tejas Verdes, La Cuesta del Huerto, la Hondonada (Sra. Lynde), la casa del Sr. Harrison, la tienda de Lawson, la escuela, la iglesia, la casa parroquial, la aldea (afuera)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_buhonero: …» o una escena «si: hecho:llego_buhonero»</t>
+          <t>un comentario de Ana con «si: ana:camison»</t>
         </is>
       </c>
     </row>
@@ -31486,22 +31486,22 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Llegadas</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>una veraneante del hotel llega (de visita)</t>
+          <t>Ana sin sombrero: ella misma no lo nota</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota (solo queda en el diario)</t>
+          <t>en Tejas Verdes, La Cuesta del Huerto, la Hondonada (Sra. Lynde), la casa del Sr. Harrison, la tienda de Lawson, la escuela, la iglesia, la casa parroquial, la aldea (afuera)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_veraneante: …» o una escena «si: hecho:llego_veraneante»</t>
+          <t>un comentario de Ana con «si: ana:sin_sombrero»</t>
         </is>
       </c>
     </row>
@@ -31513,22 +31513,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Presentación propia (cómo se presenta la primera vez)</t>
+          <t>70 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>32 usan la de siempre: Diana, el Sr. Shearer, el buhonero, el Sr. Phillips, el reverendo Allan, la Sra. Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King, Jasper Dale, Alec King, Janet King…</t>
+          <t>les falta: Ana no va en la calesa por el camino</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>«presentacion» en personajes.json, o «presenta» en src/js/56-gente-de-avonlea.js, con su voz</t>
+          <t>ej.: avenida, newbridge, avenida_petalos, avenida_paso</t>
         </is>
       </c>
     </row>
@@ -31540,22 +31540,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>el buhonero</t>
+          <t>56 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: podía pasar (no tocó)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: primera_gwin, primera_mirror, primera_armario, primera_stairs</t>
         </is>
       </c>
     </row>
@@ -31567,22 +31567,22 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Gertie Pye</t>
+          <t>38 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando se encuentran</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: diana_por_casualidad, par:ana+diana:0, par:ana+diana:1, par:ana+diana:2</t>
         </is>
       </c>
     </row>
@@ -31594,22 +31594,22 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Jane Andrews</t>
+          <t>19 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando Ana usa gwin</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: ventana_primavera_manana, ventana_primavera_tarde, ventana_verano_manana, ventana_verano_noche</t>
         </is>
       </c>
     </row>
@@ -31621,22 +31621,22 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Prissy Andrews</t>
+          <t>13 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando Ana conversa con diana</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: conv_diana_pelo, conv_diana_minnie, conv_diana_nombres, conv_diana_escuela</t>
         </is>
       </c>
     </row>
@@ -31648,22 +31648,22 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Charlie Sloane</t>
+          <t>8 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: ana no está en gg</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: quiere_amiga, broche, prohibida, invita_allan</t>
         </is>
       </c>
     </row>
@@ -31675,22 +31675,22 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Moody Spurgeon</t>
+          <t>7 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando Ana conversa con marilla</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: conv_marilla_perdon, conv_marilla_cocina, conv_marilla_diana, conv_marilla_genio</t>
         </is>
       </c>
     </row>
@@ -31702,22 +31702,22 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Tillie Boulter</t>
+          <t>6 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando Ana usa mirror</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: espejo_pelo, espejo_cordelia, espejo_tejas_verdes, espejo_zanahorias</t>
         </is>
       </c>
     </row>
@@ -31729,22 +31729,22 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Felicity King</t>
+          <t>5 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando Ana conversa con matthew</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: conv_matthew_nombres, conv_matthew_mangas, conv_matthew_mujeres, conv_matthew_queens</t>
         </is>
       </c>
     </row>
@@ -31756,22 +31756,22 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Felix King</t>
+          <t>4 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: diana no está en Avonlea</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: conoce_diana, te_grosella, crup_aviso, cama_josephine</t>
         </is>
       </c>
     </row>
@@ -31783,22 +31783,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Cecily King</t>
+          <t>4 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: falta hecho:blewett_duda</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: duda_matthew, duda_suplica, duda_calla, devuelta_blewett</t>
         </is>
       </c>
     </row>
@@ -31810,22 +31810,22 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Sara Stanley</t>
+          <t>4 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>les falta: cuando Ana usa faro</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>ej.: faro_verano, faro_invierno, faro_manana, faro_queens</t>
         </is>
       </c>
     </row>
@@ -31837,22 +31837,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Phillips</t>
+          <t>«huerfano»: los Cuthbert van a traer un niño del orfanato</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:huerfano» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -31864,22 +31864,22 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>el reverendo Allan</t>
+          <t>«cerdo_pye»: a los Pye se les escapó otra vez el cerdo</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:cerdo_pye» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -31891,22 +31891,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>«maestra_plumas»: la maestra nueva usa sombrero con plumas</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:maestra_plumas» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -31918,22 +31918,22 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>el herrero</t>
+          <t>«loro_harrison»: el loro del Sr. Harrison dice cosas terribles</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:loro_harrison» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -31945,22 +31945,22 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>el editor de La Crónica</t>
+          <t>«rastrillo_matthew»: Matthew Cuthbert compró un rastrillo en invierno</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:rastrillo_matthew» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -31972,22 +31972,22 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>la Srta. Hetty King</t>
+          <t>«ana_lengua»</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>es de Ana y no tiene versión exagerada</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una línea «exagerada:» (los chismosos la agrandan)</t>
         </is>
       </c>
     </row>
@@ -31999,22 +31999,22 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Olivia King</t>
+          <t>«pastor_nuevo»: llegó un pastor nuevo, el Sr. Allan, con su esposa</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:pastor_nuevo» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -32026,22 +32026,22 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Jasper Dale</t>
+          <t>«tia_josephine»: la tía Josephine de los Barry vino de Charlottetown</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:tia_josephine» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -32053,22 +32053,22 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Alec King</t>
+          <t>«se_va_phillips»: el Sr. Phillips se va de la escuela de Avonlea</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena o una frase con «sabe:quien:se_va_phillips» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -32080,22 +32080,22 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Llegadas</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Janet King</t>
+          <t>Prissy Andrews se va</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie lo nota</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una noticia o una escena con «hecho:se_fue_prissy»</t>
         </is>
       </c>
     </row>
@@ -32107,22 +32107,22 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Llegadas</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Pye</t>
+          <t>el buhonero llega (de visita)</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>nadie lo nota (solo queda en el diario)</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una noticia «saben si hecho:llego_buhonero: …» o una escena «si: hecho:llego_buhonero»</t>
         </is>
       </c>
     </row>
@@ -32134,22 +32134,22 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Llegadas</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Sloane</t>
+          <t>una veraneante del hotel llega (de visita)</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>nadie lo nota (solo queda en el diario)</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una noticia «saben si hecho:llego_veraneante: …» o una escena «si: hecho:llego_veraneante»</t>
         </is>
       </c>
     </row>
@@ -32166,17 +32166,17 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Andrews</t>
+          <t>Presentación propia (cómo se presenta la primera vez)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>32 usan la de siempre: Diana, el Sr. Shearer, el buhonero, el Sr. Phillips, el reverendo Allan, la Sra. Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King, Jasper Dale, Alec King, Janet King…</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>«presentacion» en personajes.json, o «presenta» en src/js/56-gente-de-avonlea.js, con su voz</t>
         </is>
       </c>
     </row>
@@ -32193,7 +32193,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Peg Bowen</t>
+          <t>el buhonero</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Barry</t>
+          <t>Gertie Pye</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -32247,7 +32247,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Mary Joe</t>
+          <t>Jane Andrews</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -32274,7 +32274,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Jerry Buote</t>
+          <t>Prissy Andrews</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -32301,7 +32301,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>el médico</t>
+          <t>Charlie Sloane</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Bell</t>
+          <t>Moody Spurgeon</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -32355,7 +32355,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Spencer</t>
+          <t>Tillie Boulter</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
@@ -32382,7 +32382,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Blewett</t>
+          <t>Felicity King</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
+          <t>Felix King</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>el jefe de estación</t>
+          <t>Cecily King</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -32463,12 +32463,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Thomas Lynde</t>
+          <t>Sara Stanley</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>una veraneante del hotel</t>
+          <t>el Sr. Phillips</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -32517,12 +32517,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>un pescador</t>
+          <t>el reverendo Allan</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -32544,17 +32544,17 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Sin ninguna escena</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>42 de la gente del pueblo solo tienen frases sueltas: el buhonero, Josie Pye, Gertie Pye, Ruby Gillis, Jane Andrews, Prissy Andrews, Charlie Sloane, Moody Spurgeon, Tillie Boulter, Felicity King, Felix King, Cecily King, Sara Stanley, el Sr. Phillips, el reverendo Allan, el Sr. Lawson…</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>una escena pequeña para los que importan en el libro</t>
+          <t>unas frases más en la hoja «Frases»</t>
         </is>
       </c>
     </row>
@@ -32566,22 +32566,22 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Hechos</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>«ana_admite_gilbert»</t>
+          <t>el herrero</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>una escena, una frase o una noticia que lo recuerde</t>
+          <t>unas frases más en la hoja «Frases»</t>
         </is>
       </c>
     </row>
@@ -32593,22 +32593,22 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Hechos</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>«blewett_orgullo»</t>
+          <t>el editor de La Crónica</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>una escena, una frase o una noticia que lo recuerde</t>
+          <t>unas frases más en la hoja «Frases»</t>
         </is>
       </c>
     </row>
@@ -32620,22 +32620,22 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Hechos</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>«devuelta»</t>
+          <t>la Srta. Hetty King</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>una escena, una frase o una noticia que lo recuerde</t>
+          <t>unas frases más en la hoja «Frases»</t>
         </is>
       </c>
     </row>
@@ -32647,22 +32647,22 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Hechos</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>«marilla_doblo_ropa»</t>
+          <t>Olivia King</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>una escena, una frase o una noticia que lo recuerde</t>
+          <t>unas frases más en la hoja «Frases»</t>
         </is>
       </c>
     </row>
@@ -32674,28 +32674,676 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Jasper Dale</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>Alec King</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Janet King</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>la Sra. Pye</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>el Sr. Sloane</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>tiene 1 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>el Sr. Andrews</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>tiene 1 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Peg Bowen</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>el Sr. Barry</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Mary Joe</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>Jerry Buote</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>el médico</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>el Sr. Bell</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>la Sra. Spencer</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>la Sra. Blewett</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Carrie Sloane</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>el jefe de estación</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Thomas Lynde</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>tiene 1 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>una veraneante del hotel</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>tiene 2 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>un pescador</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>tiene 1 frase(s) suelta(s)</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>unas frases más en la hoja «Frases»</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Sin ninguna escena</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>42 de la gente del pueblo solo tienen frases sueltas: el buhonero, Josie Pye, Gertie Pye, Ruby Gillis, Jane Andrews, Prissy Andrews, Charlie Sloane, Moody Spurgeon, Tillie Boulter, Felicity King, Felix King, Cecily King, Sara Stanley, el Sr. Phillips, el reverendo Allan, el Sr. Lawson…</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>una escena pequeña para los que importan en el libro</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
           <t>Hechos</t>
         </is>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>«ana_admite_gilbert»</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>una escena, una frase o una noticia que lo recuerde</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>«blewett_orgullo»</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>una escena, una frase o una noticia que lo recuerde</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>«devuelta»</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>una escena, una frase o una noticia que lo recuerde</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>«marilla_doblo_ropa»</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>una escena, una frase o una noticia que lo recuerde</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>«queens_primera»</t>
         </is>
       </c>
-      <c r="D87" s="11" t="inlineStr">
+      <c r="D111" s="11" t="inlineStr">
         <is>
           <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
         </is>
       </c>
-      <c r="E87" s="11" t="inlineStr">
+      <c r="E111" s="11" t="inlineStr">
         <is>
           <t>una escena, una frase o una noticia que lo recuerde</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E87"/>
-  <conditionalFormatting sqref="A2:A87">
+  <autoFilter ref="A1:E111"/>
+  <conditionalFormatting sqref="A2:A111">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>A2="alta"</formula>
     </cfRule>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -9,26 +9,28 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usar" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Huecos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noticias" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegadas" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diálogos" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hechos" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metas" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Huecos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noticias" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegadas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diálogos" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hechos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metas" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cobertura'!$A$1:$E$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Personas'!$A$1:$H$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Escenas'!$A$1:$Q$164</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Noticias'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Llegadas'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Diálogos'!$A$1:$C$621</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Hechos'!$A$1:$D$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Noticias'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Llegadas'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Diálogos'!$A$1:$C$621</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 07:00 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 07:20 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -773,6 +775,272 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Quién</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>De visita</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Llega si… (una alternativa por línea)</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Se va si… (una por línea)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Al llegar (diario)</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Al irse (diario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>diana</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>dias_desde:llegada_tv:17</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Diana Barry volvió de Carmody, donde su tía.</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>gilbert</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>dias_desde:escuela:4
+estacion:invierno</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Gilbert Blythe volvió de Nuevo Brunswick.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>josephine</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>estacion:invierno</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>La tía Josephine llegó de Charlottetown a La Cuesta del Huerto.</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>La tía Josephine se volvió a Charlottetown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>allan</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>estacion:primavera, dias_desde:se_fue_josephine:7</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Llegó el pastor nuevo, el Sr. Allan, con su esposa.</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>sraallan</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>estacion:primavera, dias_desde:se_fue_josephine:7</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>phillips</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>estacion:verano, hecho:llego_josephine</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>El Sr. Phillips se despidió de la escuela: todas las niñas lloraron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>prissy</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>hecho:se_fue_phillips</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Prissy Andrews se fue a Queen's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>stacy</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>estacion:otoño, hecho:se_fue_phillips</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Llegó la maestra nueva, la Srta. Stacy.</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>buhonero</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>dia_estacion:4
+dia_estacion:11</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>veraneante</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>estacion:verano</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B211" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"sí"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11350,7 +11618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12982,7 +13250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30334,6 +30602,3618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Clase</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Quién</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Tiene</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Una situación</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Lo que falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>algo que decirle</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Gertie Pye</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a Gertie Pye: sí</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>dias_desde:escuela:3 (2); !conoce:gertie (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Alec King</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Alec King: sí</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>el reverendo Allan</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el reverendo Allan: sí</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Andrews</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Andrews: sí</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Barry</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Barry: no</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>hora:7-21 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Blewett</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Blewett: sí</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>el buhonero</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el buhonero: sí</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>el editor de La Crónica</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el editor de La Crónica: sí</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>el capitán Jim</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el capitán Jim: sí</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Harrison</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Harrison: sí</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>el herrero</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el herrero: sí</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Hetty King</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Srta. Hetty King: sí</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Janet King</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Janet King: sí</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Jasper Dale</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Jasper Dale: sí</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>el jefe de estación</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el jefe de estación: sí</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Jerry Buote</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Jerry Buote: sí</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Josephine Barry</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Srta. Josephine Barry: no</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Lawson</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Lawson: sí</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Lynde</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Lynde: no</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>hora:7-21 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Marilla</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Marilla: sí</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>hora:9-19 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Mary Joe</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la casa del Sr. Harrison · Ana: en camisón · conoce a Mary Joe: sí</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Matthew: sí</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>el médico</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el médico: sí</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Olivia King</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Olivia King: sí</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Peg Bowen</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Peg Bowen: sí</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>un pescador</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a un pescador: sí</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Phillips</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Phillips: sí</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Shearer</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Shearer: sí</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Sloane</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Sloane: sí</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Spencer</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Spencer: sí</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Allan</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Sra. Allan: sí</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Pye</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Pye: sí</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Barry</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el Sr. Barry: sí</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Bell</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la tienda de Lawson · Ana: en camisón · conoce a el Sr. Bell: sí</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Stacy</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Srta. Stacy: sí</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Thomas Lynde</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: la casa de la Sra. Lynde · Ana: en camisón · conoce a Thomas Lynde: sí</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>un vecino (sin nombre)</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: en camisón · conoce a un vecino (sin nombre): no</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>una veraneante del hotel</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a una veraneante del hotel: sí</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Alec King</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>día: 67 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Alec King: sí</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>el reverendo Allan</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>día: 113 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el reverendo Allan: sí</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Andrews</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Andrews: sí</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Barry</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Barry: no</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Blewett</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Blewett: sí</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>el buhonero</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>día: 11 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el buhonero: sí</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>el editor de La Crónica</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el editor de La Crónica: sí</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>el capitán Jim</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>día: 126 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el capitán Jim: sí</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Harrison</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>día: 3 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Harrison: sí</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>el herrero</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el herrero: sí</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Hetty King</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Hetty King: sí</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Janet King</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Janet King: sí</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Jasper Dale</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Jasper Dale: sí</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>el jefe de estación</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el jefe de estación: sí</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Jerry Buote</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Jerry Buote: sí</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Josephine Barry</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Josephine Barry: no</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Lawson</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Lawson: sí</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Lynde</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Lynde: no</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Marilla</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Marilla: sí</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Mary Joe</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Mary Joe: sí</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Matthew: sí</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>el médico</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>día: 85 · estación: otoño · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el médico: sí</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Olivia King</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Olivia King: sí</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Peg Bowen</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Peg Bowen: sí</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>un pescador</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a un pescador: sí</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Phillips</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Phillips: sí</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Shearer</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Shearer: sí</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Sloane</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Sloane: sí</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Spencer</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Spencer: sí</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Allan</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Allan: sí</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Pye</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Pye: sí</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Barry</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Barry: sí</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Bell</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Bell: sí</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Stacy</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>día: 113 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Stacy: sí</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Thomas Lynde</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Thomas Lynde: sí</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>un vecino (sin nombre)</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>día: 113 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a un vecino (sin nombre): no</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>una veraneante del hotel</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>día: 127 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a una veraneante del hotel: sí</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Alec King</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Alec King: sí</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>el reverendo Allan</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el reverendo Allan: sí</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Andrews</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Andrews: sí</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Barry</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Barry: no</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Blewett</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Blewett: sí</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>el buhonero</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>día: 102 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el buhonero: sí</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>el editor de La Crónica</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a el editor de La Crónica: sí</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>el capitán Jim</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el capitán Jim: sí</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Harrison</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Harrison: sí</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>el herrero</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el herrero: sí</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Hetty King</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Hetty King: sí</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Janet King</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Janet King: sí</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Jasper Dale</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Jasper Dale: sí</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>el jefe de estación</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el jefe de estación: sí</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Jerry Buote</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a Jerry Buote: sí</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Josephine Barry</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Josephine Barry: no</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Lawson</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Lawson: sí</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Lynde</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Lynde: no</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Marilla</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Marilla: sí</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Mary Joe</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 21:00 · Ana en: La Cuesta del Huerto · conoce a Mary Joe: sí</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Matthew: sí</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>el médico</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el médico: sí</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Olivia King</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Olivia King: sí</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Peg Bowen</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Peg Bowen: sí</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>un pescador</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a un pescador: sí</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Phillips</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Phillips: sí</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Shearer</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Shearer: sí</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Sloane</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Sloane: sí</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Spencer</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Spencer: sí</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Allan</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Allan: sí</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Pye</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Pye: sí</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Barry</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Barry: sí</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Bell</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Bell: sí</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Stacy</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Stacy: sí</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Thomas Lynde</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Thomas Lynde: sí</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>un vecino (sin nombre)</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a un vecino (sin nombre): no</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>reacciona si Ana anda sola de noche</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>una veraneante del hotel</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>día: 71 · estación: verano · hora: 21:00 · Ana en: el camino o la aldea · conoce a una veraneante del hotel: sí</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>no tiene ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>«pasa» invita a entrar</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Barry</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>frase de invierno</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la casa de la Sra. Lynde · conoce a la Sra. Barry: sí</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>«Pasa, pasa, que hace un frío terrible. Diana está junto al fuego.» exige donde:barry:propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>«pasa» invita a entrar</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Lynde</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>frase de invierno</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Sra. Lynde: sí</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>«Pasa, niña, que hace un frío de mil demonios... perdón, de los que dan escalofrí» exige donde:lynde:propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>la Srta. Stacy, cuando ya llegó</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Carrie Sloane</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>frase</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>día: 88 · estación: otoño · hora: 6:00 · Ana en: el camino o la aldea · conoce a Carrie Sloane: sí</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>«¿Viste la composición de Ana? ¡La señorita Stacy la leyó en voz alta!» exige hecho:llego_stacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Gilbert, cuando ya volvió</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>escena al encontrarse</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: su pieza · conoce a Diana: sí</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>«diana: Gilbert Blythe te miró otra vez en clase.» exige hecho:llego_gilbert</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>«saludos a Marilla», fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Barry</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>frase</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Sra. Barry: no</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>«Saluda a Marilla de mi parte.» exige !donde:ana:tejas</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>«saludos a Marilla», fuera de Tejas Verdes</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>un vecino (sin nombre)</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>frase</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a un vecino (sin nombre): no</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>«¡Qué grande estás, niña! Saludos a Marilla.» exige !donde:ana:tejas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F119"/>
+  <conditionalFormatting sqref="A2:A119">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>A2="incoherencia"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -33355,7 +37235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37113,7 +40993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38275,7 +42155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40157,7 +44037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48595,7 +52475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49118,270 +52998,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Quién</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>De visita</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Llega si… (una alternativa por línea)</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Se va si… (una por línea)</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Al llegar (diario)</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Al irse (diario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>diana</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>dias_desde:llegada_tv:17</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>Diana Barry volvió de Carmody, donde su tía.</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>gilbert</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>dias_desde:escuela:4
-estacion:invierno</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Gilbert Blythe volvió de Nuevo Brunswick.</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>josephine</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>estacion:invierno</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>La tía Josephine llegó de Charlottetown a La Cuesta del Huerto.</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>La tía Josephine se volvió a Charlottetown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>allan</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>estacion:primavera, dias_desde:se_fue_josephine:7</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Llegó el pastor nuevo, el Sr. Allan, con su esposa.</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>sraallan</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>estacion:primavera, dias_desde:se_fue_josephine:7</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>phillips</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>estacion:verano, hecho:llego_josephine</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>El Sr. Phillips se despidió de la escuela: todas las niñas lloraron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>prissy</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>hecho:se_fue_phillips</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Prissy Andrews se fue a Queen's.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>stacy</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>estacion:otoño, hecho:se_fue_phillips</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Llegó la maestra nueva, la Srta. Stacy.</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>buhonero</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>dia_estacion:4
-dia_estacion:11</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>veraneante</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>estacion:verano</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F11"/>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B211" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"sí"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -23,14 +23,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Noticias'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Llegadas'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Diálogos'!$A$1:$C$621</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 07:20 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 12:30 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11700,7 +11700,7 @@
       <c r="B4" s="11" t="inlineStr"/>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>escena falta_noche, escena falta_viaje</t>
+          <t>escena falta_noche, escena falta_viaje, una frase de barry, una frase de vecino</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr"/>
@@ -11930,17 +11930,13 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>conoce_gilbert</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>escena zanahorias</t>
-        </is>
-      </c>
+          <t>conoce_gertie</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>una frase de gilbert</t>
+          <t>una frase de gertie</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
@@ -11948,13 +11944,17 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>conoce_harrison</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr"/>
+          <t>conoce_gilbert</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias</t>
+        </is>
+      </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>una frase de harrison</t>
+          <t>una frase de gilbert</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr"/>
@@ -11962,13 +11962,13 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>conoce_jane</t>
+          <t>conoce_harrison</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>una frase de jane</t>
+          <t>una frase de harrison</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>conoce_lynde</t>
+          <t>conoce_jane</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>una frase de lynde</t>
+          <t>una frase de jane</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr"/>
@@ -11990,13 +11990,13 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>conoce_minnie</t>
+          <t>conoce_lynde</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>una frase de minnie</t>
+          <t>una frase de lynde</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -12004,13 +12004,13 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>conoce_sara</t>
+          <t>conoce_minnie</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>una frase de sara</t>
+          <t>una frase de minnie</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr"/>
@@ -12018,17 +12018,13 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>conoce_sraallan</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>escena invita_allan</t>
-        </is>
-      </c>
+          <t>conoce_sara</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>una frase de sraallan, código</t>
+          <t>una frase de sara</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -12036,13 +12032,17 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>conoce_stacy</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr"/>
+          <t>conoce_sraallan</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>escena invita_allan</t>
+        </is>
+      </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>escena espejo_estudio, escena conv_marilla_queens, escena conv_matthew_queens, escena conv_diana_futuro, una frase de stacy, meta queens (pista), código</t>
+          <t>una frase de sraallan, código</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -12050,17 +12050,13 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>conocidas_diana</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>escena conoce_diana, escena diana_por_casualidad, código</t>
-        </is>
-      </c>
+          <t>conoce_stacy</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>escena broche, escena cama_josephine, escena ventana_diana, escena banco_lago_diana, escena pupitre_diana, escena lugar_puente_diana, escena lugar_cuesta_huerto, escena conv_marilla_diana, escena conv_diana_pelo, escena conv_diana_minnie, escena conv_diana_nombres, escena conv_diana_escuela, escena conv_diana_bosque, escena conv_diana_vestidos, escena conv_diana_club, escena conv_barry_diana, un comentario de pupitre, una frase de marilla, una frase de diana, una frase de barry, meta te_diana, meta josephine</t>
+          <t>escena espejo_estudio, escena conv_marilla_queens, escena conv_matthew_queens, escena conv_diana_futuro, una frase de stacy, meta queens (pista), código</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -12068,17 +12064,17 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>crup</t>
+          <t>conocidas_diana</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>escena crup_aviso</t>
+          <t>escena conoce_diana, escena diana_por_casualidad, código</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>escena crup_salva, meta perdon_barry (pista)</t>
+          <t>escena broche, escena cama_josephine, escena ventana_diana, escena banco_lago_diana, escena pupitre_diana, escena lugar_puente_diana, escena lugar_cuesta_huerto, escena conv_marilla_diana, escena conv_diana_pelo, escena conv_diana_minnie, escena conv_diana_nombres, escena conv_diana_escuela, escena conv_diana_bosque, escena conv_diana_vestidos, escena conv_diana_club, escena conv_barry_diana, un comentario de pupitre, una frase de marilla, una frase de diana, una frase de barry, meta te_diana, meta josephine</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -12086,17 +12082,17 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>desayuno_prueba</t>
+          <t>crup</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>escena desayuno_prueba</t>
+          <t>escena crup_aviso</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_se_entera, escena viaje_spencer, escena llamar_almuerzo, escena llamar_almuerzo_afuera, escena falta_camison, escena falta_noche, escena falta_viaje, escena viaje_spencer_duda, escena primera_stairs</t>
+          <t>escena crup_salva, meta perdon_barry (pista)</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
@@ -12104,53 +12100,53 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>devuelta</t>
+          <t>desayuno_prueba</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>escena devuelta_blewett</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena desayuno_prueba</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_se_entera, escena viaje_spencer, escena llamar_almuerzo, escena llamar_almuerzo_afuera, escena falta_camison, escena falta_noche, escena falta_viaje, escena viaje_spencer_duda, escena primera_stairs</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>diana_borracha</t>
+          <t>devuelta</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>escena te_grosella</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>escena prohibida, meta perdon_barry</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr"/>
+          <t>escena devuelta_blewett</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>disculpa_lynde</t>
+          <t>diana_borracha</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_disculpa</t>
+          <t>escena te_grosella</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>una frase de lynde</t>
+          <t>escena prohibida, meta perdon_barry</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -12158,17 +12154,17 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>examen</t>
+          <t>disculpa_lynde</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera, escena examen_entra, escena examen_no</t>
+          <t>escena lynde_disculpa</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>meta queens (pista)</t>
+          <t>una frase de lynde</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
@@ -12176,35 +12172,39 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_20</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>habilidad estudio</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr"/>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>una frase de gertie</t>
+        </is>
+      </c>
       <c r="D33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_50</t>
+          <t>examen</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>habilidad estudio</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr"/>
+          <t>escena examen_primera, escena examen_entra, escena examen_no</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>meta queens (pista)</t>
+        </is>
+      </c>
       <c r="D34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_85</t>
+          <t>hito_estudio_20</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -12218,12 +12218,12 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_10</t>
+          <t>hito_estudio_50</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>habilidad granja</t>
+          <t>habilidad estudio</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr"/>
@@ -12232,12 +12232,12 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_40</t>
+          <t>hito_estudio_85</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>habilidad granja</t>
+          <t>habilidad estudio</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_80</t>
+          <t>hito_granja_10</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -12260,12 +12260,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_10</t>
+          <t>hito_granja_40</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>habilidad letras</t>
+          <t>habilidad granja</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr"/>
@@ -12274,12 +12274,12 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_30</t>
+          <t>hito_granja_80</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>habilidad letras</t>
+          <t>habilidad granja</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr"/>
@@ -12288,7 +12288,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_60</t>
+          <t>hito_letras_10</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -12302,12 +12302,12 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>hito_paciencia_4</t>
+          <t>hito_letras_30</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>habilidad paciencia</t>
+          <t>habilidad letras</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr"/>
@@ -12316,49 +12316,45 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>inicio_juego</t>
+          <t>hito_letras_60</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>habilidad letras</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr"/>
       <c r="D43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>invierno</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr"/>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild</t>
-        </is>
-      </c>
+          <t>hito_paciencia_4</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>habilidad paciencia</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr"/>
       <c r="D44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>llamada_almuerzo</t>
+          <t>inicio_juego</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
@@ -12366,17 +12362,13 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>llegada_tv</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>escena llegada, escena inicio_llegada</t>
-        </is>
-      </c>
+          <t>invierno</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr"/>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche, escena desayuno_prueba, una frase de vecino, llegadas de diana</t>
+          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr"/>
@@ -12384,17 +12376,17 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>llegaron</t>
+          <t>llamada_almuerzo</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>escena llegada</t>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr"/>
@@ -12402,31 +12394,35 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>llego_</t>
+          <t>llegada_tv</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr"/>
+          <t>escena llegada, escena inicio_llegada</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>escena primera_noche, escena desayuno_prueba, una frase de vecino, llegadas de diana</t>
+        </is>
+      </c>
       <c r="D48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>llego_allan</t>
+          <t>llegaron</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>noticia pastor_nuevo</t>
+          <t>escena llegada</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr"/>
@@ -12434,12 +12430,12 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>llego_buhonero</t>
+          <t>llego_</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr"/>
@@ -12448,7 +12444,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>llego_diana</t>
+          <t>llego_allan</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -12456,13 +12452,17 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr"/>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>noticia pastor_nuevo</t>
+        </is>
+      </c>
       <c r="D51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>llego_gilbert</t>
+          <t>llego_buhonero</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -12476,7 +12476,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>llego_josephine</t>
+          <t>llego_diana</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -12484,17 +12484,13 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>llegadas de phillips</t>
-        </is>
-      </c>
+      <c r="C53" s="11" t="inlineStr"/>
       <c r="D53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>llego_sraallan</t>
+          <t>llego_gilbert</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -12502,13 +12498,17 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr"/>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="D54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>llego_stacy</t>
+          <t>llego_josephine</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>llegadas de phillips</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr"/>
@@ -12526,7 +12526,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>llego_veraneante</t>
+          <t>llego_sraallan</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -12540,13 +12540,17 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>lynde</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr"/>
+          <t>llego_stacy</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_se_entera, una frase de lynde</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr"/>
@@ -12554,31 +12558,27 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>llego_veraneante</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>una frase de lynde, noticia ana_lengua</t>
-        </is>
-      </c>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr"/>
       <c r="D58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>marilla</t>
+          <t>lynde</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr"/>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza</t>
+          <t>escena lynde_se_entera, una frase de lynde</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr"/>
@@ -12586,31 +12586,31 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>marilla_doblo_ropa</t>
+          <t>lynde_visita</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena lynde_visita</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>una frase de lynde, noticia ana_lengua</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>marilla_sabe_camison</t>
+          <t>marilla</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr"/>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison_descalza</t>
+          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr"/>
@@ -12618,7 +12618,7 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>matthew_en_estacion</t>
+          <t>marilla_doblo_ropa</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -12626,27 +12626,23 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>escena estacion</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr"/>
+      <c r="C62" s="11" t="inlineStr"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>matthew_llego_casa</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>marilla_sabe_camison</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr"/>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>escena tejas_verdes (alternativa)</t>
+          <t>escena marilla_sabe_camison_descalza</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr"/>
@@ -12654,7 +12650,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>nombre_propio_</t>
+          <t>matthew_en_estacion</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -12662,17 +12658,17 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>escena estacion</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>nombro_</t>
+          <t>matthew_llego_casa</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -12680,40 +12676,40 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>escena tejas_verdes (alternativa)</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>nombro_avenida</t>
+          <t>nombre_propio_</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>escena nombra_avenida</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>escena conv_matthew_nombres</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>nombro_burbuja</t>
+          <t>nombro_</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr"/>
@@ -12726,48 +12722,48 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>nombro_cerezo</t>
+          <t>nombro_avenida</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>escena primera_gwin</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena nombra_avenida</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>escena conv_matthew_nombres</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>nombro_lago</t>
+          <t>nombro_burbuja</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>escena lago</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>escena conv_matthew_nombres</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr"/>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>nombro_senda</t>
+          <t>nombro_cerezo</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
+          <t>escena primera_gwin</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr"/>
@@ -12780,17 +12776,17 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>nombro_lago</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita (una opción)</t>
+          <t>escena lago</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_disculpa, una frase de lynde, noticia ana_lengua</t>
+          <t>escena conv_matthew_nombres</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr"/>
@@ -12798,35 +12794,35 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>pastel_linimento</t>
+          <t>nombro_senda</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>escena pastel_linimento</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>meta allan</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr"/>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>perdon_pedido</t>
+          <t>ofendio_lynde</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_perdon_marilla</t>
+          <t>escena lynde_visita (una opción)</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_perdon_marilla</t>
+          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, una frase de lynde, noticia ana_lengua</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr"/>
@@ -12834,17 +12830,17 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>pastel_linimento</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>escena crup_salva</t>
+          <t>escena pastel_linimento</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico</t>
+          <t>meta allan</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr"/>
@@ -12852,17 +12848,17 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>pide_amiga</t>
+          <t>perdon_pedido</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr"/>
@@ -12870,13 +12866,17 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>primera_bed</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr"/>
+          <t>perdonada</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>escena crup_salva</t>
+        </is>
+      </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche_sube</t>
+          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr"/>
@@ -12884,17 +12884,17 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>primera_noche</t>
+          <t>pide_amiga</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>escena inicio_llegada, escena primera_noche</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr"/>
@@ -12902,17 +12902,13 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>prohibida</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>escena prohibida</t>
-        </is>
-      </c>
+          <t>primera_bed</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr"/>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>escena barry_no_perdona, escena crup_aviso, escena crup_salva, escena ventana_prohibida, escena lugar_cuesta_prohibida, una frase de barry</t>
+          <t>escena primera_noche_sube</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr"/>
@@ -12920,17 +12916,17 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>queens</t>
+          <t>primera_noche</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera, escena examen_entra</t>
+          <t>escena inicio_llegada, escena primera_noche</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_queens, escena faro_queens</t>
+          <t>escena primera_noche</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr"/>
@@ -12938,35 +12934,35 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>queens_primera</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena prohibida</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>escena barry_no_perdona, escena crup_aviso, escena crup_salva, escena ventana_prohibida, escena lugar_cuesta_prohibida, una frase de diana, una frase de barry</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>quiere_amiga</t>
+          <t>queens</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>escena quiere_amiga</t>
+          <t>escena examen_primera, escena examen_entra</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>escena barry_recibe, meta conocer_diana (pista)</t>
+          <t>escena ventana_queens, escena faro_queens</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr"/>
@@ -12974,35 +12970,35 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>rachel_en_casa_bell</t>
+          <t>queens_primera</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>escena rachel_bell</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr"/>
+          <t>escena examen_primera</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>rachel_llego_tejas_verdes</t>
+          <t>quiere_amiga</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena quiere_amiga</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
+          <t>escena barry_recibe, meta conocer_diana (pista)</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr"/>
@@ -13010,17 +13006,17 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>rachel_lo_sabe</t>
+          <t>rachel_en_casa_bell</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena rachel_bell</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr"/>
@@ -13028,7 +13024,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>ropa_arrugada</t>
+          <t>rachel_llego_tejas_verdes</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
@@ -13038,7 +13034,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla</t>
+          <t>escena rachel_marilla</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr"/>
@@ -13046,17 +13042,17 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>ropa_ordenada</t>
+          <t>rachel_lo_sabe</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
+          <t>escena rachel_marilla</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
           <t>código</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>una frase de marilla, código</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr"/>
@@ -13064,7 +13060,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>ropa_tirada_otra</t>
+          <t>ropa_arrugada</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
@@ -13074,7 +13070,7 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>escena falta_ropa (una opción), código</t>
+          <t>una frase de marilla</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr"/>
@@ -13082,7 +13078,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>se_fue_</t>
+          <t>ropa_ordenada</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
@@ -13090,45 +13086,49 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C88" s="11" t="inlineStr"/>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>una frase de marilla, código</t>
+        </is>
+      </c>
       <c r="D88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>se_fue_buhonero</t>
+          <t>ropa_tirada_otra</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>escena falta_ropa (una opción), código</t>
+        </is>
+      </c>
       <c r="D89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>se_fue_josephine</t>
+          <t>se_fue_</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C90" s="11" t="inlineStr">
-        <is>
-          <t>llegadas de allan, llegadas de sraallan</t>
-        </is>
-      </c>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr"/>
       <c r="D90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>se_fue_phillips</t>
+          <t>se_fue_buhonero</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -13136,17 +13136,13 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
-        </is>
-      </c>
+      <c r="C91" s="11" t="inlineStr"/>
       <c r="D91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>se_fue_prissy</t>
+          <t>se_fue_josephine</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -13154,13 +13150,17 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr"/>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>llegadas de allan, llegadas de sraallan</t>
+        </is>
+      </c>
       <c r="D92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>se_fue_veraneante</t>
+          <t>se_fue_phillips</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -13168,51 +13168,55 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
+        </is>
+      </c>
       <c r="D93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>se_fue_prissy</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>escena se_queda</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, un comentario de espejo, una frase de matthew, una frase de marilla, una frase de lynde, meta conocer_diana</t>
-        </is>
-      </c>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr"/>
       <c r="D94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>undefined</t>
-        </is>
-      </c>
-      <c r="B95" s="11" t="inlineStr"/>
-      <c r="C95" s="11" t="inlineStr">
-        <is>
-          <t>escena primera_noche</t>
-        </is>
-      </c>
+          <t>se_fue_veraneante</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr"/>
       <c r="D95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="inlineStr"/>
+          <t>se_queda</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>escena se_queda</t>
+        </is>
+      </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, un comentario de espejo, una frase de matthew, una frase de marilla, una frase de lynde, meta conocer_diana</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
@@ -13220,25 +13224,67 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
+          <t>undefined</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr"/>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>escena primera_noche</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>verano</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr"/>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>una frase de phillips</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr"/>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
           <t>zanahorias</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>escena zanahorias</t>
         </is>
       </c>
-      <c r="C97" s="11" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, un comentario de pupitre, un comentario de pizarra, una frase de gilbert, meta paces</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <autoFilter ref="A1:D97"/>
-  <conditionalFormatting sqref="D2:D97">
+  <autoFilter ref="A1:D100"/>
+  <conditionalFormatting sqref="D2:D100">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(D2,5)="nunca"</formula>
     </cfRule>
@@ -15036,7 +15082,11 @@
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I30" s="7" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr"/>
     </row>
@@ -15067,7 +15117,11 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr"/>
     </row>
@@ -15114,18 +15168,18 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>¡Mira los manzanos en flor, Ana! Parecen novias vestidas de blanco.</t>
+          <t>(Diana baja la vista.) Mamá dice que no puedo hablar contigo, Ana... Lo siento tanto.</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>conocidas_diana</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
@@ -15145,12 +15199,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>¡Qué calor! ¿Vamos a remojar los pies en el lago?</t>
+          <t>¡Mira los manzanos en flor, Ana! Parecen novias vestidas de blanco.</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr"/>
@@ -15160,7 +15214,11 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr"/>
     </row>
@@ -15176,12 +15234,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>El Bosque Encantado está todo rojo y dorado... ¡como un cuento!</t>
+          <t>¡Qué calor! ¿Vamos a remojar los pies en el lago?</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr"/>
@@ -15191,7 +15249,11 @@
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="9" t="inlineStr"/>
     </row>
@@ -15207,12 +15269,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>¡Está nevando! Mamá no me deja salir sin bufanda. Ven, entra a calentarte junto al fuego.</t>
+          <t>El Bosque Encantado está todo rojo y dorado... ¡como un cuento!</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
@@ -15222,14 +15284,18 @@
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>barry</t>
+          <t>diana</t>
         </is>
       </c>
       <c r="B37" s="8">
@@ -15238,32 +15304,28 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Tú debes ser la niña que trajeron los Cuthbert. Buenas tardes.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
+          <t>¡Está nevando! Mamá no me deja salir sin bufanda. Ven, entra a calentarte junto al fuego.</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>conocidas_diana</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>barry_presenta</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>sabe:barry:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -15282,23 +15344,27 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Ana Shirley, siempre es un gusto verte por aquí. Pórtate bien, ¿eh?</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>barry_presenta</t>
-        </is>
-      </c>
+          <t>Tú debes ser la niña que trajeron los Cuthbert. Buenas tardes.</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>barry_presenta</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>sabe:barry:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -15317,13 +15383,13 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Diana habla de ti todo el día, ¿sabes?</t>
+          <t>Ana Shirley, siempre es un gusto verte por aquí. Pórtate bien, ¿eh?</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>conocidas_diana</t>
+          <t>barry_presenta</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
@@ -15352,17 +15418,21 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Esta vez el cordial de frambuesa está bien etiquetado, te lo aseguro.</t>
+          <t>Diana habla de ti todo el día, ¿sabes?</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>conocidas_diana</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr"/>
     </row>
@@ -15383,21 +15453,17 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Buenas tardes. (La Sra. Barry no la invita a pasar.)</t>
+          <t>Esta vez el cordial de frambuesa está bien etiquetado, te lo aseguro.</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr"/>
     </row>
@@ -15418,13 +15484,21 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Saluda a Marilla de mi parte.</t>
+          <t>Buenas tardes. (La Sra. Barry no la invita a pasar.)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>perdonada</t>
+        </is>
+      </c>
       <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr"/>
     </row>
@@ -15440,20 +15514,16 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Buenos días, Ana. Diana está deseando verte.</t>
+          <t>Saluda a Marilla de mi parte.</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>barry_presenta</t>
-        </is>
-      </c>
+      <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -15461,7 +15531,11 @@
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="9" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>!donde:ana:tejas</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -15475,24 +15549,24 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Qué calor, ¿verdad? Hay limonada en la despensa.</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>barry_presenta</t>
-        </is>
-      </c>
+          <t>Buenos días, niña. ¿Y Marilla, cómo está? Hace tiempo que no la veo.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>barry_presenta</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr"/>
@@ -15510,12 +15584,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Diana me ayudó con las manzanas. Llévale algunas a Marilla.</t>
+          <t>Buenos días, Ana. Diana está deseando verte.</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr"/>
@@ -15545,12 +15619,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Pasa, pasa, que hace un frío terrible. Diana está junto al fuego.</t>
+          <t>Qué calor, ¿verdad? Hay limonada en la despensa.</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr"/>
@@ -15571,7 +15645,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>lynde</t>
+          <t>barry</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -15580,37 +15654,33 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>¿Así que tú eres la huérfana de Tejas Verdes? Ya iré a verte con calma, ya.</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
+          <t>Diana me ayudó con las manzanas. Llévale algunas a Marilla.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>barry_presenta</t>
+        </is>
+      </c>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>sabe:lynde:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>lynde</t>
+          <t>barry</t>
         </is>
       </c>
       <c r="B48" s="8">
@@ -15619,28 +15689,32 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Hmpf. No tengo nada que hablar contigo, niña malcriada.</t>
+          <t>Pasa, pasa, que hace un frío terrible. Diana está junto al fuego.</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>barry_presenta</t>
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>disculpa_lynde</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>escena_ana:os</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -15659,15 +15733,27 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Desde mi ventana veo todo el camino: no se me escapa nadie. Lo digo sin mala intención, ¿eh?</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr"/>
+          <t>¿Así que tú eres la huérfana de Tejas Verdes? Ya iré a verte con calma, ya.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="inlineStr"/>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>lynde_visita</t>
+        </is>
+      </c>
       <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="9" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>sabe:lynde:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -15686,13 +15772,21 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Llevo cincuenta y dos cubrecamas de retazos, ¡cincuenta y dos! Y no pienso parar.</t>
+          <t>Hmpf. No tengo nada que hablar contigo, niña malcriada.</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr"/>
-      <c r="F50" s="7" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>disculpa_lynde</t>
+        </is>
+      </c>
       <c r="I50" s="7" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr"/>
     </row>
@@ -15713,15 +15807,11 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Marilla hizo bien en quedarse contigo, y lo digo yo, que nunca me callo lo que pienso.</t>
+          <t>Desde mi ventana veo todo el camino: no se me escapa nadie. Lo digo sin mala intención, ¿eh?</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>se_queda</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -15729,11 +15819,7 @@
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>hecho:lynde_visita</t>
-        </is>
-      </c>
+      <c r="J51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -15752,17 +15838,17 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>A una niña hay que enseñarle a ser útil. Pero, bueno, tú vas por buen camino.</t>
+          <t>Llevo cincuenta y dos cubrecamas de retazos, ¡cincuenta y dos! Y no pienso parar.</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>lynde_visita</t>
-        </is>
-      </c>
+      <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I52" s="7" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr"/>
     </row>
@@ -15783,13 +15869,13 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Ana Shirley, hablas más que un molino... pero tienes buen corazón, eso lo reconozco.</t>
+          <t>Marilla hizo bien en quedarse contigo, y lo digo yo, que nunca me callo lo que pienso.</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>se_queda</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
@@ -15799,7 +15885,11 @@
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="9" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>hecho:lynde_visita</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -15813,12 +15903,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>¡Vaya, vaya, ya brotó todo! Ya es hora de limpiar la casa, digo yo.</t>
+          <t>A una niña hay que enseñarle a ser útil. Pero, bueno, tú vas por buen camino.</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -15828,7 +15918,11 @@
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I54" s="7" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
     </row>
@@ -15844,12 +15938,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Con este calor no hay quien teja... ¡pero yo tejo, claro que tejo!</t>
+          <t>Ana Shirley, hablas más que un molino... pero tienes buen corazón, eso lo reconozco.</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
@@ -15859,7 +15953,11 @@
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="9" t="inlineStr"/>
     </row>
@@ -15875,12 +15973,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>El otoño siempre me hace pensar en los cubrecamas. Este año haré uno rojo y dorado.</t>
+          <t>¡Vaya, vaya, ya brotó todo! Ya es hora de limpiar la casa, digo yo.</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr"/>
@@ -15890,7 +15988,11 @@
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr"/>
     </row>
@@ -15906,12 +16008,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Pasa, niña, que hace un frío de mil demonios... perdón, de los que dan escalofríos.</t>
+          <t>Con este calor no hay quien teja... ¡pero yo tejo, claro que tejo!</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr"/>
@@ -15921,14 +16023,18 @@
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I57" s="7" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>harrison</t>
+          <t>lynde</t>
         </is>
       </c>
       <c r="B58" s="8">
@@ -15937,25 +16043,33 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Hmpf. Buenos días... si es que son buenos.</t>
+          <t>El otoño siempre me hace pensar en los cubrecamas. Este año haré uno rojo y dorado.</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>lynde_visita</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>harrison</t>
+          <t>lynde</t>
         </is>
       </c>
       <c r="B59" s="8">
@@ -15964,26 +16078,32 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>¿Esa vaca tuya se ha portado bien hoy? Más le vale.</t>
+          <t>Pasa, niña, que hace un frío de mil demonios... perdón, de los que dan escalofríos.</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>conoce_harrison</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
+          <t>lynde_visita</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>escena_ana:rl</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -16002,7 +16122,7 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>No me mires la casa, que el desorden es mío.</t>
+          <t>Hmpf. Buenos días... si es que son buenos.</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
@@ -16029,12 +16149,18 @@
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Ginger, ¡silencio!... No le hagas caso, muchacha.</t>
+          <t>¿Esa vaca tuya se ha portado bien hoy? Más le vale.</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr"/>
-      <c r="F61" s="7" t="inlineStr"/>
-      <c r="G61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>conoce_harrison</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr"/>
@@ -16051,12 +16177,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>La avena ya asoma. Que nadie la pise, ¿eh?</t>
+          <t>No me mires la casa, que el desorden es mío.</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr"/>
@@ -16078,12 +16204,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Calor de mil demonios para segar... con perdón.</t>
+          <t>Ginger, ¡silencio!... No le hagas caso, muchacha.</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
@@ -16105,12 +16231,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Buena cosecha este año, aunque no lo diga mucho.</t>
+          <t>La avena ya asoma. Que nadie la pise, ¿eh?</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
@@ -16132,12 +16258,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Con este frío, ni Ginger quiere hablar. Bueno, sí quiere.</t>
+          <t>Calor de mil demonios para segar... con perdón.</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr"/>
@@ -16150,7 +16276,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>shearer</t>
+          <t>harrison</t>
         </is>
       </c>
       <c r="B66" s="8">
@@ -16159,12 +16285,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Buen día, señorita. ¿Algún animal para vender?</t>
+          <t>Buena cosecha este año, aunque no lo diga mucho.</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
@@ -16177,7 +16303,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>shearer</t>
+          <t>harrison</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -16186,12 +16312,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Ando apurado: me esperan en Carmody.</t>
+          <t>Con este frío, ni Ginger quiere hablar. Bueno, sí quiere.</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
@@ -16218,7 +16344,7 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Buena tierra la de por aquí, sí señor.</t>
+          <t>Buen día, señorita. ¿Algún animal para vender?</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
@@ -16240,12 +16366,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Primavera: buen tiempo para comprar terneros.</t>
+          <t>Ando apurado: me esperan en Carmody.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
@@ -16267,12 +16393,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Con este calor las vacas dan menos leche, ¿sabía?</t>
+          <t>Buena tierra la de por aquí, sí señor.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
@@ -16294,12 +16420,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>En otoño se vende bien el ganado.</t>
+          <t>Primavera: buen tiempo para comprar terneros.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr"/>
@@ -16321,12 +16447,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>En invierno casi no salgo, pero hoy hacía falta.</t>
+          <t>Con este calor las vacas dan menos leche, ¿sabía?</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
@@ -16339,7 +16465,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>gilbert</t>
+          <t>shearer</t>
         </is>
       </c>
       <c r="B73" s="8">
@@ -16348,20 +16474,16 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>¡Buenos días, Zanahorias!... Perdón, perdón. Era una broma, Ana.</t>
+          <t>En otoño se vende bien el ganado.</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="inlineStr"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
@@ -16370,7 +16492,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>gilbert</t>
+          <t>shearer</t>
         </is>
       </c>
       <c r="B74" s="8">
@@ -16379,20 +16501,16 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>¿Me vas a hablar algún día, Ana Shirley?</t>
+          <t>En invierno casi no salgo, pero hoy hacía falta.</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="inlineStr"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="inlineStr"/>
       <c r="I74" s="7" t="inlineStr"/>
@@ -16415,18 +16533,16 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Te gané en ortografía. Pero en composición... bueno, ahí ganas tú.</t>
+          <t>¡Buenos días, Zanahorias!... Perdón, perdón. Era una broma, Ana.</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>3</v>
-      </c>
+          <t>zanahorias</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="9" t="inlineStr"/>
@@ -16448,15 +16564,15 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>¿Quieres que te ayude a cruzar el arroyo? ¿No? Bueno...</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr"/>
+          <t>¿Me vas a hablar algún día, Ana Shirley?</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="inlineStr"/>
       <c r="I76" s="7" t="inlineStr"/>
@@ -16474,21 +16590,23 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Hmpf.</t>
+          <t>Te gané en ortografía. Pero en composición... bueno, ahí ganas tú.</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="n"/>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr"/>
@@ -16505,20 +16623,20 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>No le hablo a Gilbert Blythe. Nunca jamás.</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
+          <t>¿Quieres que te ayude a cruzar el arroyo? ¿No? Bueno...</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
@@ -16541,7 +16659,7 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>(Ana sigue de largo con la nariz en alto.)</t>
+          <t>Hmpf.</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr"/>
@@ -16558,7 +16676,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>buhonero</t>
+          <t>gilbert</t>
         </is>
       </c>
       <c r="B80" s="8">
@@ -16567,16 +16685,20 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>¡Cintas, botones, peinetas, tinte para el pelo! ¡Todo lo que una señorita necesita!</t>
+          <t>No le hablo a Gilbert Blythe. Nunca jamás.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr"/>
-      <c r="F80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr"/>
@@ -16585,7 +16707,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>buhonero</t>
+          <t>gilbert</t>
         </is>
       </c>
       <c r="B81" s="8">
@@ -16594,16 +16716,20 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Un tinte que deja el pelo negro azabache, señorita. Garantizado.</t>
+          <t>(Ana sigue de largo con la nariz en alto.)</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
@@ -16612,7 +16738,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>josie</t>
+          <t>buhonero</t>
         </is>
       </c>
       <c r="B82" s="8">
@@ -16626,7 +16752,7 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>¿Ese vestido es nuevo, Ana? Ah, no... es el de siempre.</t>
+          <t>¡Cintas, botones, peinetas, tinte para el pelo! ¡Todo lo que una señorita necesita!</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr"/>
@@ -16639,7 +16765,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>josie</t>
+          <t>buhonero</t>
         </is>
       </c>
       <c r="B83" s="8">
@@ -16653,7 +16779,7 @@
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Te apuesto a que no te atreves a caminar por el techo de la casa de los Barry.</t>
+          <t>Un tinte que deja el pelo negro azabache, señorita. Garantizado.</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr"/>
@@ -16680,7 +16806,7 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá dice que las pelirrojas tienen mal genio. ¿Es verdad?</t>
+          <t>¿Ese vestido es nuevo, Ana? Ah, no... es el de siempre.</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr"/>
@@ -16702,12 +16828,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Josie Pye, eres... ¡eres una Pye!</t>
+          <t>Te apuesto a que no te atreves a caminar por el techo de la casa de los Barry.</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr"/>
@@ -16729,12 +16855,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>No pienso contestarte eso.</t>
+          <t>Mi mamá dice que las pelirrojas tienen mal genio. ¿Es verdad?</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr"/>
@@ -16747,7 +16873,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>gertie</t>
+          <t>josie</t>
         </is>
       </c>
       <c r="B87" s="8">
@@ -16756,23 +16882,17 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Josie dice que tú inventas palabras difíciles para lucirte.</t>
+          <t>Josie Pye, eres... ¡eres una Pye!</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="9" t="inlineStr"/>
@@ -16780,7 +16900,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>gertie</t>
+          <t>josie</t>
         </is>
       </c>
       <c r="B88" s="8">
@@ -16789,23 +16909,17 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>¿Me prestas tu lápiz? El mío se perdió... otra vez.</t>
+          <t>No pienso contestarte eso.</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr"/>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="7" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr"/>
@@ -16813,7 +16927,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>gertie</t>
         </is>
       </c>
       <c r="B89" s="8">
@@ -16827,20 +16941,28 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>¡Ay, Ana! ¿Viste cómo me miró Charlie Sloane?</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr"/>
+          <t>Josie dice que tú hablas como un libro. ¿Es verdad? Di algo difícil.</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>!dias_desde:escuela:3</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>gertie</t>
         </is>
       </c>
       <c r="B90" s="8">
@@ -16854,12 +16976,18 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Mi hermana tiene un pretendiente nuevo. ¡Es tan romántico!</t>
+          <t>Josie dice que tú inventas palabras difíciles para lucirte.</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr"/>
-      <c r="F90" s="7" t="inlineStr"/>
-      <c r="G90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="7" t="inlineStr"/>
       <c r="J90" s="9" t="inlineStr"/>
@@ -16867,7 +16995,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>gertie</t>
         </is>
       </c>
       <c r="B91" s="8">
@@ -16881,12 +17009,18 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>¿Vamos a ver las botellas de leche en el río? La mía tiene una cinta azul.</t>
+          <t>¿Me prestas tu lápiz? El mío se perdió... otra vez.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="7" t="inlineStr"/>
       <c r="J91" s="9" t="inlineStr"/>
@@ -16894,7 +17028,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="B92" s="8">
@@ -16908,18 +17042,12 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>¿Hiciste los problemas de aritmética? Yo los hice dos veces, por si acaso.</t>
+          <t>¡Ay, Ana! ¿Viste cómo me miró Charlie Sloane?</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="9" t="inlineStr"/>
@@ -16927,7 +17055,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="B93" s="8">
@@ -16941,14 +17069,10 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá dice que eres muy imaginativa. No sé si lo dice como algo bueno.</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>Mi hermana tiene un pretendiente nuevo. ¡Es tan romántico!</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="inlineStr"/>
@@ -16958,7 +17082,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>prissy</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="B94" s="8">
@@ -16972,7 +17096,7 @@
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>El año que viene voy a estudiar para entrar a Queen's.</t>
+          <t>¿Vamos a ver las botellas de leche en el río? La mía tiene una cinta azul.</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr"/>
@@ -16985,7 +17109,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>prissy</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="B95" s="8">
@@ -16999,12 +17123,18 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Ya tengo dieciséis años, ¿sabes? Casi una señorita.</t>
+          <t>¿Hiciste los problemas de aritmética? Yo los hice dos veces, por si acaso.</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="n"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="9" t="inlineStr"/>
@@ -17012,7 +17142,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>charlie</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="B96" s="8">
@@ -17026,18 +17156,16 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Ana, ¿quieres... quieres usar mi pizarra nueva? Prestada, digo.</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr"/>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="n">
-        <v>3</v>
-      </c>
+          <t>Mi mamá dice que eres muy imaginativa. No sé si lo dice como algo bueno.</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="7" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr"/>
@@ -17045,7 +17173,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>charlie</t>
+          <t>prissy</t>
         </is>
       </c>
       <c r="B97" s="8">
@@ -17059,14 +17187,10 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá hizo tarta de grosellas. Te guardé un pedazo... si quieres.</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>El año que viene voy a estudiar para entrar a Queen's.</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr"/>
       <c r="G97" s="7" t="n"/>
       <c r="H97" s="7" t="inlineStr"/>
@@ -17076,7 +17200,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>moody</t>
+          <t>prissy</t>
         </is>
       </c>
       <c r="B98" s="8">
@@ -17090,7 +17214,7 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Voy a ser pastor cuando sea grande. Ya practico los sermones con las vacas.</t>
+          <t>Ya tengo dieciséis años, ¿sabes? Casi una señorita.</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
@@ -17103,7 +17227,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>moody</t>
+          <t>charlie</t>
         </is>
       </c>
       <c r="B99" s="8">
@@ -17117,12 +17241,18 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Ayer el maestro me dejó sin recreo. Fue injusto, aunque sí me reí en la oración.</t>
+          <t>Ana, ¿quieres... quieres usar mi pizarra nueva? Prestada, digo.</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr"/>
-      <c r="F99" s="7" t="inlineStr"/>
-      <c r="G99" s="7" t="n"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr"/>
       <c r="J99" s="9" t="inlineStr"/>
@@ -17130,7 +17260,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>tillie</t>
+          <t>charlie</t>
         </is>
       </c>
       <c r="B100" s="8">
@@ -17144,10 +17274,14 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>¿Juegas a la mancha? ¡Tú la llevas!</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
+          <t>Mi mamá hizo tarta de grosellas. Te guardé un pedazo... si quieres.</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F100" s="7" t="inlineStr"/>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="inlineStr"/>
@@ -17157,7 +17291,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>tillie</t>
+          <t>moody</t>
         </is>
       </c>
       <c r="B101" s="8">
@@ -17171,7 +17305,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Encontré un nido de petirrojos detrás de la escuela. ¡No le digas a nadie!</t>
+          <t>Voy a ser pastor cuando sea grande. Ya practico los sermones con las vacas.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr"/>
@@ -17184,7 +17318,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>felicity</t>
+          <t>moody</t>
         </is>
       </c>
       <c r="B102" s="8">
@@ -17198,7 +17332,7 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Mi madre dice que una señorita nunca corre. Pero yo corro si llego tarde.</t>
+          <t>Ayer el maestro me dejó sin recreo. Fue injusto, aunque sí me reí en la oración.</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr"/>
@@ -17211,7 +17345,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>felicity</t>
+          <t>tillie</t>
         </is>
       </c>
       <c r="B103" s="8">
@@ -17225,7 +17359,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Esta mañana hice pan yo solita. Bueno, casi solita.</t>
+          <t>¿Juegas a la mancha? ¡Tú la llevas!</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr"/>
@@ -17238,7 +17372,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>felix</t>
+          <t>tillie</t>
         </is>
       </c>
       <c r="B104" s="8">
@@ -17252,7 +17386,7 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>¿Sabías que en el bosque de Peg Bowen vive una bruja de verdad?</t>
+          <t>Encontré un nido de petirrojos detrás de la escuela. ¡No le digas a nadie!</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr"/>
@@ -17265,7 +17399,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>felix</t>
+          <t>felicity</t>
         </is>
       </c>
       <c r="B105" s="8">
@@ -17279,7 +17413,7 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Estoy juntando valor para tocar la puerta de Peg Bowen. Mañana. O pasado.</t>
+          <t>Mi madre dice que una señorita nunca corre. Pero yo corro si llego tarde.</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
@@ -17292,7 +17426,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>cecily</t>
+          <t>felicity</t>
         </is>
       </c>
       <c r="B106" s="8">
@@ -17306,18 +17440,12 @@
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>¿Me enseñas a recitar como tú? Cuando tú recitas, me dan escalofríos.</t>
+          <t>Esta mañana hice pan yo solita. Bueno, casi solita.</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
       <c r="J106" s="9" t="inlineStr"/>
@@ -17325,7 +17453,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>cecily</t>
+          <t>felix</t>
         </is>
       </c>
       <c r="B107" s="8">
@@ -17339,7 +17467,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>¿Tú eres la niña de Tejas Verdes? Dicen que hablas como en los libros.</t>
+          <t>¿Sabías que en el bosque de Peg Bowen vive una bruja de verdad?</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr"/>
@@ -17347,16 +17475,12 @@
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>sabe:cecily:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>sara</t>
+          <t>felix</t>
         </is>
       </c>
       <c r="B108" s="8">
@@ -17370,7 +17494,7 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>¿Te cuento una historia? Es de un barco fantasma que se ve desde el faro las noches de niebla.</t>
+          <t>Estoy juntando valor para tocar la puerta de Peg Bowen. Mañana. O pasado.</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr"/>
@@ -17383,7 +17507,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>sara</t>
+          <t>cecily</t>
         </is>
       </c>
       <c r="B109" s="8">
@@ -17397,16 +17521,18 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>La tía Hetty dice que hablo demasiado. Tú también, ¿no? ¡Qué bien!</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr"/>
-      <c r="G109" s="7" t="n"/>
+          <t>¿Me enseñas a recitar como tú? Cuando tú recitas, me dan escalofríos.</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="7" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
@@ -17414,7 +17540,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>phillips</t>
+          <t>cecily</t>
         </is>
       </c>
       <c r="B110" s="8">
@@ -17428,26 +17554,24 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Señorita Shirley, ¿no debería estar repasando su ortografía?</t>
+          <t>¿Tú eres la niña de Tejas Verdes? Dicen que hablas como en los libros.</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr"/>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F110" s="7" t="inlineStr"/>
+      <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr"/>
-      <c r="J110" s="9" t="inlineStr"/>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>sabe:cecily:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>phillips</t>
+          <t>sara</t>
         </is>
       </c>
       <c r="B111" s="8">
@@ -17461,7 +17585,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Mañana hay examen de geometría. Que nadie lo olvide.</t>
+          <t>¿Te cuento una historia? Es de un barco fantasma que se ve desde el faro las noches de niebla.</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr"/>
@@ -17474,7 +17598,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>allan</t>
+          <t>sara</t>
         </is>
       </c>
       <c r="B112" s="8">
@@ -17488,10 +17612,14 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Que Dios te bendiga, Ana. ¿Te veremos el domingo en la escuela dominical?</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr"/>
+          <t>La tía Hetty dice que hablo demasiado. Tú también, ¿no? ¡Qué bien!</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F112" s="7" t="inlineStr"/>
       <c r="G112" s="7" t="n"/>
       <c r="H112" s="7" t="inlineStr"/>
@@ -17501,7 +17629,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>allan</t>
+          <t>phillips</t>
         </is>
       </c>
       <c r="B113" s="8">
@@ -17515,20 +17643,24 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Hermoso día para dar gracias, ¿no te parece?</t>
+          <t>¡Vacaciones, por fin! Hasta los maestros las necesitamos, señorita.</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr"/>
       <c r="G113" s="7" t="n"/>
       <c r="H113" s="7" t="inlineStr"/>
-      <c r="I113" s="7" t="inlineStr"/>
+      <c r="I113" s="7" t="inlineStr">
+        <is>
+          <t>verano</t>
+        </is>
+      </c>
       <c r="J113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>sraallan</t>
+          <t>phillips</t>
         </is>
       </c>
       <c r="B114" s="8">
@@ -17542,20 +17674,30 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>¡Ana, querida! ¡Qué gusto verte! ¿Cómo van tus estudios?</t>
+          <t>Señorita Shirley, ¿no debería estar repasando su ortografía?</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
-      <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="7" t="n"/>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
-      <c r="J114" s="9" t="inlineStr"/>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>!estacion:verano</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>sraallan</t>
+          <t>phillips</t>
         </is>
       </c>
       <c r="B115" s="8">
@@ -17569,24 +17711,24 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Me encantó tu recitación. Tienes un don, Ana.</t>
+          <t>Mañana hay examen de geometría. Que nadie lo olvide.</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr"/>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>escuela_dominical</t>
-        </is>
-      </c>
+      <c r="F115" s="7" t="inlineStr"/>
       <c r="G115" s="7" t="n"/>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="9" t="inlineStr"/>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>!estacion:verano</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>sraallan</t>
+          <t>allan</t>
         </is>
       </c>
       <c r="B116" s="8">
@@ -17600,7 +17742,7 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Qué tarde tan linda para pasear, ¿verdad?</t>
+          <t>Que Dios te bendiga, Ana. ¿Te veremos el domingo en la escuela dominical?</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
@@ -17613,7 +17755,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>sraallan</t>
+          <t>allan</t>
         </is>
       </c>
       <c r="B117" s="8">
@@ -17622,19 +17764,15 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>¡Oh, Sra. Allan! Usted es mi espíritu afín.</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>Hermoso día para dar gracias, ¿no te parece?</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr"/>
       <c r="G117" s="7" t="n"/>
       <c r="H117" s="7" t="inlineStr"/>
@@ -17644,7 +17782,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>lawson</t>
+          <t>sraallan</t>
         </is>
       </c>
       <c r="B118" s="8">
@@ -17658,7 +17796,7 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>¡Buenos días, Ana! Llegaron caramelos de menta y cintas nuevas.</t>
+          <t>¡Ana, querida! ¡Qué gusto verte! ¿Cómo van tus estudios?</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr"/>
@@ -17671,7 +17809,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>lawson</t>
+          <t>sraallan</t>
         </is>
       </c>
       <c r="B119" s="8">
@@ -17685,11 +17823,15 @@
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>¿Qué te manda Marilla hoy? ¿Azúcar? ¿Hilo?</t>
+          <t>Me encantó tu recitación. Tienes un don, Ana.</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr"/>
-      <c r="F119" s="7" t="inlineStr"/>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>escuela_dominical</t>
+        </is>
+      </c>
       <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="inlineStr"/>
       <c r="I119" s="7" t="inlineStr"/>
@@ -17698,7 +17840,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>herrero</t>
+          <t>sraallan</t>
         </is>
       </c>
       <c r="B120" s="8">
@@ -17712,7 +17854,7 @@
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>¡Cuidado con las chispas, niña!</t>
+          <t>Qué tarde tan linda para pasear, ¿verdad?</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr"/>
@@ -17725,7 +17867,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>herrero</t>
+          <t>sraallan</t>
         </is>
       </c>
       <c r="B121" s="8">
@@ -17734,15 +17876,19 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>El caballo del Sr. Barry perdió una herradura. Otra vez.</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr"/>
+          <t>¡Oh, Sra. Allan! Usted es mi espíritu afín.</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F121" s="7" t="inlineStr"/>
       <c r="G121" s="7" t="n"/>
       <c r="H121" s="7" t="inlineStr"/>
@@ -17752,7 +17898,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>lawson</t>
         </is>
       </c>
       <c r="B122" s="8">
@@ -17766,7 +17912,7 @@
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>¿Tienes alguna noticia para La Crónica, Ana? Se me acabaron las historias.</t>
+          <t>¡Buenos días, Ana! Llegaron caramelos de menta y cintas nuevas.</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr"/>
@@ -17779,7 +17925,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>lawson</t>
         </is>
       </c>
       <c r="B123" s="8">
@@ -17793,7 +17939,7 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Si escribes un cuento bonito, te lo publico. Palabra de editor.</t>
+          <t>¿Qué te manda Marilla hoy? ¿Azúcar? ¿Hilo?</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
@@ -17806,7 +17952,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>hetty</t>
+          <t>herrero</t>
         </is>
       </c>
       <c r="B124" s="8">
@@ -17820,7 +17966,7 @@
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Los niños de hoy no saben estarse quietos. En mis tiempos...</t>
+          <t>¡Cuidado con las chispas, niña!</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
@@ -17833,7 +17979,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>hetty</t>
+          <t>herrero</t>
         </is>
       </c>
       <c r="B125" s="8">
@@ -17847,7 +17993,7 @@
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Señorita, no se corre por la calle principal. ¡Y menos con el sombrero torcido!</t>
+          <t>El caballo del Sr. Barry perdió una herradura. Otra vez.</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr"/>
@@ -17860,7 +18006,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>olivia</t>
+          <t>editor</t>
         </is>
       </c>
       <c r="B126" s="8">
@@ -17874,7 +18020,7 @@
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>¡Hola, Ana! ¿No es un día perfecto para un picnic?</t>
+          <t>¿Tienes alguna noticia para La Crónica, Ana? Se me acabaron las historias.</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr"/>
@@ -17887,7 +18033,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>olivia</t>
+          <t>editor</t>
         </is>
       </c>
       <c r="B127" s="8">
@@ -17901,7 +18047,7 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Jasper Dale me saludó esta mañana. Bueno... casi me saludó.</t>
+          <t>Si escribes un cuento bonito, te lo publico. Palabra de editor.</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
@@ -17914,7 +18060,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>jasper</t>
+          <t>hetty</t>
         </is>
       </c>
       <c r="B128" s="8">
@@ -17928,7 +18074,7 @@
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>B-buenos días. Estoy... estoy probando un invento. Para la lluvia.</t>
+          <t>Los niños de hoy no saben estarse quietos. En mis tiempos...</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr"/>
@@ -17941,7 +18087,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>jasper</t>
+          <t>hetty</t>
         </is>
       </c>
       <c r="B129" s="8">
@@ -17955,7 +18101,7 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Si ves a la Srta. Olivia... no, nada. No le digas nada.</t>
+          <t>Señorita, no se corre por la calle principal. ¡Y menos con el sombrero torcido!</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr"/>
@@ -17968,7 +18114,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>alec</t>
+          <t>olivia</t>
         </is>
       </c>
       <c r="B130" s="8">
@@ -17982,7 +18128,7 @@
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Buen día para la siega, Ana. ¡Si no llueve!</t>
+          <t>¡Hola, Ana! ¿No es un día perfecto para un picnic?</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr"/>
@@ -17995,7 +18141,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>alec</t>
+          <t>olivia</t>
         </is>
       </c>
       <c r="B131" s="8">
@@ -18009,7 +18155,7 @@
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Saluda a Matthew de mi parte. Hace tiempo que no conversamos.</t>
+          <t>Jasper Dale me saludó esta mañana. Bueno... casi me saludó.</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr"/>
@@ -18022,7 +18168,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>jasper</t>
         </is>
       </c>
       <c r="B132" s="8">
@@ -18036,7 +18182,7 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>¿Has visto a Felix? Tendría que estar trayendo leña.</t>
+          <t>B-buenos días. Estoy... estoy probando un invento. Para la lluvia.</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr"/>
@@ -18049,7 +18195,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>jasper</t>
         </is>
       </c>
       <c r="B133" s="8">
@@ -18063,7 +18209,7 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Dile a Marilla que le devuelvo la fuente el sábado.</t>
+          <t>Si ves a la Srta. Olivia... no, nada. No le digas nada.</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr"/>
@@ -18076,7 +18222,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>srapye</t>
+          <t>alec</t>
         </is>
       </c>
       <c r="B134" s="8">
@@ -18090,7 +18236,7 @@
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>¿Ya supiste lo del Sr. Harrison? Dicen que su loro dice cosas terribles.</t>
+          <t>Buen día para la siega, Ana. ¡Si no llueve!</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
@@ -18103,7 +18249,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>srapye</t>
+          <t>alec</t>
         </is>
       </c>
       <c r="B135" s="8">
@@ -18117,7 +18263,7 @@
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Pelo rojo, genio vivo, como dice el refrán.</t>
+          <t>Saluda a Matthew de mi parte. Hace tiempo que no conversamos.</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
@@ -18130,7 +18276,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>sloane</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B136" s="8">
@@ -18144,7 +18290,7 @@
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Las papas vienen buenas este año. Ya lo verás.</t>
+          <t>¿Has visto a Felix? Tendría que estar trayendo leña.</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
@@ -18157,7 +18303,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>andrews</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B137" s="8">
@@ -18171,7 +18317,7 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Buenas tardes. ¿Va todo bien en Tejas Verdes?</t>
+          <t>Dile a Marilla que le devuelvo la fuente el sábado.</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
@@ -18184,7 +18330,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>peg</t>
+          <t>srapye</t>
         </is>
       </c>
       <c r="B138" s="8">
@@ -18198,7 +18344,7 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Je, je. ¿Tú eres la pelirroja de los Cuthbert? Dile a Marilla que Peg Bowen la saluda.</t>
+          <t>¿Ya supiste lo del Sr. Harrison? Dicen que su loro dice cosas terribles.</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr"/>
@@ -18211,7 +18357,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>peg</t>
+          <t>srapye</t>
         </is>
       </c>
       <c r="B139" s="8">
@@ -18225,7 +18371,7 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>En el bosque no hay brujas, niña. Solo estoy yo... je, je.</t>
+          <t>Pelo rojo, genio vivo, como dice el refrán.</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
@@ -18238,7 +18384,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>peg</t>
+          <t>sloane</t>
         </is>
       </c>
       <c r="B140" s="8">
@@ -18247,12 +18393,12 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>(¡Es Peg Bowen! Felix dice que es una bruja...)</t>
+          <t>Las papas vienen buenas este año. Ya lo verás.</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr"/>
@@ -18265,7 +18411,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>farero</t>
+          <t>andrews</t>
         </is>
       </c>
       <c r="B141" s="8">
@@ -18279,7 +18425,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Ese faro lleva cuarenta años encendido, y yo con él. Las noches de tormenta son las más hermosas.</t>
+          <t>Buenas tardes. ¿Va todo bien en Tejas Verdes?</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
@@ -18292,7 +18438,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>farero</t>
+          <t>peg</t>
         </is>
       </c>
       <c r="B142" s="8">
@@ -18306,7 +18452,7 @@
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>¿Ves esa vela allá lejos? Va a Charlottetown. Antes yo navegaba hasta las Antillas.</t>
+          <t>Je, je. ¿Tú eres la pelirroja de los Cuthbert? Dile a Marilla que Peg Bowen la saluda.</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
@@ -18319,7 +18465,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>farero</t>
+          <t>peg</t>
         </is>
       </c>
       <c r="B143" s="8">
@@ -18333,7 +18479,7 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Si subes al faro al atardecer, el mar se pone de oro. Pregúntale a cualquier gaviota.</t>
+          <t>En el bosque no hay brujas, niña. Solo estoy yo... je, je.</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
@@ -18346,7 +18492,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>farero</t>
+          <t>peg</t>
         </is>
       </c>
       <c r="B144" s="8">
@@ -18360,7 +18506,7 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>¡Capitán Jim, cuénteme una historia del mar!</t>
+          <t>(¡Es Peg Bowen! Felix dice que es una bruja...)</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
@@ -18382,12 +18528,12 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>¡Qué vida tan romántica la de un farero!</t>
+          <t>Ese faro lleva cuarenta años encendido, y yo con él. Las noches de tormenta son las más hermosas.</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
@@ -18400,7 +18546,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>stacy</t>
+          <t>farero</t>
         </is>
       </c>
       <c r="B146" s="8">
@@ -18414,18 +18560,12 @@
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Ana, tu composición fue la mejor de la clase. Pero cuidado con los adjetivos: ¡no hacen falta tantos!</t>
+          <t>¿Ves esa vela allá lejos? Va a Charlottetown. Antes yo navegaba hasta las Antillas.</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr"/>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F146" s="7" t="inlineStr"/>
+      <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="inlineStr"/>
       <c r="I146" s="7" t="inlineStr"/>
       <c r="J146" s="9" t="inlineStr"/>
@@ -18433,7 +18573,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>stacy</t>
+          <t>farero</t>
         </is>
       </c>
       <c r="B147" s="8">
@@ -18447,7 +18587,7 @@
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>El viernes por la tarde salimos al bosque a estudiar botánica. ¿Te apuntas?</t>
+          <t>Si subes al faro al atardecer, el mar se pone de oro. Pregúntale a cualquier gaviota.</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
@@ -18460,7 +18600,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>stacy</t>
+          <t>farero</t>
         </is>
       </c>
       <c r="B148" s="8">
@@ -18469,12 +18609,12 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Este año preparamos a los mejores para el examen de Queen's. Tú puedes, Ana.</t>
+          <t>¡Capitán Jim, cuénteme una historia del mar!</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr"/>
@@ -18482,16 +18622,12 @@
       <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="inlineStr"/>
       <c r="I148" s="7" t="inlineStr"/>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>estudio:ana&gt;=20</t>
-        </is>
-      </c>
+      <c r="J148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>stacy</t>
+          <t>farero</t>
         </is>
       </c>
       <c r="B149" s="8">
@@ -18505,14 +18641,10 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>¡Srta. Stacy! Usted es mi espíritu afín, ¿lo sabía?</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>¡Qué vida tan romántica la de un farero!</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr"/>
       <c r="G149" s="7" t="n"/>
       <c r="H149" s="7" t="inlineStr"/>
@@ -18522,7 +18654,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>minnie</t>
+          <t>stacy</t>
         </is>
       </c>
       <c r="B150" s="8">
@@ -18536,16 +18668,18 @@
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>¡Ana! ¿Me cuentas el cuento del hada otra vez?</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr"/>
-      <c r="G150" s="7" t="n"/>
+          <t>Ana, tu composición fue la mejor de la clase. Pero cuidado con los adjetivos: ¡no hacen falta tantos!</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr"/>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H150" s="7" t="inlineStr"/>
       <c r="I150" s="7" t="inlineStr"/>
       <c r="J150" s="9" t="inlineStr"/>
@@ -18553,7 +18687,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>minnie</t>
+          <t>stacy</t>
         </is>
       </c>
       <c r="B151" s="8">
@@ -18567,14 +18701,10 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Diana no me deja jugar con sus muñecas. ¿Tú me dejas?</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>El viernes por la tarde salimos al bosque a estudiar botánica. ¿Te apuntas?</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr"/>
       <c r="G151" s="7" t="n"/>
       <c r="H151" s="7" t="inlineStr"/>
@@ -18584,7 +18714,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>minnie</t>
+          <t>stacy</t>
         </is>
       </c>
       <c r="B152" s="8">
@@ -18598,7 +18728,7 @@
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>¿Tú eres la niña nueva de Tejas Verdes? Mamá dice que eres pelirroja. ¡Y es verdad!</t>
+          <t>Este año preparamos a los mejores para el examen de Queen's. Tú puedes, Ana.</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
@@ -18608,14 +18738,14 @@
       <c r="I152" s="7" t="inlineStr"/>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>sabe:minnie:nina_cuthbert</t>
+          <t>estudio:ana&gt;=20</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>minnie</t>
+          <t>stacy</t>
         </is>
       </c>
       <c r="B153" s="8">
@@ -18624,20 +18754,20 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Ya no tengo tos. ¡Mamá dice que tú me salvaste!</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr"/>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+          <t>¡Srta. Stacy! Usted es mi espíritu afín, ¿lo sabía?</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr"/>
       <c r="G153" s="7" t="n"/>
       <c r="H153" s="7" t="inlineStr"/>
       <c r="I153" s="7" t="inlineStr"/>
@@ -18646,7 +18776,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>srbarry</t>
+          <t>minnie</t>
         </is>
       </c>
       <c r="B154" s="8">
@@ -18660,10 +18790,14 @@
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Buenas, Ana. Diana está en la casa, creo. O en el huerto.</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr"/>
+          <t>¡Ana! ¿Me cuentas el cuento del hada otra vez?</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="n"/>
       <c r="H154" s="7" t="inlineStr"/>
@@ -18673,7 +18807,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>srbarry</t>
+          <t>minnie</t>
         </is>
       </c>
       <c r="B155" s="8">
@@ -18687,10 +18821,14 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>El heno está listo para entrar. Si no llueve, mañana lo cargamos.</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr"/>
+          <t>Diana no me deja jugar con sus muñecas. ¿Tú me dejas?</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F155" s="7" t="inlineStr"/>
       <c r="G155" s="7" t="n"/>
       <c r="H155" s="7" t="inlineStr"/>
@@ -18700,7 +18838,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>maryjoe</t>
+          <t>minnie</t>
         </is>
       </c>
       <c r="B156" s="8">
@@ -18714,24 +18852,24 @@
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>¡Ay, señorita Ana! Yo no sé nada de enfermedades, menos mal que usted vino aquella noche.</t>
+          <t>¿Tú eres la niña nueva de Tejas Verdes? Mamá dice que eres pelirroja. ¡Y es verdad!</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="F156" s="7" t="inlineStr"/>
       <c r="G156" s="7" t="n"/>
       <c r="H156" s="7" t="inlineStr"/>
       <c r="I156" s="7" t="inlineStr"/>
-      <c r="J156" s="9" t="inlineStr"/>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>sabe:minnie:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>maryjoe</t>
+          <t>minnie</t>
         </is>
       </c>
       <c r="B157" s="8">
@@ -18745,11 +18883,15 @@
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>La señora Barry dice que tienda la ropa antes de que se nuble.</t>
+          <t>Ya no tengo tos. ¡Mamá dice que tú me salvaste!</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
-      <c r="F157" s="7" t="inlineStr"/>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>perdonada</t>
+        </is>
+      </c>
       <c r="G157" s="7" t="n"/>
       <c r="H157" s="7" t="inlineStr"/>
       <c r="I157" s="7" t="inlineStr"/>
@@ -18758,7 +18900,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>jerry</t>
+          <t>srbarry</t>
         </is>
       </c>
       <c r="B158" s="8">
@@ -18772,7 +18914,7 @@
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>El Sr. Cuthbert me pidió que entrara la leña antes de la cena.</t>
+          <t>Buenas, Ana. Diana está en la casa, creo. O en el huerto.</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
@@ -18785,7 +18927,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>jerry</t>
+          <t>srbarry</t>
         </is>
       </c>
       <c r="B159" s="8">
@@ -18799,7 +18941,7 @@
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>Oui, oui... ya voy, ya voy. ¡Esa vaca no se quiere mover!</t>
+          <t>El heno está listo para entrar. Si no llueve, mañana lo cargamos.</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
@@ -18812,7 +18954,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>medico</t>
+          <t>maryjoe</t>
         </is>
       </c>
       <c r="B160" s="8">
@@ -18826,11 +18968,15 @@
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>¿Alguien enfermo en Tejas Verdes? Espero que no.</t>
+          <t>¡Ay, señorita Ana! Yo no sé nada de enfermedades, menos mal que usted vino aquella noche.</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr"/>
-      <c r="F160" s="7" t="inlineStr"/>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>perdonada</t>
+        </is>
+      </c>
       <c r="G160" s="7" t="n"/>
       <c r="H160" s="7" t="inlineStr"/>
       <c r="I160" s="7" t="inlineStr"/>
@@ -18839,7 +18985,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>medico</t>
+          <t>maryjoe</t>
         </is>
       </c>
       <c r="B161" s="8">
@@ -18853,15 +18999,11 @@
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Esa niña Shirley tiene buena cabeza: salvó a la pequeña Barry del crup antes de que yo llegara.</t>
+          <t>La señora Barry dice que tienda la ropa antes de que se nuble.</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="F161" s="7" t="inlineStr"/>
       <c r="G161" s="7" t="n"/>
       <c r="H161" s="7" t="inlineStr"/>
       <c r="I161" s="7" t="inlineStr"/>
@@ -18870,7 +19012,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>srbell</t>
+          <t>jerry</t>
         </is>
       </c>
       <c r="B162" s="8">
@@ -18884,7 +19026,7 @@
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>Te esperamos el domingo en la escuela dominical, Ana. Y apréndete el versículo.</t>
+          <t>El Sr. Cuthbert me pidió que entrara la leña antes de la cena.</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
@@ -18897,7 +19039,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>srbell</t>
+          <t>jerry</t>
         </is>
       </c>
       <c r="B163" s="8">
@@ -18911,7 +19053,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>Una oración larga no es mejor que una sincera, niña.</t>
+          <t>Oui, oui... ya voy, ya voy. ¡Esa vaca no se quiere mover!</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
@@ -18924,7 +19066,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>medico</t>
         </is>
       </c>
       <c r="B164" s="8">
@@ -18938,7 +19080,7 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>Así que tú eres la niña de Tejas Verdes. Hmm. Ya veremos qué clase de niña eres.</t>
+          <t>¿Alguien enfermo en Tejas Verdes? Espero que no.</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
@@ -18946,16 +19088,12 @@
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="7" t="inlineStr"/>
       <c r="I164" s="7" t="inlineStr"/>
-      <c r="J164" s="9" t="inlineStr">
-        <is>
-          <t>sabe:josephine:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J164" s="9" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>medico</t>
         </is>
       </c>
       <c r="B165" s="8">
@@ -18969,13 +19107,13 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>¡La niña Ana! Desde que me saltaste encima en la cama, no me había reído tanto en años.</t>
+          <t>Esa niña Shirley tiene buena cabeza: salvó a la pequeña Barry del crup antes de que yo llegara.</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>cama_josephine</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="G165" s="7" t="n"/>
@@ -18986,7 +19124,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>srbell</t>
         </is>
       </c>
       <c r="B166" s="8">
@@ -19000,15 +19138,11 @@
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>Cuando vengas a Charlottetown, te alojas en mi casa. Te llevo a la exposición.</t>
+          <t>Te esperamos el domingo en la escuela dominical, Ana. Y apréndete el versículo.</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>cama_josephine</t>
-        </is>
-      </c>
+      <c r="F166" s="7" t="inlineStr"/>
       <c r="G166" s="7" t="n"/>
       <c r="H166" s="7" t="inlineStr"/>
       <c r="I166" s="7" t="inlineStr"/>
@@ -19017,7 +19151,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>srbell</t>
         </is>
       </c>
       <c r="B167" s="8">
@@ -19026,12 +19160,12 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>¡Srta. Barry! Usted es un espíritu afín, aunque no lo parezca a primera vista.</t>
+          <t>Una oración larga no es mejor que una sincera, niña.</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
@@ -19044,7 +19178,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>spencer</t>
+          <t>josephine</t>
         </is>
       </c>
       <c r="B168" s="8">
@@ -19058,7 +19192,7 @@
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>¡Ana! Qué bien te ves. Y yo que creí que los Cuthbert querían una niña… ¡qué enredo!</t>
+          <t>Así que tú eres la niña de Tejas Verdes. Hmm. Ya veremos qué clase de niña eres.</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
@@ -19066,12 +19200,16 @@
       <c r="G168" s="7" t="n"/>
       <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="7" t="inlineStr"/>
-      <c r="J168" s="9" t="inlineStr"/>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>sabe:josephine:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>spencer</t>
+          <t>josephine</t>
         </is>
       </c>
       <c r="B169" s="8">
@@ -19085,11 +19223,15 @@
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Mi Lily estuvo enferma, por eso no pude llevarte yo a Tejas Verdes.</t>
+          <t>¡La niña Ana! Desde que me saltaste encima en la cama, no me había reído tanto en años.</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
-      <c r="F169" s="7" t="inlineStr"/>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>cama_josephine</t>
+        </is>
+      </c>
       <c r="G169" s="7" t="n"/>
       <c r="H169" s="7" t="inlineStr"/>
       <c r="I169" s="7" t="inlineStr"/>
@@ -19098,7 +19240,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>blewett</t>
+          <t>josephine</t>
         </is>
       </c>
       <c r="B170" s="8">
@@ -19112,13 +19254,13 @@
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Así que te quedaste con los Cuthbert. Hmm. Yo te habría hecho trabajar de verdad.</t>
+          <t>Cuando vengas a Charlottetown, te alojas en mi casa. Te llevo a la exposición.</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>a_prueba</t>
+          <t>cama_josephine</t>
         </is>
       </c>
       <c r="G170" s="7" t="n"/>
@@ -19129,7 +19271,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>blewett</t>
+          <t>josephine</t>
         </is>
       </c>
       <c r="B171" s="8">
@@ -19138,12 +19280,12 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Hmm. Flacucha. En mi casa no hay tiempo para mirar las nubes, ¿sabes?</t>
+          <t>¡Srta. Barry! Usted es un espíritu afín, aunque no lo parezca a primera vista.</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
@@ -19156,7 +19298,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>blewett</t>
+          <t>spencer</t>
         </is>
       </c>
       <c r="B172" s="8">
@@ -19165,20 +19307,16 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>(Ana se esconde detrás de un árbol. ¡Menos mal que Marilla no la dejó irse con ella!)</t>
+          <t>¡Ana! Qué bien te ves. Y yo que creí que los Cuthbert querían una niña… ¡qué enredo!</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>a_prueba</t>
-        </is>
-      </c>
+      <c r="F172" s="7" t="inlineStr"/>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="7" t="inlineStr"/>
       <c r="I172" s="7" t="inlineStr"/>
@@ -19187,7 +19325,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>carrie</t>
+          <t>spencer</t>
         </is>
       </c>
       <c r="B173" s="8">
@@ -19201,18 +19339,12 @@
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>¿Viste la composición de Ana? ¡La señorita Stacy la leyó en voz alta!</t>
+          <t>Mi Lily estuvo enferma, por eso no pude llevarte yo a Tejas Verdes.</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F173" s="7" t="inlineStr"/>
+      <c r="G173" s="7" t="n"/>
       <c r="H173" s="7" t="inlineStr"/>
       <c r="I173" s="7" t="inlineStr"/>
       <c r="J173" s="9" t="inlineStr"/>
@@ -19220,7 +19352,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>carrie</t>
+          <t>blewett</t>
         </is>
       </c>
       <c r="B174" s="8">
@@ -19234,24 +19366,24 @@
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá dice que en Tejas Verdes hay una niña nueva. ¿Eres tú?</t>
+          <t>Así que te quedaste con los Cuthbert. Hmm. Yo te habría hecho trabajar de verdad.</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
-      <c r="F174" s="7" t="inlineStr"/>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>a_prueba</t>
+        </is>
+      </c>
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="inlineStr"/>
       <c r="I174" s="7" t="inlineStr"/>
-      <c r="J174" s="9" t="inlineStr">
-        <is>
-          <t>sabe:carrie:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J174" s="9" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>jefe</t>
+          <t>blewett</t>
         </is>
       </c>
       <c r="B175" s="8">
@@ -19265,7 +19397,7 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>El tren de las cinco y media ya pasó, ¿sabe? Hoy no viene otro.</t>
+          <t>Hmm. Flacucha. En mi casa no hay tiempo para mirar las nubes, ¿sabes?</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr"/>
@@ -19278,7 +19410,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>jefe</t>
+          <t>blewett</t>
         </is>
       </c>
       <c r="B176" s="8">
@@ -19287,16 +19419,20 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>Esa niñita de pelo rojo... se sentó en las tejuelas a imaginar cosas. Todo un caso.</t>
+          <t>(Ana se esconde detrás de un árbol. ¡Menos mal que Marilla no la dejó irse con ella!)</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr"/>
-      <c r="F176" s="7" t="inlineStr"/>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>a_prueba</t>
+        </is>
+      </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="7" t="inlineStr"/>
@@ -19305,7 +19441,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>thomas</t>
+          <t>carrie</t>
         </is>
       </c>
       <c r="B177" s="8">
@@ -19319,20 +19455,30 @@
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Buenas. Rachel está adentro. Ella habla por los dos, ¿sabes?</t>
+          <t>¿Viste la composición de Ana? ¡La señorita Stacy la leyó en voz alta!</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
-      <c r="F177" s="7" t="inlineStr"/>
-      <c r="G177" s="7" t="n"/>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="7" t="inlineStr"/>
-      <c r="J177" s="9" t="inlineStr"/>
+      <c r="J177" s="9" t="inlineStr">
+        <is>
+          <t>hecho:llego_stacy</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>veraneante</t>
+          <t>carrie</t>
         </is>
       </c>
       <c r="B178" s="8">
@@ -19346,7 +19492,7 @@
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>¡Qué playa tan encantadora! En Boston no hay nada parecido.</t>
+          <t>Mi mamá dice que en Tejas Verdes hay una niña nueva. ¿Eres tú?</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
@@ -19354,12 +19500,16 @@
       <c r="G178" s="7" t="n"/>
       <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="7" t="inlineStr"/>
-      <c r="J178" s="9" t="inlineStr"/>
+      <c r="J178" s="9" t="inlineStr">
+        <is>
+          <t>sabe:carrie:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>veraneante</t>
+          <t>jefe</t>
         </is>
       </c>
       <c r="B179" s="8">
@@ -19373,7 +19523,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>¿Eres de aquí, niña? ¡Qué suerte vivir en un lugar así!</t>
+          <t>El tren de las cinco y media ya pasó, ¿sabe? Hoy no viene otro.</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr"/>
@@ -19386,7 +19536,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>pescador</t>
+          <t>jefe</t>
         </is>
       </c>
       <c r="B180" s="8">
@@ -19400,7 +19550,7 @@
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>Hoy vienen buenas las caballas. Si Marilla quiere pescado, que mande a Matthew.</t>
+          <t>Esa niñita de pelo rojo... se sentó en las tejuelas a imaginar cosas. Todo un caso.</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr"/>
@@ -19413,7 +19563,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>vecino</t>
+          <t>thomas</t>
         </is>
       </c>
       <c r="B181" s="8">
@@ -19427,18 +19577,12 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>¡Buenos días, Ana! ¿Cómo están Matthew y Marilla?</t>
+          <t>Buenas. Rachel está adentro. Ella habla por los dos, ¿sabes?</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr"/>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>llegada_tv</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="n">
-        <v>14</v>
-      </c>
+      <c r="F181" s="7" t="inlineStr"/>
+      <c r="G181" s="7" t="n"/>
       <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="7" t="inlineStr"/>
       <c r="J181" s="9" t="inlineStr"/>
@@ -19446,7 +19590,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>vecino</t>
+          <t>veraneante</t>
         </is>
       </c>
       <c r="B182" s="8">
@@ -19460,7 +19604,7 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>Lindo día, ¿verdad? Dicen que mañana llueve.</t>
+          <t>¡Qué playa tan encantadora! En Boston no hay nada parecido.</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr"/>
@@ -19473,7 +19617,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>vecino</t>
+          <t>veraneante</t>
         </is>
       </c>
       <c r="B183" s="8">
@@ -19487,18 +19631,12 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>¡Qué grande estás, niña! Saludos a Marilla.</t>
+          <t>¿Eres de aquí, niña? ¡Qué suerte vivir en un lugar así!</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr"/>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>llegada_tv</t>
-        </is>
-      </c>
-      <c r="G183" s="7" t="n">
-        <v>56</v>
-      </c>
+      <c r="F183" s="7" t="inlineStr"/>
+      <c r="G183" s="7" t="n"/>
       <c r="H183" s="7" t="inlineStr"/>
       <c r="I183" s="7" t="inlineStr"/>
       <c r="J183" s="9" t="inlineStr"/>
@@ -19506,7 +19644,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>vecino</t>
+          <t>pescador</t>
         </is>
       </c>
       <c r="B184" s="8">
@@ -19520,7 +19658,7 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>Buenas. Tú no eres de por aquí, ¿no?</t>
+          <t>Hoy vienen buenas las caballas. Si Marilla quiere pescado, que mande a Matthew.</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr"/>
@@ -19528,11 +19666,7 @@
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="inlineStr"/>
       <c r="I184" s="7" t="inlineStr"/>
-      <c r="J184" s="9" t="inlineStr">
-        <is>
-          <t>!dias_desde:llegada_tv:14</t>
-        </is>
-      </c>
+      <c r="J184" s="9" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
@@ -19551,12 +19685,18 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>¿Vas para la aldea? Yo vengo de la tienda de Lawson.</t>
+          <t>¡Buenos días, Ana! ¿Cómo están Matthew y Marilla?</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr"/>
-      <c r="F185" s="7" t="inlineStr"/>
-      <c r="G185" s="7" t="n"/>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>llegada_tv</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>14</v>
+      </c>
       <c r="H185" s="7" t="inlineStr"/>
       <c r="I185" s="7" t="inlineStr"/>
       <c r="J185" s="9" t="inlineStr"/>
@@ -19578,7 +19718,7 @@
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>Buenas, buenas. No te entretengas, que se hace tarde.</t>
+          <t>Lindo día, ¿verdad? Dicen que mañana llueve.</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr"/>
@@ -19605,20 +19745,30 @@
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>Mira qué cielo. Así da gusto salir.</t>
+          <t>¡Qué grande estás, niña! Saludos a Marilla.</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr"/>
-      <c r="F187" s="7" t="inlineStr"/>
-      <c r="G187" s="7" t="n"/>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>llegada_tv</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="n">
+        <v>56</v>
+      </c>
       <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
-      <c r="J187" s="9" t="inlineStr"/>
+      <c r="J187" s="9" t="inlineStr">
+        <is>
+          <t>!donde:ana:tejas</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>niño</t>
+          <t>vecino</t>
         </is>
       </c>
       <c r="B188" s="8">
@@ -19632,7 +19782,7 @@
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>¿Tú eres Ana? ¡Tienes el pelo como una zanahoria!... ¡Es bonito!</t>
+          <t>Buenas. Tú no eres de por aquí, ¿no?</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr"/>
@@ -19640,12 +19790,16 @@
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="7" t="inlineStr"/>
       <c r="I188" s="7" t="inlineStr"/>
-      <c r="J188" s="9" t="inlineStr"/>
+      <c r="J188" s="9" t="inlineStr">
+        <is>
+          <t>!dias_desde:llegada_tv:14</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>niño</t>
+          <t>vecino</t>
         </is>
       </c>
       <c r="B189" s="8">
@@ -19659,7 +19813,7 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>¡Mira, encontré una piedra que brilla!</t>
+          <t>¿Vas para la aldea? Yo vengo de la tienda de Lawson.</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr"/>
@@ -19672,7 +19826,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>niño</t>
+          <t>vecino</t>
         </is>
       </c>
       <c r="B190" s="8">
@@ -19686,7 +19840,7 @@
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>¿Jugamos? Yo me escondo y tú cuentas hasta cien.</t>
+          <t>Buenas, buenas. No te entretengas, que se hace tarde.</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr"/>
@@ -19697,28 +19851,112 @@
       <c r="J190" s="9" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="B191" s="10">
-        <f>IF(A191="","",IFERROR(INDEX(Personas!$B:$B,MATCH(A191,Personas!$A:$A,0)),"(¿quién?)"))</f>
-        <v/>
-      </c>
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>vecino</t>
+        </is>
+      </c>
+      <c r="B191" s="8">
+        <f>IFERROR(INDEX(Personas!$B:$B,MATCH(A191,Personas!$A:$A,0)),"(¿quién?)")</f>
+        <v/>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>Mira qué cielo. Así da gusto salir.</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr"/>
+      <c r="F191" s="7" t="inlineStr"/>
+      <c r="G191" s="7" t="n"/>
+      <c r="H191" s="7" t="inlineStr"/>
+      <c r="I191" s="7" t="inlineStr"/>
+      <c r="J191" s="9" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="B192" s="10">
-        <f>IF(A192="","",IFERROR(INDEX(Personas!$B:$B,MATCH(A192,Personas!$A:$A,0)),"(¿quién?)"))</f>
-        <v/>
-      </c>
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>niño</t>
+        </is>
+      </c>
+      <c r="B192" s="8">
+        <f>IFERROR(INDEX(Personas!$B:$B,MATCH(A192,Personas!$A:$A,0)),"(¿quién?)")</f>
+        <v/>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>¿Tú eres Ana? ¡Tienes el pelo como una zanahoria!... ¡Es bonito!</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr"/>
+      <c r="F192" s="7" t="inlineStr"/>
+      <c r="G192" s="7" t="n"/>
+      <c r="H192" s="7" t="inlineStr"/>
+      <c r="I192" s="7" t="inlineStr"/>
+      <c r="J192" s="9" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="B193" s="10">
-        <f>IF(A193="","",IFERROR(INDEX(Personas!$B:$B,MATCH(A193,Personas!$A:$A,0)),"(¿quién?)"))</f>
-        <v/>
-      </c>
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>niño</t>
+        </is>
+      </c>
+      <c r="B193" s="8">
+        <f>IFERROR(INDEX(Personas!$B:$B,MATCH(A193,Personas!$A:$A,0)),"(¿quién?)")</f>
+        <v/>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>¡Mira, encontré una piedra que brilla!</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr"/>
+      <c r="F193" s="7" t="inlineStr"/>
+      <c r="G193" s="7" t="n"/>
+      <c r="H193" s="7" t="inlineStr"/>
+      <c r="I193" s="7" t="inlineStr"/>
+      <c r="J193" s="9" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="B194" s="10">
-        <f>IF(A194="","",IFERROR(INDEX(Personas!$B:$B,MATCH(A194,Personas!$A:$A,0)),"(¿quién?)"))</f>
-        <v/>
-      </c>
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>niño</t>
+        </is>
+      </c>
+      <c r="B194" s="8">
+        <f>IFERROR(INDEX(Personas!$B:$B,MATCH(A194,Personas!$A:$A,0)),"(¿quién?)")</f>
+        <v/>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>¿Jugamos? Yo me escondo y tú cuentas hasta cien.</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr"/>
+      <c r="F194" s="7" t="inlineStr"/>
+      <c r="G194" s="7" t="n"/>
+      <c r="H194" s="7" t="inlineStr"/>
+      <c r="I194" s="7" t="inlineStr"/>
+      <c r="J194" s="9" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="B195" s="10">
@@ -30579,10 +30817,10 @@
       <formula1>=Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="No es un hecho ni una meta que exista (¿está bien escrito?)." type="list" errorStyle="warning">
-      <formula1>=Listas!$E$2:$E$114</formula1>
+      <formula1>=Listas!$E$2:$E$115</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="No es un hecho ni una meta que exista (¿está bien escrito?)." type="list" errorStyle="warning">
-      <formula1>=Listas!$E$2:$E$114</formula1>
+      <formula1>=Listas!$E$2:$E$115</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="primavera, verano, otoño o invierno." type="list" errorStyle="stop">
       <formula1>=Listas!$D$2:$D$5</formula1>
@@ -30602,7 +30840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30658,20 +30896,20 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Gertie Pye</t>
+          <t>la Sra. Barry</t>
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a Gertie Pye: sí</t>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Sra. Barry: sí</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>dias_desde:escuela:3 (2); !conoce:gertie (1)</t>
+          <t>hecho:barry_presenta (6); !conoce:barry (2); hecho:prohibida (2); hecho:conocidas_diana (1); hecho:perdonada (1); !donde:ana:tejas (1)</t>
         </is>
       </c>
     </row>
@@ -30683,25 +30921,25 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>reacciona al camisón fuera de Tejas Verdes</t>
+          <t>algo que decirle</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Alec King</t>
+          <t>Gertie Pye</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Alec King: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a Gertie Pye: sí</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>no tiene ninguna</t>
+          <t>dias_desde:escuela:3 (2); !conoce:gertie (1)</t>
         </is>
       </c>
     </row>
@@ -30713,25 +30951,25 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>reacciona al camisón fuera de Tejas Verdes</t>
+          <t>algo que decirle</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>el reverendo Allan</t>
+          <t>la Sra. Lynde</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el reverendo Allan: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Sra. Lynde: sí</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>no tiene ninguna</t>
+          <t>!hecho:ofendio_lynde (12); !conoce:lynde (2); afecto:lynde:ana&gt;=3 (2); !hecho:disculpa_lynde (1); ana:camison (1); !hecho:lynde_visita (1)</t>
         </is>
       </c>
     </row>
@@ -30743,25 +30981,25 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>reacciona al camisón fuera de Tejas Verdes</t>
+          <t>algo que decirle</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Andrews</t>
+          <t>el Sr. Phillips</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Andrews: sí</t>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a el Sr. Phillips: sí</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>no tiene ninguna</t>
+          <t>dias_desde:escuela:3 (1); !estacion:verano (1); !conoce:phillips (1)</t>
         </is>
       </c>
     </row>
@@ -30778,20 +31016,20 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Barry</t>
+          <t>Alec King</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Barry: no</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Alec King: sí</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>hora:7-21 (1)</t>
+          <t>no tiene ninguna</t>
         </is>
       </c>
     </row>
@@ -30808,7 +31046,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Blewett</t>
+          <t>el reverendo Allan</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
@@ -30816,7 +31054,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Blewett: sí</t>
+          <t>día: 112 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el reverendo Allan: sí</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -30838,7 +31076,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>el buhonero</t>
+          <t>el Sr. Andrews</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -30846,7 +31084,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el buhonero: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Andrews: sí</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -30868,20 +31106,20 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>el editor de La Crónica</t>
+          <t>la Sra. Barry</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el editor de La Crónica: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Sra. Barry: sí</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>no tiene ninguna</t>
+          <t>hora:7-21 (1)</t>
         </is>
       </c>
     </row>
@@ -30898,7 +31136,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>el capitán Jim</t>
+          <t>la Sra. Blewett</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -30906,7 +31144,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el capitán Jim: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Blewett: sí</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -30928,7 +31166,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Harrison</t>
+          <t>el buhonero</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
@@ -30936,7 +31174,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Harrison: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el buhonero: sí</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -30958,7 +31196,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>el herrero</t>
+          <t>el editor de La Crónica</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -30966,7 +31204,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el herrero: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el editor de La Crónica: sí</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -30988,7 +31226,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Hetty King</t>
+          <t>el capitán Jim</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
@@ -30996,7 +31234,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Srta. Hetty King: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el capitán Jim: sí</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -31018,7 +31256,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Janet King</t>
+          <t>el Sr. Harrison</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -31026,7 +31264,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Janet King: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Harrison: sí</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -31048,7 +31286,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Jasper Dale</t>
+          <t>el herrero</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
@@ -31056,7 +31294,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Jasper Dale: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el herrero: sí</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -31078,7 +31316,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>el jefe de estación</t>
+          <t>la Srta. Hetty King</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -31086,7 +31324,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el jefe de estación: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Srta. Hetty King: sí</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -31108,7 +31346,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Jerry Buote</t>
+          <t>Janet King</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
@@ -31116,7 +31354,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Jerry Buote: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Janet King: sí</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -31138,7 +31376,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Josephine Barry</t>
+          <t>Jasper Dale</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -31146,7 +31384,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Srta. Josephine Barry: no</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Jasper Dale: sí</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -31168,7 +31406,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>el jefe de estación</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
@@ -31176,7 +31414,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Lawson: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el jefe de estación: sí</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -31198,20 +31436,20 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Lynde</t>
+          <t>Jerry Buote</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Lynde: no</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Jerry Buote: sí</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>hora:7-21 (1)</t>
+          <t>no tiene ninguna</t>
         </is>
       </c>
     </row>
@@ -31228,20 +31466,20 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Marilla</t>
+          <t>la Srta. Josephine Barry</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Marilla: sí</t>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Srta. Josephine Barry: no</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>hora:9-19 (1)</t>
+          <t>no tiene ninguna</t>
         </is>
       </c>
     </row>
@@ -31258,7 +31496,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Mary Joe</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -31266,7 +31504,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la casa del Sr. Harrison · Ana: en camisón · conoce a Mary Joe: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Lawson: sí</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -31288,20 +31526,20 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>la Sra. Lynde</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Matthew: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Lynde: no</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>no tiene ninguna</t>
+          <t>hora:7-21 (1)</t>
         </is>
       </c>
     </row>
@@ -31318,20 +31556,20 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>el médico</t>
+          <t>Marilla</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el médico: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: la casa de la Sra. Lynde · Ana: en camisón · conoce a Marilla: sí</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>no tiene ninguna</t>
+          <t>hora:9-19 (1)</t>
         </is>
       </c>
     </row>
@@ -31348,7 +31586,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Olivia King</t>
+          <t>Mary Joe</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
@@ -31356,7 +31594,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Olivia King: sí</t>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a Mary Joe: sí</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -31378,7 +31616,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Peg Bowen</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -31386,7 +31624,7 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Peg Bowen: sí</t>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Matthew: sí</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -31408,7 +31646,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>un pescador</t>
+          <t>el médico</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
@@ -31416,7 +31654,7 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a un pescador: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el médico: sí</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -31438,7 +31676,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Phillips</t>
+          <t>Olivia King</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
@@ -31446,7 +31684,7 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Phillips: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Olivia King: sí</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -31468,7 +31706,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Shearer</t>
+          <t>Peg Bowen</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
@@ -31476,7 +31714,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Shearer: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Peg Bowen: sí</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -31498,7 +31736,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Sloane</t>
+          <t>un pescador</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
@@ -31506,7 +31744,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Sloane: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a un pescador: sí</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -31528,7 +31766,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Spencer</t>
+          <t>el Sr. Phillips</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
@@ -31536,7 +31774,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Spencer: sí</t>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Phillips: sí</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -31558,7 +31796,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Allan</t>
+          <t>el Sr. Shearer</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
@@ -31566,7 +31804,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Sra. Allan: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Shearer: sí</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -31588,7 +31826,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Pye</t>
+          <t>el Sr. Sloane</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
@@ -31596,7 +31834,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Pye: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Sloane: sí</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -31618,7 +31856,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Barry</t>
+          <t>la Sra. Spencer</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
@@ -31626,7 +31864,7 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el Sr. Barry: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Spencer: sí</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -31648,7 +31886,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Bell</t>
+          <t>la Sra. Allan</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
@@ -31656,7 +31894,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la tienda de Lawson · Ana: en camisón · conoce a el Sr. Bell: sí</t>
+          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Allan: sí</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -31678,7 +31916,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Stacy</t>
+          <t>la Sra. Pye</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
@@ -31686,7 +31924,7 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Srta. Stacy: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a la Sra. Pye: sí</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -31708,7 +31946,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Thomas Lynde</t>
+          <t>el Sr. Barry</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
@@ -31716,7 +31954,7 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: la casa de la Sra. Lynde · Ana: en camisón · conoce a Thomas Lynde: sí</t>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a el Sr. Barry: sí</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -31738,7 +31976,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>un vecino (sin nombre)</t>
+          <t>el Sr. Bell</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
@@ -31746,7 +31984,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: en camisón · conoce a un vecino (sin nombre): no</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a el Sr. Bell: sí</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -31768,7 +32006,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>una veraneante del hotel</t>
+          <t>la Srta. Stacy</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
@@ -31776,7 +32014,7 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a una veraneante del hotel: sí</t>
+          <t>día: 126 · estación: primavera · hora: 6:00 · Ana en: La Cuesta del Huerto · Ana: en camisón · conoce a la Srta. Stacy: sí</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -31793,12 +32031,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Alec King</t>
+          <t>Thomas Lynde</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
@@ -31806,7 +32044,7 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>día: 67 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Alec King: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a Thomas Lynde: sí</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -31823,12 +32061,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>el reverendo Allan</t>
+          <t>un vecino (sin nombre)</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
@@ -31836,7 +32074,7 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>día: 113 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el reverendo Allan: sí</t>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a un vecino (sin nombre): no</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -31853,12 +32091,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>reacciona si Ana está sin sombrero en la iglesia</t>
+          <t>reacciona al camisón fuera de Tejas Verdes</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Andrews</t>
+          <t>una veraneante del hotel</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
@@ -31866,7 +32104,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Andrews: sí</t>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: el camino o la aldea · Ana: en camisón · conoce a una veraneante del hotel: sí</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -31888,7 +32126,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Barry</t>
+          <t>Alec King</t>
         </is>
       </c>
       <c r="D43" s="8" t="n">
@@ -31896,7 +32134,7 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Barry: no</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Alec King: sí</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -31918,7 +32156,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Blewett</t>
+          <t>el reverendo Allan</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
@@ -31926,7 +32164,7 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Blewett: sí</t>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el reverendo Allan: sí</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -31948,7 +32186,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>el buhonero</t>
+          <t>el Sr. Andrews</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
@@ -31956,7 +32194,7 @@
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>día: 11 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el buhonero: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Andrews: sí</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -31978,7 +32216,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>el editor de La Crónica</t>
+          <t>la Sra. Barry</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
@@ -31986,7 +32224,7 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el editor de La Crónica: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Barry: sí</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -32008,7 +32246,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>el capitán Jim</t>
+          <t>la Sra. Blewett</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
@@ -32016,7 +32254,7 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>día: 126 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el capitán Jim: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Blewett: sí</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -32038,7 +32276,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Harrison</t>
+          <t>el buhonero</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
@@ -32046,7 +32284,7 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>día: 3 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Harrison: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el buhonero: sí</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -32068,7 +32306,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>el herrero</t>
+          <t>el editor de La Crónica</t>
         </is>
       </c>
       <c r="D49" s="8" t="n">
@@ -32076,7 +32314,7 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el herrero: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el editor de La Crónica: sí</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -32098,7 +32336,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Hetty King</t>
+          <t>el capitán Jim</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
@@ -32106,7 +32344,7 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Hetty King: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el capitán Jim: sí</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -32128,7 +32366,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Janet King</t>
+          <t>el Sr. Harrison</t>
         </is>
       </c>
       <c r="D51" s="8" t="n">
@@ -32136,7 +32374,7 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Janet King: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Harrison: sí</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -32158,7 +32396,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Jasper Dale</t>
+          <t>el herrero</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
@@ -32166,7 +32404,7 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Jasper Dale: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el herrero: sí</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -32188,7 +32426,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>el jefe de estación</t>
+          <t>la Srta. Hetty King</t>
         </is>
       </c>
       <c r="D53" s="8" t="n">
@@ -32196,7 +32434,7 @@
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el jefe de estación: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Hetty King: sí</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -32218,7 +32456,7 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Jerry Buote</t>
+          <t>Janet King</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
@@ -32226,7 +32464,7 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Jerry Buote: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Janet King: sí</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -32248,7 +32486,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Josephine Barry</t>
+          <t>Jasper Dale</t>
         </is>
       </c>
       <c r="D55" s="8" t="n">
@@ -32256,7 +32494,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Josephine Barry: no</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Jasper Dale: sí</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -32278,7 +32516,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>el jefe de estación</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
@@ -32286,7 +32524,7 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Lawson: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el jefe de estación: sí</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -32308,7 +32546,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Lynde</t>
+          <t>Jerry Buote</t>
         </is>
       </c>
       <c r="D57" s="8" t="n">
@@ -32316,7 +32554,7 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Lynde: no</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Jerry Buote: sí</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -32338,7 +32576,7 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Marilla</t>
+          <t>la Srta. Josephine Barry</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
@@ -32346,7 +32584,7 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Marilla: sí</t>
+          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Josephine Barry: no</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -32368,7 +32606,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Mary Joe</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
@@ -32376,7 +32614,7 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Mary Joe: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Lawson: sí</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -32398,7 +32636,7 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>la Sra. Lynde</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
@@ -32406,7 +32644,7 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Matthew: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Lynde: no</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -32428,7 +32666,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>el médico</t>
+          <t>Marilla</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
@@ -32436,7 +32674,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>día: 85 · estación: otoño · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el médico: sí</t>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Marilla: sí</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -32458,7 +32696,7 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Olivia King</t>
+          <t>Mary Joe</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
@@ -32466,7 +32704,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Olivia King: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Mary Joe: sí</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -32488,7 +32726,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Peg Bowen</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="D63" s="8" t="n">
@@ -32496,7 +32734,7 @@
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Peg Bowen: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Matthew: sí</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -32518,7 +32756,7 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>un pescador</t>
+          <t>el médico</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
@@ -32526,7 +32764,7 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a un pescador: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el médico: sí</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -32548,7 +32786,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Phillips</t>
+          <t>Olivia King</t>
         </is>
       </c>
       <c r="D65" s="8" t="n">
@@ -32556,7 +32794,7 @@
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Phillips: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Olivia King: sí</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -32578,7 +32816,7 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Shearer</t>
+          <t>Peg Bowen</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -32586,7 +32824,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Shearer: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Peg Bowen: sí</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -32608,7 +32846,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Sloane</t>
+          <t>un pescador</t>
         </is>
       </c>
       <c r="D67" s="8" t="n">
@@ -32616,7 +32854,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Sloane: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a un pescador: sí</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -32638,7 +32876,7 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Spencer</t>
+          <t>el Sr. Phillips</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
@@ -32646,7 +32884,7 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Spencer: sí</t>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Phillips: sí</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -32668,7 +32906,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Allan</t>
+          <t>el Sr. Shearer</t>
         </is>
       </c>
       <c r="D69" s="8" t="n">
@@ -32676,7 +32914,7 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Allan: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Shearer: sí</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -32698,7 +32936,7 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Pye</t>
+          <t>el Sr. Sloane</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
@@ -32706,7 +32944,7 @@
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Pye: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Sloane: sí</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -32728,7 +32966,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Barry</t>
+          <t>la Sra. Spencer</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
@@ -32736,7 +32974,7 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Barry: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Spencer: sí</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -32758,7 +32996,7 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Bell</t>
+          <t>la Sra. Allan</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
@@ -32766,7 +33004,7 @@
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Bell: sí</t>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Allan: sí</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -32788,7 +33026,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Stacy</t>
+          <t>la Sra. Pye</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
@@ -32796,7 +33034,7 @@
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>día: 113 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Stacy: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Sra. Pye: sí</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -32818,7 +33056,7 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Thomas Lynde</t>
+          <t>el Sr. Barry</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -32826,7 +33064,7 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Thomas Lynde: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Barry: sí</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -32848,7 +33086,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>un vecino (sin nombre)</t>
+          <t>el Sr. Bell</t>
         </is>
       </c>
       <c r="D75" s="8" t="n">
@@ -32856,7 +33094,7 @@
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>día: 113 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a un vecino (sin nombre): no</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a el Sr. Bell: sí</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -32878,7 +33116,7 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>una veraneante del hotel</t>
+          <t>la Srta. Stacy</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -32886,7 +33124,7 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>día: 127 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a una veraneante del hotel: sí</t>
+          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a la Srta. Stacy: sí</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -32903,12 +33141,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>reacciona si Ana anda sola de noche</t>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Alec King</t>
+          <t>Thomas Lynde</t>
         </is>
       </c>
       <c r="D77" s="8" t="n">
@@ -32916,7 +33154,7 @@
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Alec King: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a Thomas Lynde: sí</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -32933,12 +33171,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>reacciona si Ana anda sola de noche</t>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>el reverendo Allan</t>
+          <t>un vecino (sin nombre)</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
@@ -32946,7 +33184,7 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el reverendo Allan: sí</t>
+          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a un vecino (sin nombre): no</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -32963,12 +33201,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>reacciona si Ana anda sola de noche</t>
+          <t>reacciona si Ana está sin sombrero en la iglesia</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Andrews</t>
+          <t>una veraneante del hotel</t>
         </is>
       </c>
       <c r="D79" s="8" t="n">
@@ -32976,7 +33214,7 @@
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Andrews: sí</t>
+          <t>día: 71 · estación: verano · hora: 6:00 · Ana en: la iglesia · Ana: sin sombrero · conoce a una veraneante del hotel: sí</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -32998,7 +33236,7 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Barry</t>
+          <t>Alec King</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
@@ -33006,7 +33244,7 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Barry: no</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Alec King: sí</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -33028,7 +33266,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Blewett</t>
+          <t>el reverendo Allan</t>
         </is>
       </c>
       <c r="D81" s="8" t="n">
@@ -33036,7 +33274,7 @@
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Blewett: sí</t>
+          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el reverendo Allan: sí</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -33058,7 +33296,7 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>el buhonero</t>
+          <t>el Sr. Andrews</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
@@ -33066,7 +33304,7 @@
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>día: 102 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el buhonero: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Andrews: sí</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -33088,7 +33326,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>el editor de La Crónica</t>
+          <t>la Sra. Barry</t>
         </is>
       </c>
       <c r="D83" s="8" t="n">
@@ -33096,7 +33334,7 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a el editor de La Crónica: sí</t>
+          <t>día: 1 · estación: primavera · hora: 21:00 · Ana en: La Cuesta del Huerto · conoce a la Sra. Barry: sí</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -33118,7 +33356,7 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>el capitán Jim</t>
+          <t>la Sra. Blewett</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
@@ -33126,7 +33364,7 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el capitán Jim: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Blewett: sí</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -33148,7 +33386,7 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Harrison</t>
+          <t>el buhonero</t>
         </is>
       </c>
       <c r="D85" s="8" t="n">
@@ -33156,7 +33394,7 @@
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Harrison: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el buhonero: sí</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -33178,7 +33416,7 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>el herrero</t>
+          <t>el editor de La Crónica</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
@@ -33186,7 +33424,7 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el herrero: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el editor de La Crónica: sí</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -33208,7 +33446,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Hetty King</t>
+          <t>el capitán Jim</t>
         </is>
       </c>
       <c r="D87" s="8" t="n">
@@ -33216,7 +33454,7 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Hetty King: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el capitán Jim: sí</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -33238,7 +33476,7 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Janet King</t>
+          <t>el Sr. Harrison</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
@@ -33246,7 +33484,7 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Janet King: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Harrison: sí</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -33268,7 +33506,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Jasper Dale</t>
+          <t>el herrero</t>
         </is>
       </c>
       <c r="D89" s="8" t="n">
@@ -33276,7 +33514,7 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Jasper Dale: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el herrero: sí</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -33298,7 +33536,7 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>el jefe de estación</t>
+          <t>la Srta. Hetty King</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
@@ -33306,7 +33544,7 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el jefe de estación: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Hetty King: sí</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -33328,7 +33566,7 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Jerry Buote</t>
+          <t>Janet King</t>
         </is>
       </c>
       <c r="D91" s="8" t="n">
@@ -33336,7 +33574,7 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>día: 1 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a Jerry Buote: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Janet King: sí</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -33358,7 +33596,7 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Josephine Barry</t>
+          <t>Jasper Dale</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
@@ -33366,7 +33604,7 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Josephine Barry: no</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Jasper Dale: sí</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -33388,7 +33626,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>el jefe de estación</t>
         </is>
       </c>
       <c r="D93" s="8" t="n">
@@ -33396,7 +33634,7 @@
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Lawson: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el jefe de estación: sí</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -33418,7 +33656,7 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Lynde</t>
+          <t>Jerry Buote</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
@@ -33426,7 +33664,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Lynde: no</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Jerry Buote: sí</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -33448,7 +33686,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Marilla</t>
+          <t>la Srta. Josephine Barry</t>
         </is>
       </c>
       <c r="D95" s="8" t="n">
@@ -33456,7 +33694,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Marilla: sí</t>
+          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: La Cuesta del Huerto · conoce a la Srta. Josephine Barry: no</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -33478,7 +33716,7 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Mary Joe</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
@@ -33486,7 +33724,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 21:00 · Ana en: La Cuesta del Huerto · conoce a Mary Joe: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Lawson: sí</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -33508,7 +33746,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>la Sra. Lynde</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
@@ -33516,7 +33754,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Matthew: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Lynde: no</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -33538,7 +33776,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>el médico</t>
+          <t>Marilla</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
@@ -33546,7 +33784,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el médico: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Marilla: sí</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -33568,7 +33806,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Olivia King</t>
+          <t>Mary Joe</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
@@ -33576,7 +33814,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Olivia King: sí</t>
+          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: La Cuesta del Huerto · conoce a Mary Joe: sí</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -33598,7 +33836,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Peg Bowen</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
@@ -33606,7 +33844,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Peg Bowen: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Matthew: sí</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -33628,7 +33866,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>un pescador</t>
+          <t>el médico</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
@@ -33636,7 +33874,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a un pescador: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el médico: sí</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -33658,7 +33896,7 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Phillips</t>
+          <t>Olivia King</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
@@ -33666,7 +33904,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Phillips: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Olivia King: sí</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -33688,7 +33926,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Shearer</t>
+          <t>Peg Bowen</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
@@ -33696,7 +33934,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Shearer: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Peg Bowen: sí</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -33718,7 +33956,7 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Sloane</t>
+          <t>un pescador</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
@@ -33726,7 +33964,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Sloane: sí</t>
+          <t>día: 1 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a un pescador: sí</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -33748,7 +33986,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Spencer</t>
+          <t>el Sr. Phillips</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
@@ -33756,7 +33994,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Spencer: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Phillips: sí</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -33778,7 +34016,7 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Allan</t>
+          <t>el Sr. Shearer</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
@@ -33786,7 +34024,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Allan: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Shearer: sí</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -33808,7 +34046,7 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Pye</t>
+          <t>el Sr. Sloane</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
@@ -33816,7 +34054,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Pye: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Sloane: sí</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -33838,7 +34076,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Barry</t>
+          <t>la Sra. Spencer</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
@@ -33846,7 +34084,7 @@
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Barry: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Spencer: sí</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -33868,7 +34106,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>el Sr. Bell</t>
+          <t>la Sra. Allan</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
@@ -33876,7 +34114,7 @@
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Bell: sí</t>
+          <t>día: 43 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Allan: sí</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -33898,7 +34136,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Stacy</t>
+          <t>la Sra. Pye</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
@@ -33906,7 +34144,7 @@
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>día: 57 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Stacy: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Sra. Pye: sí</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -33928,7 +34166,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Thomas Lynde</t>
+          <t>el Sr. Barry</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
@@ -33936,7 +34174,7 @@
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Thomas Lynde: sí</t>
+          <t>día: 60 · estación: primavera · hora: 21:00 · Ana en: La Cuesta del Huerto · conoce a el Sr. Barry: sí</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -33958,7 +34196,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>un vecino (sin nombre)</t>
+          <t>el Sr. Bell</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
@@ -33966,7 +34204,7 @@
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a un vecino (sin nombre): no</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a el Sr. Bell: sí</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -33988,7 +34226,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>una veraneante del hotel</t>
+          <t>la Srta. Stacy</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
@@ -33996,7 +34234,7 @@
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>día: 71 · estación: verano · hora: 21:00 · Ana en: el camino o la aldea · conoce a una veraneante del hotel: sí</t>
+          <t>día: 126 · estación: primavera · hora: 21:00 · Ana en: el camino o la aldea · conoce a la Srta. Stacy: sí</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -34008,198 +34246,96 @@
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>incoherencia</t>
+          <t>hueco</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>«pasa» invita a entrar</t>
+          <t>reacciona si Ana anda sola de noche</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Barry</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>frase de invierno</t>
-        </is>
+          <t>Thomas Lynde</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>día: 99 · estación: invierno · hora: 6:00 · Ana en: la casa de la Sra. Lynde · conoce a la Sra. Barry: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a Thomas Lynde: sí</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>«Pasa, pasa, que hace un frío terrible. Diana está junto al fuego.» exige donde:barry:propia</t>
+          <t>no tiene ninguna</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>incoherencia</t>
+          <t>hueco</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>«pasa» invita a entrar</t>
+          <t>reacciona si Ana anda sola de noche</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>la Sra. Lynde</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>frase de invierno</t>
-        </is>
+          <t>un vecino (sin nombre)</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Sra. Lynde: sí</t>
+          <t>día: 46 · estación: invierno · hora: 21:00 · Ana en: el camino o la aldea · conoce a un vecino (sin nombre): no</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>«Pasa, niña, que hace un frío de mil demonios... perdón, de los que dan escalofrí» exige donde:lynde:propia</t>
+          <t>no tiene ninguna</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>incoherencia</t>
+          <t>hueco</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>la Srta. Stacy, cuando ya llegó</t>
+          <t>reacciona si Ana anda sola de noche</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
+          <t>una veraneante del hotel</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>día: 88 · estación: otoño · hora: 6:00 · Ana en: el camino o la aldea · conoce a Carrie Sloane: sí</t>
+          <t>día: 127 · estación: verano · hora: 21:00 · Ana en: el camino o la aldea · conoce a una veraneante del hotel: sí</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>«¿Viste la composición de Ana? ¡La señorita Stacy la leyó en voz alta!» exige hecho:llego_stacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>Gilbert, cuando ya volvió</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>Diana</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>escena al encontrarse</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: su pieza · conoce a Diana: sí</t>
-        </is>
-      </c>
-      <c r="F117" s="11" t="inlineStr">
-        <is>
-          <t>«diana: Gilbert Blythe te miró otra vez en clase.» exige hecho:llego_gilbert</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>«saludos a Marilla», fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>la Sra. Barry</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
-      </c>
-      <c r="E118" s="11" t="inlineStr">
-        <is>
-          <t>día: 60 · estación: primavera · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Sra. Barry: no</t>
-        </is>
-      </c>
-      <c r="F118" s="11" t="inlineStr">
-        <is>
-          <t>«Saluda a Marilla de mi parte.» exige !donde:ana:tejas</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>«saludos a Marilla», fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>un vecino (sin nombre)</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>día: 57 · estación: primavera · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a un vecino (sin nombre): no</t>
-        </is>
-      </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
-          <t>«¡Qué grande estás, niña! Saludos a Marilla.» exige !donde:ana:tejas</t>
+          <t>no tiene ninguna</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F119"/>
-  <conditionalFormatting sqref="A2:A119">
+  <autoFilter ref="A1:F116"/>
+  <conditionalFormatting sqref="A2:A116">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>A2="incoherencia"</formula>
     </cfRule>
@@ -34214,7 +34350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -34723,12 +34859,12 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Gertie Pye</t>
+          <t>la Sra. Barry</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -34750,7 +34886,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Jane Andrews</t>
+          <t>Gertie Pye</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -34777,12 +34913,12 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Charlie Sloane</t>
+          <t>Jane Andrews</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -34804,12 +34940,12 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Cecily King</t>
+          <t>Charlie Sloane</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -34831,12 +34967,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Minnie May Barry</t>
+          <t>Cecily King</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -34858,12 +34994,12 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
+          <t>Minnie May Barry</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -34885,12 +35021,12 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>la Srta. Josephine Barry</t>
+          <t>Carrie Sloane</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 45 (sin conocerla), Día 45 (conociéndola)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -34907,22 +35043,22 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Metas</t>
+          <t>Frases</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>«perdon_barry»</t>
+          <t>la Srta. Josephine Barry</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
+          <t>no tiene qué decir: Día 45 (sin conocerla), Día 45 (conociéndola)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
+          <t>frases para esos momentos (hoja «Huecos»)</t>
         </is>
       </c>
     </row>
@@ -34939,7 +35075,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>«carta»</t>
+          <t>«perdon_barry»</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -34966,7 +35102,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>«sala»</t>
+          <t>«carta»</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -34993,7 +35129,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>«sombrero»</t>
+          <t>«sala»</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -35020,7 +35156,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>«tinte»</t>
+          <t>«sombrero»</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -35047,7 +35183,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>«pelo_corto»</t>
+          <t>«tinte»</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -35074,7 +35210,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>«techo»</t>
+          <t>«pelo_corto»</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -35091,27 +35227,27 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>media</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Situaciones</t>
+          <t>Metas</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en Tejas Verdes</t>
+          <t>«techo»</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: Marilla, Matthew, la Sra. Lynde)</t>
+          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>una escena de noche (hora:21-26) con quien esté</t>
+          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
         </is>
       </c>
     </row>
@@ -35128,12 +35264,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en La Cuesta del Huerto</t>
+          <t>Ana de noche en Tejas Verdes</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
+          <t>nadie reacciona, en ningún momento (estaban: Marilla, Matthew, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -35155,12 +35291,12 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la Hondonada (Sra. Lynde)</t>
+          <t>Ana de noche en La Cuesta del Huerto</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: Thomas Lynde, la Sra. Lynde)</t>
+          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -35182,12 +35318,12 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la casa del Sr. Harrison</t>
+          <t>Ana de noche en la Hondonada (Sra. Lynde)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
+          <t>nadie reacciona, en ningún momento (estaban: Thomas Lynde, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -35209,12 +35345,12 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la tienda de Lawson</t>
+          <t>Ana de noche en la casa del Sr. Harrison</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -35236,12 +35372,12 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la escuela</t>
+          <t>Ana de noche en la tienda de Lawson</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -35263,12 +35399,12 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la iglesia</t>
+          <t>Ana de noche en la escuela</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Bell, el reverendo Allan, la Sra. Allan, la Sra. Lynde, la Sra. Pye)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -35290,12 +35426,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la casa parroquial</t>
+          <t>Ana de noche en la iglesia</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Bell, el reverendo Allan, la Sra. Allan, la Sra. Lynde, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -35317,12 +35453,12 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la aldea (afuera)</t>
+          <t>Ana de noche en la casa parroquial</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison, el Sr. Lawson, la Sra. Barry, la Sra. Lynde, la Sra. Pye, v0)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -35344,17 +35480,17 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón: ella misma no lo nota</t>
+          <t>Ana de noche en la aldea (afuera)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>en Tejas Verdes, La Cuesta del Huerto, la Hondonada (Sra. Lynde), la casa del Sr. Harrison, la tienda de Lawson, la escuela, la iglesia, la casa parroquial, la aldea (afuera)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison, el Sr. Lawson, la Sra. Barry, la Sra. Lynde, la Sra. Pye, v0)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>un comentario de Ana con «si: ana:camison»</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -35371,7 +35507,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Ana sin sombrero: ella misma no lo nota</t>
+          <t>Ana en camisón: ella misma no lo nota</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -35381,7 +35517,7 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>un comentario de Ana con «si: ana:sin_sombrero»</t>
+          <t>un comentario de Ana con «si: ana:camison»</t>
         </is>
       </c>
     </row>
@@ -35393,22 +35529,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Exploración</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>70 escena(s) que no pasaron en 4 días</t>
+          <t>Ana sin sombrero: ella misma no lo nota</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>les falta: Ana no va en la calesa por el camino</t>
+          <t>en Tejas Verdes, La Cuesta del Huerto, la Hondonada (Sra. Lynde), la casa del Sr. Harrison, la tienda de Lawson, la escuela, la iglesia, la casa parroquial, la aldea (afuera)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>ej.: avenida, newbridge, avenida_petalos, avenida_paso</t>
+          <t>un comentario de Ana con «si: ana:sin_sombrero»</t>
         </is>
       </c>
     </row>
@@ -35425,17 +35561,17 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>56 escena(s) que no pasaron en 4 días</t>
+          <t>70 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>les falta: podía pasar (no tocó)</t>
+          <t>les falta: Ana no va en la calesa por el camino</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>ej.: primera_gwin, primera_mirror, primera_armario, primera_stairs</t>
+          <t>ej.: avenida, newbridge, avenida_petalos, avenida_paso</t>
         </is>
       </c>
     </row>
@@ -35452,17 +35588,17 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>38 escena(s) que no pasaron en 4 días</t>
+          <t>56 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando se encuentran</t>
+          <t>les falta: podía pasar (no tocó)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>ej.: diana_por_casualidad, par:ana+diana:0, par:ana+diana:1, par:ana+diana:2</t>
+          <t>ej.: primera_gwin, primera_mirror, primera_armario, primera_stairs</t>
         </is>
       </c>
     </row>
@@ -35479,17 +35615,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>19 escena(s) que no pasaron en 4 días</t>
+          <t>38 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana usa gwin</t>
+          <t>les falta: cuando se encuentran</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>ej.: ventana_primavera_manana, ventana_primavera_tarde, ventana_verano_manana, ventana_verano_noche</t>
+          <t>ej.: diana_por_casualidad, par:ana+diana:0, par:ana+diana:1, par:ana+diana:2</t>
         </is>
       </c>
     </row>
@@ -35506,17 +35642,17 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>13 escena(s) que no pasaron en 4 días</t>
+          <t>19 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana conversa con diana</t>
+          <t>les falta: cuando Ana usa gwin</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>ej.: conv_diana_pelo, conv_diana_minnie, conv_diana_nombres, conv_diana_escuela</t>
+          <t>ej.: ventana_primavera_manana, ventana_primavera_tarde, ventana_verano_manana, ventana_verano_noche</t>
         </is>
       </c>
     </row>
@@ -35533,17 +35669,17 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>8 escena(s) que no pasaron en 4 días</t>
+          <t>13 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>les falta: ana no está en gg</t>
+          <t>les falta: cuando Ana conversa con diana</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>ej.: quiere_amiga, broche, prohibida, invita_allan</t>
+          <t>ej.: conv_diana_pelo, conv_diana_minnie, conv_diana_nombres, conv_diana_escuela</t>
         </is>
       </c>
     </row>
@@ -35560,17 +35696,17 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>7 escena(s) que no pasaron en 4 días</t>
+          <t>8 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana conversa con marilla</t>
+          <t>les falta: ana no está en gg</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>ej.: conv_marilla_perdon, conv_marilla_cocina, conv_marilla_diana, conv_marilla_genio</t>
+          <t>ej.: quiere_amiga, broche, prohibida, invita_allan</t>
         </is>
       </c>
     </row>
@@ -35587,17 +35723,17 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>6 escena(s) que no pasaron en 4 días</t>
+          <t>7 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana usa mirror</t>
+          <t>les falta: cuando Ana conversa con marilla</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>ej.: espejo_pelo, espejo_cordelia, espejo_tejas_verdes, espejo_zanahorias</t>
+          <t>ej.: conv_marilla_perdon, conv_marilla_cocina, conv_marilla_diana, conv_marilla_genio</t>
         </is>
       </c>
     </row>
@@ -35614,17 +35750,17 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>5 escena(s) que no pasaron en 4 días</t>
+          <t>6 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana conversa con matthew</t>
+          <t>les falta: cuando Ana usa mirror</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>ej.: conv_matthew_nombres, conv_matthew_mangas, conv_matthew_mujeres, conv_matthew_queens</t>
+          <t>ej.: espejo_pelo, espejo_cordelia, espejo_tejas_verdes, espejo_zanahorias</t>
         </is>
       </c>
     </row>
@@ -35641,17 +35777,17 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>4 escena(s) que no pasaron en 4 días</t>
+          <t>5 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>les falta: diana no está en Avonlea</t>
+          <t>les falta: cuando Ana conversa con matthew</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>ej.: conoce_diana, te_grosella, crup_aviso, cama_josephine</t>
+          <t>ej.: conv_matthew_nombres, conv_matthew_mangas, conv_matthew_mujeres, conv_matthew_queens</t>
         </is>
       </c>
     </row>
@@ -35673,12 +35809,12 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>les falta: falta hecho:blewett_duda</t>
+          <t>les falta: diana no está en Avonlea</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>ej.: duda_matthew, duda_suplica, duda_calla, devuelta_blewett</t>
+          <t>ej.: conoce_diana, te_grosella, crup_aviso, cama_josephine</t>
         </is>
       </c>
     </row>
@@ -35700,12 +35836,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana usa faro</t>
+          <t>les falta: falta hecho:blewett_duda</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>ej.: faro_verano, faro_invierno, faro_manana, faro_queens</t>
+          <t>ej.: duda_matthew, duda_suplica, duda_calla, devuelta_blewett</t>
         </is>
       </c>
     </row>
@@ -35717,22 +35853,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>«huerfano»: los Cuthbert van a traer un niño del orfanato</t>
+          <t>4 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>les falta: cuando Ana usa faro</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:huerfano» (alguien que se entera y hace o dice algo)</t>
+          <t>ej.: faro_verano, faro_invierno, faro_manana, faro_queens</t>
         </is>
       </c>
     </row>
@@ -35749,7 +35885,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>«cerdo_pye»: a los Pye se les escapó otra vez el cerdo</t>
+          <t>«huerfano»: los Cuthbert van a traer un niño del orfanato</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -35759,7 +35895,7 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:cerdo_pye» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:huerfano» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35776,7 +35912,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>«maestra_plumas»: la maestra nueva usa sombrero con plumas</t>
+          <t>«cerdo_pye»: a los Pye se les escapó otra vez el cerdo</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -35786,7 +35922,7 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:maestra_plumas» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:cerdo_pye» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35803,7 +35939,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>«loro_harrison»: el loro del Sr. Harrison dice cosas terribles</t>
+          <t>«maestra_plumas»: la maestra nueva usa sombrero con plumas</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -35813,7 +35949,7 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:loro_harrison» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:maestra_plumas» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35830,7 +35966,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>«rastrillo_matthew»: Matthew Cuthbert compró un rastrillo en invierno</t>
+          <t>«loro_harrison»: el loro del Sr. Harrison dice cosas terribles</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -35840,7 +35976,7 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:rastrillo_matthew» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:loro_harrison» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35857,17 +35993,17 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>«ana_lengua»</t>
+          <t>«rastrillo_matthew»: Matthew Cuthbert compró un rastrillo en invierno</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>es de Ana y no tiene versión exagerada</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>una línea «exagerada:» (los chismosos la agrandan)</t>
+          <t>una escena o una frase con «sabe:quien:rastrillo_matthew» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35884,17 +36020,17 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>«pastor_nuevo»: llegó un pastor nuevo, el Sr. Allan, con su esposa</t>
+          <t>«ana_lengua»</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>es de Ana y no tiene versión exagerada</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:pastor_nuevo» (alguien que se entera y hace o dice algo)</t>
+          <t>una línea «exagerada:» (los chismosos la agrandan)</t>
         </is>
       </c>
     </row>
@@ -35911,7 +36047,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>«tia_josephine»: la tía Josephine de los Barry vino de Charlottetown</t>
+          <t>«pastor_nuevo»: llegó un pastor nuevo, el Sr. Allan, con su esposa</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -35921,7 +36057,7 @@
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:tia_josephine» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:pastor_nuevo» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35938,7 +36074,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>«se_va_phillips»: el Sr. Phillips se va de la escuela de Avonlea</t>
+          <t>«tia_josephine»: la tía Josephine de los Barry vino de Charlottetown</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -35948,7 +36084,7 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:se_va_phillips» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:tia_josephine» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35960,22 +36096,22 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Llegadas</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Prissy Andrews se va</t>
+          <t>«se_va_phillips»: el Sr. Phillips se va de la escuela de Avonlea</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>una noticia o una escena con «hecho:se_fue_prissy»</t>
+          <t>una escena o una frase con «sabe:quien:se_va_phillips» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -35992,17 +36128,17 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>el buhonero llega (de visita)</t>
+          <t>Prissy Andrews se va</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota (solo queda en el diario)</t>
+          <t>nadie lo nota</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_buhonero: …» o una escena «si: hecho:llego_buhonero»</t>
+          <t>una noticia o una escena con «hecho:se_fue_prissy»</t>
         </is>
       </c>
     </row>
@@ -36019,7 +36155,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>una veraneante del hotel llega (de visita)</t>
+          <t>el buhonero llega (de visita)</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -36029,7 +36165,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_veraneante: …» o una escena «si: hecho:llego_veraneante»</t>
+          <t>una noticia «saben si hecho:llego_buhonero: …» o una escena «si: hecho:llego_buhonero»</t>
         </is>
       </c>
     </row>
@@ -36041,22 +36177,22 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Llegadas</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Presentación propia (cómo se presenta la primera vez)</t>
+          <t>una veraneante del hotel llega (de visita)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>32 usan la de siempre: Diana, el Sr. Shearer, el buhonero, el Sr. Phillips, el reverendo Allan, la Sra. Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King, Jasper Dale, Alec King, Janet King…</t>
+          <t>nadie lo nota (solo queda en el diario)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>«presentacion» en personajes.json, o «presenta» en src/js/56-gente-de-avonlea.js, con su voz</t>
+          <t>una noticia «saben si hecho:llego_veraneante: …» o una escena «si: hecho:llego_veraneante»</t>
         </is>
       </c>
     </row>
@@ -36073,17 +36209,17 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>el buhonero</t>
+          <t>Presentación propia (cómo se presenta la primera vez)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>32 usan la de siempre: Diana, el Sr. Shearer, el buhonero, el Sr. Phillips, el reverendo Allan, la Sra. Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King, Jasper Dale, Alec King, Janet King…</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>«presentacion» en personajes.json, o «presenta» en src/js/56-gente-de-avonlea.js, con su voz</t>
         </is>
       </c>
     </row>
@@ -36100,7 +36236,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Gertie Pye</t>
+          <t>el buhonero</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -36370,7 +36506,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Phillips</t>
+          <t>el reverendo Allan</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -36397,7 +36533,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>el reverendo Allan</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -36424,7 +36560,7 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>el herrero</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -36451,7 +36587,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>el herrero</t>
+          <t>el editor de La Crónica</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -36478,7 +36614,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>el editor de La Crónica</t>
+          <t>la Srta. Hetty King</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -36505,7 +36641,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>la Srta. Hetty King</t>
+          <t>Olivia King</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
@@ -36532,7 +36668,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Olivia King</t>
+          <t>Jasper Dale</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
@@ -36559,7 +36695,7 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Jasper Dale</t>
+          <t>Alec King</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
@@ -36586,7 +36722,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Alec King</t>
+          <t>Janet King</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
@@ -36613,7 +36749,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Janet King</t>
+          <t>la Sra. Pye</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -36640,12 +36776,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Pye</t>
+          <t>el Sr. Sloane</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>tiene 1 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -36667,7 +36803,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Sloane</t>
+          <t>el Sr. Andrews</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -36694,12 +36830,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Andrews</t>
+          <t>Peg Bowen</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -36721,7 +36857,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Peg Bowen</t>
+          <t>el Sr. Barry</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -36748,7 +36884,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Barry</t>
+          <t>Mary Joe</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
@@ -36775,7 +36911,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Mary Joe</t>
+          <t>Jerry Buote</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -36802,7 +36938,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Jerry Buote</t>
+          <t>el médico</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -36829,7 +36965,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>el médico</t>
+          <t>el Sr. Bell</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -36856,7 +36992,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Bell</t>
+          <t>la Sra. Spencer</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -36883,7 +37019,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Spencer</t>
+          <t>la Sra. Blewett</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -36910,7 +37046,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Blewett</t>
+          <t>Carrie Sloane</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
@@ -36937,7 +37073,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
+          <t>el jefe de estación</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -36964,12 +37100,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>el jefe de estación</t>
+          <t>Thomas Lynde</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>tiene 1 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -36991,12 +37127,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Thomas Lynde</t>
+          <t>una veraneante del hotel</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -37018,12 +37154,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>una veraneante del hotel</t>
+          <t>un pescador</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>tiene 1 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -37045,17 +37181,17 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>un pescador</t>
+          <t>Sin ninguna escena</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>42 de la gente del pueblo solo tienen frases sueltas: el buhonero, Josie Pye, Gertie Pye, Ruby Gillis, Jane Andrews, Prissy Andrews, Charlie Sloane, Moody Spurgeon, Tillie Boulter, Felicity King, Felix King, Cecily King, Sara Stanley, el Sr. Phillips, el reverendo Allan, el Sr. Lawson…</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena pequeña para los que importan en el libro</t>
         </is>
       </c>
     </row>
@@ -37067,22 +37203,22 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Hechos</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Sin ninguna escena</t>
+          <t>«ana_admite_gilbert»</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>42 de la gente del pueblo solo tienen frases sueltas: el buhonero, Josie Pye, Gertie Pye, Ruby Gillis, Jane Andrews, Prissy Andrews, Charlie Sloane, Moody Spurgeon, Tillie Boulter, Felicity King, Felix King, Cecily King, Sara Stanley, el Sr. Phillips, el reverendo Allan, el Sr. Lawson…</t>
+          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>una escena pequeña para los que importan en el libro</t>
+          <t>una escena, una frase o una noticia que lo recuerde</t>
         </is>
       </c>
     </row>
@@ -37099,7 +37235,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>«ana_admite_gilbert»</t>
+          <t>«blewett_orgullo»</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
@@ -37126,7 +37262,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>«blewett_orgullo»</t>
+          <t>«devuelta»</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
@@ -37153,7 +37289,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>«devuelta»</t>
+          <t>«marilla_doblo_ropa»</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
@@ -37180,7 +37316,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>«marilla_doblo_ropa»</t>
+          <t>«queens_primera»</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
@@ -37194,36 +37330,9 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Hechos</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>«queens_primera»</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>una escena, una frase o una noticia que lo recuerde</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E111"/>
-  <conditionalFormatting sqref="A2:A111">
+  <autoFilter ref="A1:E110"/>
+  <conditionalFormatting sqref="A2:A110">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>A2="alta"</formula>
     </cfRule>
@@ -37648,52 +37757,52 @@
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="K9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="M9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" s="19" t="n">
+      <c r="Q9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="19" t="n">
+      <c r="R9" s="19" t="n">
         <v>3</v>
-      </c>
-      <c r="R9" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -37738,10 +37847,10 @@
         <v>6</v>
       </c>
       <c r="M10" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" s="19" t="n">
         <v>5</v>
-      </c>
-      <c r="N10" s="19" t="n">
-        <v>6</v>
       </c>
       <c r="O10" s="19" t="n">
         <v>5</v>
@@ -38115,25 +38224,25 @@
         <v>0</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="19" t="n">
         <v>2</v>
@@ -40487,19 +40596,19 @@
         <v>0</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="19" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="19" t="n">
         <v>0</v>
@@ -40820,16 +40929,16 @@
         <v>5</v>
       </c>
       <c r="O58" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="P58" s="19" t="n">
-        <v>6</v>
-      </c>
       <c r="Q58" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R58" s="19" t="n">
         <v>5</v>
-      </c>
-      <c r="R58" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -40999,7 +41108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42139,12 +42248,19 @@
     <row r="113">
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>verano</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="E115" s="17" t="inlineStr">
         <is>
           <t>zanahorias</t>
         </is>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$166</definedName>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 13:43 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 14:19 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -31801,7 +31801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31844,173 +31844,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>«en camisón por el camino», cuando la ven fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Marilla</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>escena</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: su pieza · conoce a Marilla: sí</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>«marilla: Ana. Me vino a contar alguien que andabas en camisón por Avonlea. En ca» exige !donde:ana:tejas</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>«en camisón por el camino», cuando la ven fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Marilla</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>escena</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>día: 43 · estación: invierno · hora: 6:00 · Ana en: su pieza · conoce a Marilla: sí</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>«marilla: Ana. Alguien me dijo que anoche te vieron sola por el camino, a esas ho» exige !donde:ana:tejas</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>«en camisón por el camino», cuando la ven fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>la Sra. Barry</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>escena</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>día: 57 · estación: primavera · hora: 7:00 · Ana en: el patio de Tejas Verdes · Ana: en camisón · conoce a la Sra. Barry: sí</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>«barry: (La Sra. Barry se lleva la mano al pecho.) ¡Niña! ¿Andas en camisón por l» exige !donde:ana:tejas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>«en camisón por el camino», cuando la ven fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>la Sra. Lynde</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>escena</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>día: 46 · estación: invierno · hora: 7:00 · Ana en: la cocina de Tejas Verdes · Ana: en camisón · conoce a la Sra. Lynde: no</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>«lynde: ¡Habráse visto! ¡La huérfana de los Cuthbert, en camisón por el camino! E» exige !donde:ana:tejas</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>«en camisón por el camino», cuando la ven fuera de Tejas Verdes</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>la Srta. Hetty King</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a la Srta. Hetty King: sí</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>«Señorita, no se corre por la calle principal. ¡Y menos con el sombrero torcido!» exige !donde:ana:tejas</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>A2="incoherencia"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51131,7 +50966,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>¿Supo que anoche vieron a la niña de los Cuthbert sola por el camino? ¡A esas horas!</t>
+          <t>¿Supo que vieron a la niña de los Cuthbert sola por el camino, de noche? ¡A esas horas!</t>
         </is>
       </c>
       <c r="I15" s="9" t="n"/>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$166</definedName>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 14:19 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 15:01 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -13488,7 +13488,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, un comentario de espejo, una frase de matthew, una frase de marilla, una frase de lynde, meta conocer_diana</t>
+          <t>escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, un comentario de espejo, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
@@ -17986,7 +17986,11 @@
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
-      <c r="F114" s="7" t="inlineStr"/>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
@@ -18404,7 +18408,11 @@
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr"/>
-      <c r="F128" s="7" t="inlineStr"/>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="inlineStr"/>
       <c r="I128" s="7" t="inlineStr"/>
@@ -19924,7 +19932,11 @@
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr"/>
-      <c r="F182" s="7" t="inlineStr"/>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
       <c r="G182" s="7" t="n"/>
       <c r="H182" s="7" t="inlineStr"/>
       <c r="I182" s="7" t="inlineStr"/>
@@ -31801,7 +31813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31844,8 +31856,109 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>lo que supone que Ana se queda, cuando ya se queda</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Tillie Boulter</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>frase</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a Tillie Boulter: sí</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>«Encontré un nido de petirrojos detrás de la escuela. ¡No le digas a nadie!» exige hecho:se_queda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>lo que supone que Ana se queda, cuando ya se queda</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>el reverendo Allan</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>frase</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a el reverendo Allan: sí</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>«Que Dios te bendiga, Ana. ¿Te veremos el domingo en la escuela dominical?» exige hecho:se_queda</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>incoherencia</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>lo que supone que Ana se queda, cuando ya se queda</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>el Sr. Bell</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>frase</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a el Sr. Bell: sí</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>«Te esperamos el domingo en la escuela dominical, Ana. Y apréndete el versículo.» exige hecho:se_queda</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F4"/>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>A2="incoherencia"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36064,10 +36177,10 @@
         </is>
       </c>
       <c r="C22" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="19" t="n">
         <v>2</v>
@@ -37767,7 +37880,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="19" t="n">
         <v>1</v>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$166</definedName>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 15:01 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 17:36 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>hecho:diana_borracha</t>
+          <t>quedarse, hecho:diana_borracha</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -13826,7 +13826,11 @@
           <t>Visitar a la Sra. Lynde</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Vive en la Hondonada, junto al camino; desde su ventana lo ve todo. Por la tarde está en casa.</t>
@@ -13899,7 +13903,11 @@
           <t>Hacerle un regalo a Marilla que le guste</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
           <t>A Marilla le gusta lo hecho a mano. Las flores de la huerta también alegran.</t>
@@ -13968,7 +13976,11 @@
           <t>Ir a la escuela dominical</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
           <t>En la iglesia, camino a Bright River.</t>
@@ -13991,7 +14003,11 @@
           <t>Ir a la escuela</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
           <t>La escuela está junto al río, más allá de la aldea. Allí van Diana, Gilbert Blythe y los demás.</t>
@@ -14070,7 +14086,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>hecho:zanahorias, dias_desde:zanahorias:28, estudio:ana&gt;=30</t>
+          <t>quedarse, hecho:zanahorias, dias_desde:zanahorias:28, estudio:ana&gt;=30</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -14095,7 +14111,11 @@
           <t>Leer un libro de principio a fin</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Diana presta libros. Un buen rincón: la silla junto a la ventana de la cocina.</t>
@@ -14118,7 +14138,11 @@
           <t>Escribir una carta y mandarla</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Se escribe en el escritorio de su pieza; el correo está en la tienda de Lawson.</t>
@@ -14245,7 +14269,11 @@
           <t>Adornar su sombrero con flores</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Con un ramo de la huerta (Marilla no lo va a aprobar).</t>
@@ -14295,7 +14323,11 @@
           <t>Patinar en el lago helado</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Solo en invierno.</t>
@@ -14318,7 +14350,11 @@
           <t>Tirarse en trineo colina abajo</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Solo en invierno, en la colina.</t>
@@ -14341,7 +14377,11 @@
           <t>Teñirse el pelo de negro azabache</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>quedarse</t>
+        </is>
+      </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
           <t>El buhonero vende un tinte que promete maravillas… y acepta huevos.</t>
@@ -31813,7 +31853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31856,109 +31896,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>lo que supone que Ana se queda, cuando ya se queda</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Tillie Boulter</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a Tillie Boulter: sí</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>«Encontré un nido de petirrojos detrás de la escuela. ¡No le digas a nadie!» exige hecho:se_queda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>lo que supone que Ana se queda, cuando ya se queda</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>el reverendo Allan</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a el reverendo Allan: sí</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>«Que Dios te bendiga, Ana. ¿Te veremos el domingo en la escuela dominical?» exige hecho:se_queda</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>incoherencia</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>lo que supone que Ana se queda, cuando ya se queda</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>el Sr. Bell</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>frase</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>día: 1 · estación: primavera · hora: 6:00 · Ana en: la cocina de Tejas Verdes · conoce a el Sr. Bell: sí</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>«Te esperamos el domingo en la escuela dominical, Ana. Y apréndete el versículo.» exige hecho:se_queda</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>A2="incoherencia"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 17:36 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-16 18:42 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -12004,7 +12004,7 @@
       <c r="B6" s="11" t="inlineStr"/>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>una frase de barry</t>
+          <t>escena camison_barry, una frase de barry</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -12850,7 +12850,7 @@
       <c r="B59" s="11" t="inlineStr"/>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_se_entera, una frase de lynde</t>
+          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr"/>
@@ -45279,7 +45279,7 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas, ve:barry, sabe:barry:nina_cuthbert, hora:7-21</t>
+          <t>ana:camison, !donde:ana:tejas, ve:barry, sabe:barry:nina_cuthbert, !comento:barry:ana:camison, hora:7-21</t>
         </is>
       </c>
       <c r="I60" s="9" t="n"/>
@@ -45334,7 +45334,7 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas, ve:lynde, sabe:lynde:nina_cuthbert, hora:7-21</t>
+          <t>ana:camison, !donde:ana:tejas, ve:lynde, sabe:lynde:nina_cuthbert, !comento:lynde:ana:camison, hora:7-21</t>
         </is>
       </c>
       <c r="I61" s="9" t="n"/>
@@ -50629,7 +50629,8 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>lynde: ¿Supo lo de los Cuthbert? ¡Pidieron un niño y les llegó una niña! Pelirroja, dicen. Yo siempre dije que eso de traer huérfanos…</t>
+          <t>lynde: ¿Supo lo de los Cuthbert? ¡Pidieron un niño y les llegó una niña! Pelirroja, dicen. Yo siempre dije que eso de traer huérfanos…
+niños: ¿Sabías? ¡En Tejas Verdes hay una niña nueva! Del orfanato. Y es pelirroja, pelirroja como una zanahoria.</t>
         </is>
       </c>
       <c r="J3" s="9" t="n"/>
@@ -50667,7 +50668,11 @@
           <t>¿Supo que la niña de los Cuthbert anda en camisón por las casas? ¡En camisón!</t>
         </is>
       </c>
-      <c r="I4" s="9" t="n"/>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>niños: ¿Sabías que la niña nueva de Tejas Verdes salió en camisón a la calle? ¡En camisón! Mi mamá dice que eso no se hace.</t>
+        </is>
+      </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
           <t>¿Supo? ¡La niña de los Cuthbert anda en camisón por todo Avonlea, y descalza! Con este frío.
@@ -50705,7 +50710,11 @@
           <t>¿Supo que a los Pye se les escapó otra vez el cerdo? Yo siempre lo dije.</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>niños: ¡Se les escapó el chancho a los Pye otra vez! Lo vi correr por el camino.</t>
+        </is>
+      </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
     </row>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Noticias'!$A$1:$K$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Llegadas'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Diálogos'!$A$1:$C$657</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-16 22:38 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-17 06:08 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12960,12 +12960,12 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>hito_paciencia_4</t>
+          <t>hito_mano_cocina_2</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>habilidad paciencia</t>
+          <t>habilidad mano_cocina</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr"/>
@@ -12974,98 +12974,82 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>inicio_juego</t>
+          <t>hito_mano_cocina_7</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>habilidad mano_cocina</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr"/>
       <c r="D46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>invierno</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr"/>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild</t>
-        </is>
-      </c>
+          <t>hito_mano_leche_3</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>habilidad mano_leche</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr"/>
       <c r="D47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>llamada_almuerzo</t>
+          <t>hito_mano_leche_7</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
-        </is>
-      </c>
+          <t>habilidad mano_leche</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr"/>
       <c r="D48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>llegada_tv</t>
+          <t>hito_mano_lena_2</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>escena llegada, escena inicio_llegada</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>escena primera_noche, escena desayuno_prueba, una frase de vecino, llegadas de diana</t>
-        </is>
-      </c>
+          <t>habilidad mano_lena</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr"/>
       <c r="D49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>llegaron</t>
+          <t>hito_mano_lena_5</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>escena llegada</t>
-        </is>
-      </c>
+          <t>habilidad mano_lena</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr"/>
       <c r="D50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>llego_</t>
+          <t>hito_paciencia_4</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>habilidad paciencia</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr"/>
@@ -13074,17 +13058,17 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>llego_allan</t>
+          <t>inicio_juego</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>noticia pastor_nuevo</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr"/>
@@ -13092,45 +13076,49 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>llego_buhonero</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr"/>
+          <t>invierno</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr"/>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild</t>
+        </is>
+      </c>
       <c r="D53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>llego_diana</t>
+          <t>llamada_almuerzo</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr"/>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
+        </is>
+      </c>
       <c r="D54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>llego_gilbert</t>
+          <t>llegada_tv</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>escena llegada, escena inicio_llegada</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena primera_noche, escena desayuno_prueba, una frase de vecino, llegadas de diana</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr"/>
@@ -13138,17 +13126,17 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>llego_josephine</t>
+          <t>llegaron</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>llegadas de phillips</t>
+          <t>escena llegada</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr"/>
@@ -13156,12 +13144,12 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>llego_sraallan</t>
+          <t>llego_</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr"/>
@@ -13170,7 +13158,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>llego_stacy</t>
+          <t>llego_allan</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -13180,7 +13168,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>noticia pastor_nuevo</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr"/>
@@ -13188,7 +13176,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>llego_veraneante</t>
+          <t>llego_buhonero</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -13202,31 +13190,31 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>lynde</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr"/>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
-        </is>
-      </c>
+          <t>llego_diana</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr"/>
       <c r="D60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>llego_gilbert</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita</t>
+          <t>llegadas</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>una frase de lynde, noticia ana_lengua</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr"/>
@@ -13234,13 +13222,17 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>marilla</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr"/>
+          <t>llego_josephine</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza, escena geranio_sola</t>
+          <t>llegadas de phillips</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr"/>
@@ -13248,31 +13240,31 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>marilla_doblo_ropa</t>
+          <t>llego_sraallan</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>llegadas</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>marilla_sabe_camison</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr"/>
+          <t>llego_stacy</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison_descalza</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr"/>
@@ -13280,35 +13272,27 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>matthew_en_estacion</t>
+          <t>llego_veraneante</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>escena estacion</t>
-        </is>
-      </c>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>matthew_llego_casa</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>lynde</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr"/>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>escena tejas_verdes (alternativa)</t>
+          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr"/>
@@ -13316,13 +13300,17 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>nombra_avenida</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr"/>
+          <t>lynde_visita</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_visita</t>
+        </is>
+      </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>escena conv_matthew_nombres</t>
+          <t>una frase de lynde, noticia ana_lengua</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr"/>
@@ -13330,25 +13318,21 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>nombre_propio_</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>marilla</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr"/>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza, escena geranio_sola</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>nombro_</t>
+          <t>marilla_doblo_ropa</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -13366,17 +13350,13 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>nombro_avenida</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>escena nombra_avenida</t>
-        </is>
-      </c>
+          <t>marilla_sabe_camison</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr"/>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>escena conv_matthew_nombres</t>
+          <t>escena marilla_sabe_camison_descalza</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr"/>
@@ -13384,53 +13364,49 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>nombro_burbuja</t>
+          <t>matthew_en_estacion</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>escena estacion</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>nombro_cerezo</t>
+          <t>matthew_llego_casa</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>escena primera_gwin</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>escena tejas_verdes (alternativa)</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>nombro_geranio</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>escena primera_geranio, escena geranio_sola</t>
-        </is>
-      </c>
+          <t>nombra_avenida</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr"/>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>escena geranio_sola</t>
+          <t>escena conv_matthew_nombres</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr"/>
@@ -13438,30 +13414,30 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>nombro_lago</t>
+          <t>nombre_propio_</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>escena lago</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>escena conv_matthew_nombres</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr"/>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>nombro_senda</t>
+          <t>nombro_</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr"/>
@@ -13474,17 +13450,17 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>nombro_avenida</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita (una opción)</t>
+          <t>escena nombra_avenida</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, una frase de lynde, noticia ana_lengua</t>
+          <t>escena conv_matthew_nombres</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr"/>
@@ -13492,53 +13468,53 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>pastel_linimento</t>
+          <t>nombro_burbuja</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>escena pastel_linimento</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>meta allan</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr"/>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>perdon_pedido</t>
+          <t>nombro_cerezo</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_perdon_marilla</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_perdon_marilla</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr"/>
+          <t>escena primera_gwin</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>nombro_geranio</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>escena crup_salva</t>
+          <t>escena primera_geranio, escena geranio_sola</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico</t>
+          <t>escena geranio_sola</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr"/>
@@ -13546,17 +13522,17 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>pide_amiga</t>
+          <t>nombro_lago</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena lago</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena conv_matthew_nombres</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr"/>
@@ -13564,31 +13540,35 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>primera_bed</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr"/>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>escena primera_noche_sube</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr"/>
+          <t>nombro_senda</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>primera_noche</t>
+          <t>ofendio_lynde</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>escena inicio_llegada, escena primera_noche</t>
+          <t>escena lynde_visita (una opción)</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche</t>
+          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, una frase de lynde, noticia ana_lengua</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr"/>
@@ -13596,17 +13576,17 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>pastel_linimento</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida</t>
+          <t>escena pastel_linimento</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>escena barry_no_perdona, escena crup_aviso, escena crup_salva, escena ventana_prohibida, escena lugar_cuesta_prohibida, una frase de diana, una frase de barry</t>
+          <t>meta allan</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr"/>
@@ -13614,17 +13594,17 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>queens</t>
+          <t>perdon_pedido</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera, escena examen_entra</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_queens, escena faro_queens</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr"/>
@@ -13632,35 +13612,35 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>queens_primera</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena crup_salva</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>quiere_amiga</t>
+          <t>pide_amiga</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>escena quiere_amiga</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>escena barry_recibe, meta conocer_diana (pista)</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr"/>
@@ -13668,17 +13648,13 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>rachel_en_casa_bell</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>primera_bed</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr"/>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_bell</t>
+          <t>escena primera_noche_sube</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr"/>
@@ -13686,17 +13662,17 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>rachel_llego_tejas_verdes</t>
+          <t>primera_noche</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena inicio_llegada, escena primera_noche</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
+          <t>escena primera_noche</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr"/>
@@ -13704,17 +13680,17 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>rachel_lo_sabe</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
+          <t>escena prohibida</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena barry_no_perdona, escena crup_aviso, escena crup_salva, escena ventana_prohibida, escena lugar_cuesta_prohibida, una frase de diana, una frase de barry</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr"/>
@@ -13722,17 +13698,17 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>ropa_arrugada</t>
+          <t>queens</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena examen_primera, escena examen_entra</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla</t>
+          <t>escena ventana_queens, escena faro_queens</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr"/>
@@ -13740,35 +13716,35 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>ropa_ordenada</t>
+          <t>queens_primera</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>una frase de marilla, código</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr"/>
+          <t>escena examen_primera</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>ropa_tirada_otra</t>
+          <t>quiere_amiga</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena quiere_amiga</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>escena falta_ropa (una opción), código</t>
+          <t>escena barry_recibe, meta conocer_diana (pista)</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr"/>
@@ -13776,7 +13752,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>se_fue_</t>
+          <t>rachel_en_casa_bell</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -13784,37 +13760,45 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>escena rachel_bell</t>
+        </is>
+      </c>
       <c r="D93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>se_fue_buhonero</t>
+          <t>rachel_llego_tejas_verdes</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>escena rachel_marilla</t>
+        </is>
+      </c>
       <c r="D94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>se_fue_josephine</t>
+          <t>rachel_lo_sabe</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>escena rachel_marilla</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>llegadas de allan, llegadas de sraallan</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr"/>
@@ -13822,17 +13806,17 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>se_fue_phillips</t>
+          <t>ropa_arrugada</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
+          <t>una frase de marilla</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
@@ -13840,73 +13824,81 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>se_fue_prissy</t>
+          <t>ropa_ordenada</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>una frase de marilla, código</t>
+        </is>
+      </c>
       <c r="D97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>se_fue_veraneante</t>
+          <t>ropa_tirada_otra</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>escena falta_ropa (una opción), código</t>
+        </is>
+      </c>
       <c r="D98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>se_fue_</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>escena se_queda</t>
-        </is>
-      </c>
-      <c r="C99" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, escena conv_marilla_por_que, un comentario de espejo, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana</t>
-        </is>
-      </c>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr"/>
       <c r="D99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>undefined</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr"/>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t>escena primera_noche, un comentario de sueno_1, un comentario de sueno_2</t>
-        </is>
-      </c>
+          <t>se_fue_buhonero</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr"/>
       <c r="D100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>verano</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="inlineStr"/>
+          <t>se_fue_josephine</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>una frase de phillips</t>
+          <t>llegadas de allan, llegadas de sraallan</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr"/>
@@ -13914,13 +13906,17 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr"/>
+          <t>se_fue_phillips</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr"/>
@@ -13928,39 +13924,127 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>zanahorias</t>
+          <t>se_fue_prissy</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>escena zanahorias</t>
-        </is>
-      </c>
-      <c r="C103" s="11" t="inlineStr">
-        <is>
-          <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, un comentario de pupitre, un comentario de pizarra, una frase de gilbert, meta paces</t>
-        </is>
-      </c>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr"/>
       <c r="D103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
+          <t>se_fue_veraneante</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr"/>
+      <c r="D104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>escena se_queda</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, escena conv_marilla_por_que, un comentario de espejo, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr"/>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>escena primera_noche, un comentario de sueno_1, un comentario de sueno_2</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>verano</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr"/>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>una frase de phillips</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr"/>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, un comentario de pupitre, un comentario de pizarra, una frase de gilbert, meta paces</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
           <t>{k}</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr"/>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr"/>
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>una frase de niños</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr"/>
+      <c r="D110" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <autoFilter ref="A1:D104"/>
-  <conditionalFormatting sqref="D2:D104">
+  <autoFilter ref="A1:D110"/>
+  <conditionalFormatting sqref="D2:D110">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(D2,5)="nunca"</formula>
     </cfRule>
@@ -32220,10 +32304,10 @@
       <formula1>=Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="No es un hecho ni una meta que exista (¿está bien escrito?)." type="list" errorStyle="warning">
-      <formula1>=Listas!$E$2:$E$119</formula1>
+      <formula1>=Listas!$E$2:$E$125</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="No es un hecho ni una meta que exista (¿está bien escrito?)." type="list" errorStyle="warning">
-      <formula1>=Listas!$E$2:$E$119</formula1>
+      <formula1>=Listas!$E$2:$E$125</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="primavera, verano, otoño o invierno." type="list" errorStyle="stop">
       <formula1>=Listas!$D$2:$D$5</formula1>
@@ -39213,7 +39297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39755,7 +39839,7 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>hito_paciencia_4</t>
+          <t>hito_mano_cocina_2</t>
         </is>
       </c>
     </row>
@@ -39767,7 +39851,7 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>huerta</t>
+          <t>hito_mano_cocina_7</t>
         </is>
       </c>
     </row>
@@ -39779,7 +39863,7 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>inicio_juego</t>
+          <t>hito_mano_leche_3</t>
         </is>
       </c>
     </row>
@@ -39791,7 +39875,7 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>hito_mano_leche_7</t>
         </is>
       </c>
     </row>
@@ -39803,7 +39887,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>hito_mano_lena_2</t>
         </is>
       </c>
     </row>
@@ -39815,7 +39899,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>leido</t>
+          <t>hito_mano_lena_5</t>
         </is>
       </c>
     </row>
@@ -39827,7 +39911,7 @@
       </c>
       <c r="E45" s="17" t="inlineStr">
         <is>
-          <t>llamada_almuerzo</t>
+          <t>hito_paciencia_4</t>
         </is>
       </c>
     </row>
@@ -39839,7 +39923,7 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>llegada_tv</t>
+          <t>huerta</t>
         </is>
       </c>
     </row>
@@ -39851,7 +39935,7 @@
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>llegaron</t>
+          <t>inicio_juego</t>
         </is>
       </c>
     </row>
@@ -39863,7 +39947,7 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>llego_</t>
+          <t>invierno</t>
         </is>
       </c>
     </row>
@@ -39875,7 +39959,7 @@
       </c>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>llego_allan</t>
+          <t>josephine</t>
         </is>
       </c>
     </row>
@@ -39887,7 +39971,7 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>llego_buhonero</t>
+          <t>leido</t>
         </is>
       </c>
     </row>
@@ -39899,7 +39983,7 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>llego_diana</t>
+          <t>llamada_almuerzo</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39995,7 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>llego_gilbert</t>
+          <t>llegada_tv</t>
         </is>
       </c>
     </row>
@@ -39923,7 +40007,7 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>llego_josephine</t>
+          <t>llegaron</t>
         </is>
       </c>
     </row>
@@ -39935,7 +40019,7 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>llego_sraallan</t>
+          <t>llego_</t>
         </is>
       </c>
     </row>
@@ -39947,7 +40031,7 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>llego_stacy</t>
+          <t>llego_allan</t>
         </is>
       </c>
     </row>
@@ -39959,7 +40043,7 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>llego_veraneante</t>
+          <t>llego_buhonero</t>
         </is>
       </c>
     </row>
@@ -39971,439 +40055,481 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>lynde</t>
+          <t>llego_diana</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>llego_gilbert</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>marilla</t>
+          <t>llego_josephine</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>marilla_doblo_ropa</t>
+          <t>llego_sraallan</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>marilla_sabe_camison</t>
+          <t>llego_stacy</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>matthew_en_estacion</t>
+          <t>llego_veraneante</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>matthew_llego_casa</t>
+          <t>lynde</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>nombra_avenida</t>
+          <t>lynde_visita</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>nombre_propio_</t>
+          <t>marilla</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>nombres</t>
+          <t>marilla_doblo_ropa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>nombro_</t>
+          <t>marilla_sabe_camison</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>nombro_avenida</t>
+          <t>matthew_en_estacion</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>nombro_burbuja</t>
+          <t>matthew_llego_casa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>nombro_cerezo</t>
+          <t>nombra_avenida</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>nombro_geranio</t>
+          <t>nombre_propio_</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>nombro_lago</t>
+          <t>nombres</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>nombro_senda</t>
+          <t>nombro_</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>nombro_avenida</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>paces</t>
+          <t>nombro_burbuja</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>pastel_linimento</t>
+          <t>nombro_cerezo</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>patinar</t>
+          <t>nombro_geranio</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>pelo_corto</t>
+          <t>nombro_lago</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>perdon_barry</t>
+          <t>nombro_senda</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>perdon_pedido</t>
+          <t>ofendio_lynde</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>paces</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>picnic</t>
+          <t>pastel_linimento</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>pide_amiga</t>
+          <t>patinar</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>primera_bed</t>
+          <t>pelo_corto</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>primera_noche</t>
+          <t>perdon_barry</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>perdon_pedido</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>quedarse</t>
+          <t>perdonada</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>queens</t>
+          <t>picnic</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>queens_primera</t>
+          <t>pide_amiga</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>quehaceres</t>
+          <t>primera_bed</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>quiere_amiga</t>
+          <t>primera_noche</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>rachel_en_casa_bell</t>
+          <t>prohibida</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>rachel_llego_tejas_verdes</t>
+          <t>quedarse</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>rachel_lo_sabe</t>
+          <t>queens</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>recito</t>
+          <t>queens_primera</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>regalo</t>
+          <t>quehaceres</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>remo</t>
+          <t>quiere_amiga</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>rezo</t>
+          <t>rachel_en_casa_bell</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>ropa_arrugada</t>
+          <t>rachel_llego_tejas_verdes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>ropa_ordenada</t>
+          <t>rachel_lo_sabe</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>ropa_tirada_otra</t>
+          <t>recito</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>sala</t>
+          <t>regalo</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>se_fue_</t>
+          <t>remo</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>se_fue_buhonero</t>
+          <t>rezo</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>se_fue_josephine</t>
+          <t>ropa_arrugada</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>se_fue_phillips</t>
+          <t>ropa_ordenada</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>se_fue_prissy</t>
+          <t>ropa_tirada_otra</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>se_fue_veraneante</t>
+          <t>sala</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>se_fue_</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>sombrero</t>
+          <t>se_fue_buhonero</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="E111" s="17" t="inlineStr">
         <is>
-          <t>te_diana</t>
+          <t>se_fue_josephine</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>techo</t>
+          <t>se_fue_phillips</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>tinte</t>
+          <t>se_fue_prissy</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>trineo</t>
+          <t>se_fue_veraneante</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>undefined</t>
+          <t>se_queda</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>sombrero</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>te_diana</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>zanahorias</t>
+          <t>techo</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>tinte</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>trineo</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>verano</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="E125" s="17" t="inlineStr">
         <is>
           <t>{k}</t>
         </is>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -24,13 +24,13 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Noticias'!$A$1:$K$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Llegadas'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Diálogos'!$A$1:$C$828</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-19 00:41 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-19 12:50 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15569,7 +15569,7 @@
       <c r="B25" s="11" t="inlineStr"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>una frase de jane</t>
+          <t>escena conv_jane_maestra, una frase de jane</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -15577,13 +15577,13 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>conoce_lawson</t>
+          <t>conoce_josie</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>una frase de lawson</t>
+          <t>escena conv_josie_cerca</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -15591,13 +15591,13 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>conoce_lynde</t>
+          <t>conoce_lawson</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr"/>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>una frase de lynde</t>
+          <t>una frase de lawson</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -15605,13 +15605,13 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>conoce_minnie</t>
+          <t>conoce_lynde</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr"/>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>una frase de minnie</t>
+          <t>una frase de lynde</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
@@ -15619,13 +15619,13 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>conoce_sara</t>
+          <t>conoce_minnie</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr"/>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>una frase de sara</t>
+          <t>escena conv_minnie_cuento, una frase de minnie</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
@@ -15633,17 +15633,13 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>conoce_sraallan</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>escena invita_allan</t>
-        </is>
-      </c>
+          <t>conoce_phillips</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr"/>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>una frase de sraallan, código</t>
+          <t>escena conv_phillips_libro</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
@@ -15651,13 +15647,13 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>conoce_stacy</t>
+          <t>conoce_ruby</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr"/>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>escena espejo_estudio, escena conv_marilla_queens, escena conv_matthew_queens, escena conv_diana_futuro, una frase de stacy, meta queens (pista), código</t>
+          <t>escena conv_ruby_muchachos</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -15665,17 +15661,13 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>conocidas_diana</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>escena conoce_diana, escena diana_por_casualidad, código</t>
-        </is>
-      </c>
+          <t>conoce_sara</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr"/>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>escena quiere_amiga, escena aviso_barry, escena barry_recibe, escena conoce_diana, escena diana_por_casualidad, una frase de diana, meta conocer_diana, código</t>
+          <t>una frase de sara</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
@@ -15683,13 +15675,17 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>conv_marilla_oraciones</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr"/>
+          <t>conoce_sraallan</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>escena invita_allan</t>
+        </is>
+      </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla</t>
+          <t>escena conv_sraallan_ser_buena, una frase de sraallan, código</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -15697,17 +15693,13 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>crup</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>escena crup_aviso</t>
-        </is>
-      </c>
+          <t>conoce_stacy</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr"/>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>escena crup_salva, meta perdon_barry (pista)</t>
+          <t>escena espejo_estudio, escena conv_marilla_queens, escena conv_matthew_queens, escena conv_diana_futuro, escena conv_stacy_queens, escena conv_stacy_escribir, una frase de stacy, meta queens (pista), código</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -15715,17 +15707,17 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>desayuno_prueba</t>
+          <t>conocidas_diana</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>escena desayuno_prueba</t>
+          <t>escena conoce_diana, escena diana_por_casualidad, código</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_se_entera, escena viaje_spencer, escena llamar_almuerzo, escena llamar_almuerzo_afuera, escena falta_camison, escena falta_noche, escena falta_viaje, escena viaje_spencer_duda, escena primera_stairs</t>
+          <t>escena quiere_amiga, escena aviso_barry, escena barry_recibe, escena conoce_diana, escena diana_por_casualidad, una frase de diana, meta conocer_diana, código</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -15733,17 +15725,13 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>desde_estacion</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>conv_marilla_oraciones</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>escena inicio_llegada (narra salvo)</t>
+          <t>una frase de marilla</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -15751,17 +15739,17 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>devuelta</t>
+          <t>crup</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>escena devuelta_blewett</t>
+          <t>escena crup_aviso</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>hito decision</t>
+          <t>escena crup_salva, meta perdon_barry (pista)</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -15769,17 +15757,17 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>diana_borracha</t>
+          <t>desayuno_prueba</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>escena te_grosella</t>
+          <t>escena desayuno_prueba</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida, meta perdon_barry, hito amistad_a_prueba</t>
+          <t>escena lynde_se_entera, escena viaje_spencer, escena llamar_almuerzo, escena llamar_almuerzo_afuera, escena falta_camison, escena falta_noche, escena falta_viaje, escena viaje_spencer_duda, escena primera_stairs</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
@@ -15787,17 +15775,17 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>disculpa_lynde</t>
+          <t>desde_estacion</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_disculpa</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>hito humillada, hito pedir_perdon</t>
+          <t>escena inicio_llegada (narra salvo)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr"/>
@@ -15805,13 +15793,17 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr"/>
+          <t>devuelta</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>escena devuelta_blewett</t>
+        </is>
+      </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>una frase de gertie</t>
+          <t>hito decision</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr"/>
@@ -15819,17 +15811,17 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>examen</t>
+          <t>diana_borracha</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera, escena examen_entra, escena examen_no</t>
+          <t>escena te_grosella</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>meta queens (pista)</t>
+          <t>escena prohibida, meta perdon_barry, hito amistad_a_prueba</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -15837,17 +15829,17 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>historia_</t>
+          <t>disculpa_lynde</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena lynde_disculpa</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>hito humillada, hito pedir_perdon</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
@@ -15855,49 +15847,57 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>historia_a_prueba</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>hitos</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr"/>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>una frase de gertie</t>
+        </is>
+      </c>
       <c r="D43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>historia_a_prueba_cerrado</t>
+          <t>examen</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>hitos</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr"/>
+          <t>escena examen_primera, escena examen_entra, escena examen_no</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>meta queens (pista)</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma</t>
+          <t>historia_</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>hitos</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="D45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_cerrado</t>
+          <t>historia_a_prueba</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -15911,7 +15911,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_juran</t>
+          <t>historia_a_prueba_cerrado</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -15925,7 +15925,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_no_juran</t>
+          <t>historia_amiga_del_alma</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -15939,7 +15939,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba</t>
+          <t>historia_amiga_del_alma_cerrado</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -15953,7 +15953,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba_cerrado</t>
+          <t>historia_amiga_del_alma_juran</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -15967,7 +15967,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba_la_recupera</t>
+          <t>historia_amiga_del_alma_no_juran</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -15981,7 +15981,7 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla</t>
+          <t>historia_amistad_a_prueba</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -15995,7 +15995,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_cerrado</t>
+          <t>historia_amistad_a_prueba_cerrado</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -16009,7 +16009,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_confiesa_en_falso</t>
+          <t>historia_amistad_a_prueba_la_recupera</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -16023,7 +16023,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_dice_la_verdad</t>
+          <t>historia_confianza_marilla</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -16037,7 +16037,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>historia_decision</t>
+          <t>historia_confianza_marilla_cerrado</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -16051,7 +16051,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>historia_decision_cerrado</t>
+          <t>historia_confianza_marilla_confiesa_en_falso</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -16065,7 +16065,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>historia_decision_devuelta</t>
+          <t>historia_confianza_marilla_dice_la_verdad</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -16079,7 +16079,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>historia_decision_se_queda</t>
+          <t>historia_decision</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -16093,7 +16093,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada</t>
+          <t>historia_decision_cerrado</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -16107,7 +16107,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_cerrado</t>
+          <t>historia_decision_devuelta</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -16121,7 +16121,7 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_estalla</t>
+          <t>historia_decision_se_queda</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -16135,7 +16135,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_llora</t>
+          <t>historia_humillada</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -16149,7 +16149,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_se_contiene</t>
+          <t>historia_humillada_cerrado</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -16163,7 +16163,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>historia_llegada</t>
+          <t>historia_humillada_estalla</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -16177,7 +16177,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>historia_llegada_cerrado</t>
+          <t>historia_humillada_llora</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -16191,7 +16191,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>historia_matthew_aliado</t>
+          <t>historia_humillada_se_contiene</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -16205,7 +16205,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>historia_matthew_aliado_cerrado</t>
+          <t>historia_llegada</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -16219,7 +16219,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon</t>
+          <t>historia_llegada_cerrado</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -16233,7 +16233,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon_a_lo_grande</t>
+          <t>historia_matthew_aliado</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -16247,7 +16247,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon_cerrado</t>
+          <t>historia_matthew_aliado_cerrado</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -16261,7 +16261,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>historia_rival</t>
+          <t>historia_pedir_perdon</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -16275,7 +16275,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_cerrado</t>
+          <t>historia_pedir_perdon_a_lo_grande</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -16289,7 +16289,7 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_le_contesta</t>
+          <t>historia_pedir_perdon_cerrado</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -16303,7 +16303,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_lo_ignora</t>
+          <t>historia_rival</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -16317,7 +16317,7 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_pizarra</t>
+          <t>historia_rival_cerrado</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -16331,7 +16331,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>historia_sombrero_iglesia</t>
+          <t>historia_rival_le_contesta</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -16345,7 +16345,7 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>historia_sombrero_iglesia_cerrado</t>
+          <t>historia_rival_lo_ignora</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -16359,12 +16359,12 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_20</t>
+          <t>historia_rival_pizarra</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>habilidad estudio</t>
+          <t>hitos</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr"/>
@@ -16373,12 +16373,12 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_50</t>
+          <t>historia_sombrero_iglesia</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>habilidad estudio</t>
+          <t>hitos</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr"/>
@@ -16387,12 +16387,12 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_85</t>
+          <t>historia_sombrero_iglesia_cerrado</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>habilidad estudio</t>
+          <t>hitos</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr"/>
@@ -16401,12 +16401,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_10</t>
+          <t>hito_estudio_20</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>habilidad granja</t>
+          <t>habilidad estudio</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr"/>
@@ -16415,12 +16415,12 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_40</t>
+          <t>hito_estudio_50</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>habilidad granja</t>
+          <t>habilidad estudio</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr"/>
@@ -16429,12 +16429,12 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_80</t>
+          <t>hito_estudio_85</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>habilidad granja</t>
+          <t>habilidad estudio</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr"/>
@@ -16443,12 +16443,12 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_10</t>
+          <t>hito_granja_10</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>habilidad letras</t>
+          <t>habilidad granja</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr"/>
@@ -16457,12 +16457,12 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_30</t>
+          <t>hito_granja_40</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>habilidad letras</t>
+          <t>habilidad granja</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr"/>
@@ -16471,12 +16471,12 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_60</t>
+          <t>hito_granja_80</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>habilidad letras</t>
+          <t>habilidad granja</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr"/>
@@ -16485,12 +16485,12 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_cocina_2</t>
+          <t>hito_letras_10</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>habilidad mano_cocina</t>
+          <t>habilidad letras</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr"/>
@@ -16499,12 +16499,12 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_cocina_7</t>
+          <t>hito_letras_30</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>habilidad mano_cocina</t>
+          <t>habilidad letras</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr"/>
@@ -16513,12 +16513,12 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_leche_3</t>
+          <t>hito_letras_60</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>habilidad mano_leche</t>
+          <t>habilidad letras</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr"/>
@@ -16527,12 +16527,12 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_leche_7</t>
+          <t>hito_mano_cocina_2</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>habilidad mano_leche</t>
+          <t>habilidad mano_cocina</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr"/>
@@ -16541,12 +16541,12 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>hito_paciencia_4</t>
+          <t>hito_mano_cocina_7</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>habilidad paciencia</t>
+          <t>habilidad mano_cocina</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr"/>
@@ -16555,67 +16555,59 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>inicio_juego</t>
+          <t>hito_mano_leche_3</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>habilidad mano_leche</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr"/>
       <c r="D93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>invierno</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr"/>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild, escena conv_matthew_huerta</t>
-        </is>
-      </c>
+          <t>hito_mano_leche_7</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>habilidad mano_leche</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr"/>
       <c r="D94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>llamada_almuerzo</t>
+          <t>hito_paciencia_4</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
-        </is>
-      </c>
-      <c r="C95" s="11" t="inlineStr">
-        <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
-        </is>
-      </c>
+          <t>habilidad paciencia</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr"/>
       <c r="D95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>llegada_tv</t>
+          <t>inicio_juego</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>escena llegada, escena inicio_llegada</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche, escena desayuno_prueba, escena lugar_aldea, una frase de lawson, una frase de vecino, llegadas de diana, hito llegada</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
@@ -16623,17 +16615,13 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>llegaron</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>invierno</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr"/>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>escena llegada</t>
+          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild, escena conv_matthew_huerta</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr"/>
@@ -16641,17 +16629,17 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>llego_</t>
+          <t>llamada_almuerzo</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr"/>
@@ -16659,17 +16647,17 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>llego_allan</t>
+          <t>llegada_tv</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>escena llegada, escena inicio_llegada</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>noticia pastor_nuevo</t>
+          <t>escena primera_noche, escena desayuno_prueba, escena lugar_aldea, una frase de lawson, una frase de vecino, llegadas de diana, hito llegada</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr"/>
@@ -16677,35 +16665,43 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>llego_buhonero</t>
+          <t>llegaron</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>escena llegada</t>
+        </is>
+      </c>
       <c r="D100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>llego_diana</t>
+          <t>llego_</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C101" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="D101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>llego_gilbert</t>
+          <t>llego_allan</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -16715,7 +16711,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>charla par:ana+diana:5</t>
+          <t>noticia pastor_nuevo</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr"/>
@@ -16723,7 +16719,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>llego_josephine</t>
+          <t>llego_buhonero</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -16731,17 +16727,13 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C103" s="11" t="inlineStr">
-        <is>
-          <t>llegadas de phillips</t>
-        </is>
-      </c>
+      <c r="C103" s="11" t="inlineStr"/>
       <c r="D103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>llego_sraallan</t>
+          <t>llego_diana</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -16755,7 +16747,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>llego_stacy</t>
+          <t>llego_gilbert</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -16765,7 +16757,7 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>charla par:lynde+marilla:3, una frase de carrie, noticia maestra_plumas</t>
+          <t>charla par:ana+diana:5</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr"/>
@@ -16773,7 +16765,7 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>llego_veraneante</t>
+          <t>llego_josephine</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -16781,37 +16773,41 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C106" s="11" t="inlineStr"/>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>llegadas de phillips</t>
+        </is>
+      </c>
       <c r="D106" s="8" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>lynde</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr"/>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
-        </is>
-      </c>
+          <t>llego_sraallan</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr"/>
       <c r="D107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>lynde_contenida</t>
+          <t>llego_stacy</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita (una opción)</t>
+          <t>llegadas</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>hito humillada</t>
+          <t>charla par:lynde+marilla:3, una frase de carrie, noticia maestra_plumas</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr"/>
@@ -16819,35 +16815,27 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>lynde_llanto</t>
+          <t>llego_veraneante</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita (una opción)</t>
-        </is>
-      </c>
-      <c r="C109" s="11" t="inlineStr">
-        <is>
-          <t>escena resp_spencer_lynde_llanto, hito humillada</t>
-        </is>
-      </c>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr"/>
       <c r="D109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
-        </is>
-      </c>
-      <c r="B110" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_visita</t>
-        </is>
-      </c>
+          <t>lynde</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr"/>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>charla par:lynde+marilla:0, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua, hito humillada</t>
+          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr"/>
@@ -16855,13 +16843,17 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>marilla</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr"/>
+          <t>lynde_contenida</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_visita (una opción)</t>
+        </is>
+      </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza, escena geranio_sola</t>
+          <t>hito humillada</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr"/>
@@ -16869,31 +16861,35 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>marilla_doblo_ropa</t>
+          <t>lynde_llanto</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C112" s="11" t="inlineStr"/>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena lynde_visita (una opción)</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>escena resp_spencer_lynde_llanto, hito humillada</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>marilla_sabe_camison</t>
-        </is>
-      </c>
-      <c r="B113" s="11" t="inlineStr"/>
+          <t>lynde_visita</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_visita</t>
+        </is>
+      </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison_descalza</t>
+          <t>charla par:lynde+marilla:0, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua, hito humillada</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr"/>
@@ -16901,17 +16897,13 @@
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>matthew_en_estacion</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>marilla</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr"/>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>escena estacion</t>
+          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza, escena geranio_sola</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr"/>
@@ -16919,7 +16911,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>matthew_llego_casa</t>
+          <t>marilla_doblo_ropa</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -16927,23 +16919,23 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C115" s="11" t="inlineStr">
-        <is>
-          <t>escena tejas_verdes (alternativa)</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr"/>
+      <c r="C115" s="11" t="inlineStr"/>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>nombra_avenida</t>
+          <t>marilla_sabe_camison</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr"/>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>escena conv_matthew_nombres</t>
+          <t>escena marilla_sabe_camison_descalza</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr"/>
@@ -16951,7 +16943,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>nombre_propio_</t>
+          <t>matthew_en_estacion</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -16959,17 +16951,17 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C117" s="11" t="inlineStr"/>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>escena estacion</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>nombro_</t>
+          <t>matthew_llego_casa</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -16977,24 +16969,20 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr"/>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>escena tejas_verdes (alternativa)</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>nombro_avenida</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>escena nombra_avenida</t>
-        </is>
-      </c>
+          <t>nombra_avenida</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr"/>
       <c r="C119" s="11" t="inlineStr">
         <is>
           <t>escena conv_matthew_nombres</t>
@@ -17005,12 +16993,12 @@
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>nombro_burbuja</t>
+          <t>nombre_propio_</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr"/>
@@ -17023,12 +17011,12 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>nombro_cerezo</t>
+          <t>nombro_</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>escena primera_gwin</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr"/>
@@ -17041,17 +17029,17 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>nombro_geranio</t>
+          <t>nombro_avenida</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>escena primera_geranio, escena geranio_sola</t>
+          <t>escena nombra_avenida</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>escena geranio_sola</t>
+          <t>escena conv_matthew_nombres</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
@@ -17059,30 +17047,30 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>nombro_lago</t>
+          <t>nombro_burbuja</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>escena lago</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr">
-        <is>
-          <t>escena conv_matthew_nombres</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr"/>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr"/>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>nombro_senda</t>
+          <t>nombro_cerezo</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
+          <t>escena primera_gwin</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr"/>
@@ -17095,17 +17083,17 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>nombro_geranio</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita (una opción)</t>
+          <t>escena primera_geranio, escena geranio_sola</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua</t>
+          <t>escena geranio_sola</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr"/>
@@ -17113,17 +17101,17 @@
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>pastel_linimento</t>
+          <t>nombro_lago</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>escena pastel_linimento</t>
+          <t>escena lago</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>meta allan</t>
+          <t>escena conv_matthew_nombres</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr"/>
@@ -17131,35 +17119,35 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>perdon_pedido</t>
+          <t>nombro_senda</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_perdon_marilla</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_perdon_marilla</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr"/>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr"/>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>ofendio_lynde</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>escena crup_salva</t>
+          <t>escena lynde_visita (una opción)</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico, hito amistad_a_prueba</t>
+          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr"/>
@@ -17167,17 +17155,13 @@
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>pide_amiga</t>
-        </is>
-      </c>
-      <c r="B129" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>paces</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr"/>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena conv_gilbert_caramelo</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr"/>
@@ -17185,13 +17169,17 @@
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>primera_bed</t>
-        </is>
-      </c>
-      <c r="B130" s="11" t="inlineStr"/>
+          <t>pastel_linimento</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>escena pastel_linimento</t>
+        </is>
+      </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche_sube</t>
+          <t>meta allan</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr"/>
@@ -17199,17 +17187,17 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>primera_noche</t>
+          <t>perdon_pedido</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>escena inicio_llegada, escena primera_noche</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr"/>
@@ -17217,17 +17205,17 @@
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida</t>
+          <t>escena crup_salva</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida, escena crup_salva, escena cama_josephine, escena ventana_diana, escena banco_lago_diana, escena pupitre_diana, escena lugar_puente_diana, escena conv_marilla_diana, escena conv_diana_pelo, escena conv_diana_minnie, escena conv_diana_nombres, escena conv_diana_escuela, escena conv_diana_bosque, escena conv_diana_vestidos, escena conv_diana_club, escena conv_diana_gilbert, escena conv_diana_gilbert_contesta, escena conv_diana_tia, escena conv_diana_secreto, escena conv_diana_futuro, escena conv_diana_casarse, escena conv_diana_vela, escena conv_barry_diana, charla par:ana+diana+marilla:1, dichos de paseo_fin_tarde, dichos de paseo_fin, dichos de paseo_si, dichos de mira:diana:flores, dichos de mira:diana:lago, dichos de te_diana:primera, dichos de te_diana_otra_vez, dichos de te_diana_cordial, una frase de diana, una frase de barry, meta picnic, meta te_diana, meta josephine, meta club, meta remo, meta techo, código</t>
+          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico, hito amistad_a_prueba</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr"/>
@@ -17235,17 +17223,17 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>queens</t>
+          <t>pide_amiga</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera, escena examen_entra</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_queens, escena faro_queens, charla par:ana+gilbert:1</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr"/>
@@ -17253,35 +17241,31 @@
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>queens_primera</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>escena examen_primera</t>
-        </is>
-      </c>
-      <c r="C134" s="11" t="inlineStr"/>
-      <c r="D134" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>primera_bed</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr"/>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>escena primera_noche_sube</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>quiere_amiga</t>
+          <t>primera_noche</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>escena quiere_amiga</t>
+          <t>escena inicio_llegada, escena primera_noche</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>escena aviso_barry, escena barry_recibe, meta conocer_diana (pista)</t>
+          <t>escena primera_noche</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr"/>
@@ -17289,17 +17273,17 @@
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>rachel_en_casa_bell</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena prohibida</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_bell</t>
+          <t>escena prohibida, escena crup_salva, escena cama_josephine, escena ventana_diana, escena banco_lago_diana, escena pupitre_diana, escena lugar_puente_diana, escena conv_marilla_diana, escena conv_diana_pelo, escena conv_diana_minnie, escena conv_diana_nombres, escena conv_diana_escuela, escena conv_diana_bosque, escena conv_diana_vestidos, escena conv_diana_club, escena conv_diana_gilbert, escena conv_diana_gilbert_contesta, escena conv_diana_tia, escena conv_diana_secreto, escena conv_diana_futuro, escena conv_diana_casarse, escena conv_diana_vela, escena conv_barry_diana, charla par:ana+diana+marilla:1, dichos de paseo_fin_tarde, dichos de paseo_fin, dichos de paseo_si, dichos de mira:diana:flores, dichos de mira:diana:lago, dichos de te_diana:primera, dichos de te_diana_otra_vez, dichos de te_diana_cordial, una frase de diana, una frase de barry, meta picnic, meta te_diana, meta josephine, meta club, meta remo, meta techo, código</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr"/>
@@ -17307,17 +17291,17 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>rachel_llego_tejas_verdes</t>
+          <t>queens</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena examen_primera, escena examen_entra</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
+          <t>escena ventana_queens, escena faro_queens, charla par:ana+gilbert:1</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr"/>
@@ -17325,35 +17309,35 @@
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>rachel_lo_sabe</t>
+          <t>queens_primera</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
-        </is>
-      </c>
-      <c r="C138" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr"/>
+          <t>escena examen_primera</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr"/>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>regado</t>
+          <t>quiere_amiga</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena quiere_amiga</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla</t>
+          <t>escena aviso_barry, escena barry_recibe, meta conocer_diana (pista)</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr"/>
@@ -17361,7 +17345,7 @@
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>ropa_arrugada</t>
+          <t>rachel_en_casa_bell</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -17371,7 +17355,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla</t>
+          <t>escena rachel_bell</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr"/>
@@ -17379,7 +17363,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>ropa_ordenada</t>
+          <t>rachel_llego_tejas_verdes</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -17389,7 +17373,7 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla, código</t>
+          <t>escena rachel_marilla</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr"/>
@@ -17397,17 +17381,17 @@
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>ropa_tirada_otra</t>
+          <t>rachel_lo_sabe</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
+          <t>escena rachel_marilla</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
           <t>código</t>
-        </is>
-      </c>
-      <c r="C142" s="11" t="inlineStr">
-        <is>
-          <t>escena falta_ropa (una opción), código</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr"/>
@@ -17415,7 +17399,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>se_fue_</t>
+          <t>regado</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -17423,37 +17407,45 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C143" s="11" t="inlineStr"/>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>una frase de marilla</t>
+        </is>
+      </c>
       <c r="D143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>se_fue_buhonero</t>
+          <t>ropa_arrugada</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
-        </is>
-      </c>
-      <c r="C144" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>una frase de marilla</t>
+        </is>
+      </c>
       <c r="D144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>se_fue_josephine</t>
+          <t>ropa_ordenada</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>llegadas de allan, llegadas de sraallan</t>
+          <t>una frase de marilla, código</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr"/>
@@ -17461,17 +17453,17 @@
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>se_fue_phillips</t>
+          <t>ropa_tirada_otra</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
+          <t>escena falta_ropa (una opción), código</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr"/>
@@ -17479,12 +17471,12 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>se_fue_prissy</t>
+          <t>se_fue_</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
@@ -17493,7 +17485,7 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>se_fue_veraneante</t>
+          <t>se_fue_buhonero</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
@@ -17507,17 +17499,17 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>se_fue_josephine</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>escena se_queda</t>
+          <t>llegadas</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>escena carta_spencer_1, escena resp_spencer_prueba_quedo, escena resp_spencer_conocidas_diana, escena resp_spencer_zanahorias_pizarra, escena resp_spencer_zanahorias_contesta, escena resp_spencer_zanahorias_ignora, escena resp_spencer_ofendio_lynde, escena resp_spencer_lynde_llanto, escena resp_spencer_prohibida, escena resp_spencer_1, escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, escena conv_marilla_por_que, un comentario de espejo, charla par:ana+matthew:2, charla par:lynde+marilla:0, charla par:marilla+matthew:1, charla par:marilla+matthew:2, charla par:ana+marilla+matthew:0, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana, hito decision</t>
+          <t>llegadas de allan, llegadas de sraallan</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr"/>
@@ -17525,13 +17517,17 @@
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>undefined</t>
-        </is>
-      </c>
-      <c r="B150" s="11" t="inlineStr"/>
+          <t>se_fue_phillips</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche, un comentario de sueno_1, un comentario de sueno_2</t>
+          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr"/>
@@ -17539,45 +17535,45 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>verano</t>
-        </is>
-      </c>
-      <c r="B151" s="11" t="inlineStr"/>
-      <c r="C151" s="11" t="inlineStr">
-        <is>
-          <t>charla par:ana+diana:5, una frase de phillips</t>
-        </is>
-      </c>
+          <t>se_fue_prissy</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B152" s="11" t="inlineStr"/>
-      <c r="C152" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>se_fue_veraneante</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr"/>
       <c r="D152" s="8" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>zanahorias</t>
+          <t>se_queda</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>escena zanahorias</t>
+          <t>escena se_queda</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, un comentario de pupitre, un comentario de pizarra, charla par:ana+gilbert:0, una frase de gilbert, meta paces, hito rival</t>
+          <t>escena carta_spencer_1, escena resp_spencer_prueba_quedo, escena resp_spencer_conocidas_diana, escena resp_spencer_zanahorias_pizarra, escena resp_spencer_zanahorias_contesta, escena resp_spencer_zanahorias_ignora, escena resp_spencer_ofendio_lynde, escena resp_spencer_lynde_llanto, escena resp_spencer_prohibida, escena resp_spencer_1, escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, escena conv_marilla_por_que, un comentario de espejo, charla par:ana+matthew:2, charla par:lynde+marilla:0, charla par:marilla+matthew:1, charla par:marilla+matthew:2, charla par:ana+marilla+matthew:0, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana, hito decision</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr"/>
@@ -17585,17 +17581,13 @@
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>zanahorias_contesta</t>
-        </is>
-      </c>
-      <c r="B154" s="11" t="inlineStr">
-        <is>
-          <t>escena zanahorias (una opción)</t>
-        </is>
-      </c>
+          <t>undefined</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr"/>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_gilbert</t>
+          <t>escena primera_noche, un comentario de sueno_1, un comentario de sueno_2</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr"/>
@@ -17603,17 +17595,13 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>zanahorias_ignora</t>
-        </is>
-      </c>
-      <c r="B155" s="11" t="inlineStr">
-        <is>
-          <t>escena zanahorias (una opción)</t>
-        </is>
-      </c>
+          <t>verano</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr"/>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>escena resp_spencer_zanahorias_ignora, hito rival</t>
+          <t>charla par:ana+diana:5, una frase de phillips</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr"/>
@@ -17621,17 +17609,13 @@
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>zanahorias_pizarra</t>
-        </is>
-      </c>
-      <c r="B156" s="11" t="inlineStr">
-        <is>
-          <t>escena zanahorias (una opción)</t>
-        </is>
-      </c>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr"/>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>escena resp_spencer_zanahorias_pizarra, hito rival</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr"/>
@@ -17639,21 +17623,93 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, escena conv_gilbert_caramelo, un comentario de pupitre, un comentario de pizarra, charla par:ana+gilbert:0, una frase de gilbert, meta paces, hito rival</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>zanahorias_contesta</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias (una opción)</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>escena conv_diana_gilbert</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>zanahorias_ignora</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias (una opción)</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>escena resp_spencer_zanahorias_ignora, hito rival</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>zanahorias_pizarra</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias (una opción)</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>escena resp_spencer_zanahorias_pizarra, hito rival</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
           <t>{k}</t>
         </is>
       </c>
-      <c r="B157" s="11" t="inlineStr"/>
-      <c r="C157" s="11" t="inlineStr">
+      <c r="B161" s="11" t="inlineStr"/>
+      <c r="C161" s="11" t="inlineStr">
         <is>
           <t>una frase de niños</t>
         </is>
       </c>
-      <c r="D157" s="8" t="inlineStr"/>
+      <c r="D161" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <autoFilter ref="A1:D157"/>
-  <conditionalFormatting sqref="D2:D157">
+  <autoFilter ref="A1:D161"/>
+  <conditionalFormatting sqref="D2:D161">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(D2,5)="nunca"</formula>
     </cfRule>
@@ -36013,7 +36069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36517,22 +36573,22 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Llegadas</t>
+          <t>Frases</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Gilbert Blythe llega</t>
+          <t>la Sra. Barry</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota (solo queda en el diario)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_gilbert: …» o una escena «si: hecho:llego_gilbert»</t>
+          <t>frases para esos momentos (hoja «Huecos»)</t>
         </is>
       </c>
     </row>
@@ -36549,12 +36605,12 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Barry</t>
+          <t>Gertie Pye</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -36576,7 +36632,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Gertie Pye</t>
+          <t>Jane Andrews</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -36603,12 +36659,12 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Jane Andrews</t>
+          <t>Charlie Sloane</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla)</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -36630,12 +36686,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Charlie Sloane</t>
+          <t>Cecily King</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -36657,12 +36713,12 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Cecily King</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -36684,7 +36740,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>Minnie May Barry</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -36711,12 +36767,12 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Minnie May Barry</t>
+          <t>Carrie Sloane</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 4 (sin conocerla), Día 16 (sin conocerla), Día 20 (sin conocerla), Día 33 (sin conocerla), Día 45 (sin conocerla)…</t>
+          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -36738,12 +36794,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
+          <t>la Srta. Josephine Barry</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 2 (sin conocerla), Día 2 (conociéndola), Día 4 (sin conocerla), Día 4 (conociéndola), Día 16 (sin conocerla), Día 16 (conociéndola)…</t>
+          <t>no tiene qué decir: Día 45 (sin conocerla), Día 45 (conociéndola)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -36760,22 +36816,22 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Frases</t>
+          <t>Metas</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>la Srta. Josephine Barry</t>
+          <t>«perdon_barry»</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>no tiene qué decir: Día 45 (sin conocerla), Día 45 (conociéndola)</t>
+          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>frases para esos momentos (hoja «Huecos»)</t>
+          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
         </is>
       </c>
     </row>
@@ -36792,7 +36848,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>«perdon_barry»</t>
+          <t>«carta»</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -36819,7 +36875,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>«carta»</t>
+          <t>«sala»</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -36846,7 +36902,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>«sala»</t>
+          <t>«sombrero»</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -36873,7 +36929,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>«sombrero»</t>
+          <t>«tinte»</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -36900,7 +36956,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>«tinte»</t>
+          <t>«pelo_corto»</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -36927,7 +36983,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>«pelo_corto»</t>
+          <t>«techo»</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -36944,27 +37000,27 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baja</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Metas</t>
+          <t>Situaciones</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>«techo»</t>
+          <t>Ana de noche en Tejas Verdes</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>nadie le sugiere a Ana hacerla (sin guiño)</t>
+          <t>nadie reacciona, en ningún momento (estaban: Marilla, Matthew, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>«guiño quien: …» en src/datos/cuaderno.txt</t>
+          <t>una escena de noche (hora:21-26) con quien esté</t>
         </is>
       </c>
     </row>
@@ -36981,12 +37037,12 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en Tejas Verdes</t>
+          <t>Ana de noche en La Cuesta del Huerto</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: Marilla, Matthew, la Sra. Lynde)</t>
+          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -37008,12 +37064,12 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en La Cuesta del Huerto</t>
+          <t>Ana de noche en la Hondonada (Sra. Lynde)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: Mary Joe, el Sr. Barry, la Sra. Barry)</t>
+          <t>nadie reacciona, en ningún momento (estaban: Thomas Lynde, la Sra. Lynde)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -37035,12 +37091,12 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la Hondonada (Sra. Lynde)</t>
+          <t>Ana de noche en la casa del Sr. Harrison</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: Thomas Lynde, la Sra. Lynde)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -37062,12 +37118,12 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la casa del Sr. Harrison</t>
+          <t>Ana de noche en la tienda de Lawson</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -37089,12 +37145,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la tienda de Lawson</t>
+          <t>Ana de noche en la escuela</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Lawson, la Sra. Pye)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -37116,12 +37172,12 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la escuela</t>
+          <t>Ana de noche en la iglesia</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Phillips, la Srta. Stacy)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Bell, el reverendo Allan, la Sra. Allan, la Sra. Lynde, la Sra. Pye)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -37143,12 +37199,12 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la iglesia</t>
+          <t>Ana de noche en la casa parroquial</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Bell, el reverendo Allan, la Sra. Allan, la Sra. Lynde, la Sra. Pye)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -37170,12 +37226,12 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la casa parroquial</t>
+          <t>Ana de noche en la aldea (afuera)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el reverendo Allan, la Sra. Allan)</t>
+          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison, el Sr. Lawson, la Sra. Barry, la Sra. Lynde, la Sra. Pye, v0)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -37197,17 +37253,17 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Ana de noche en la aldea (afuera)</t>
+          <t>Ana en camisón: ella misma no lo nota</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona, en ningún momento (estaban: el Sr. Harrison, el Sr. Lawson, la Sra. Barry, la Sra. Lynde, la Sra. Pye, v0)</t>
+          <t>en Tejas Verdes, La Cuesta del Huerto, la Hondonada (Sra. Lynde), la casa del Sr. Harrison, la tienda de Lawson, la escuela, la iglesia, la casa parroquial, la aldea (afuera)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>una escena de noche (hora:21-26) con quien esté</t>
+          <t>un comentario de Ana con «si: ana:camison»</t>
         </is>
       </c>
     </row>
@@ -37224,7 +37280,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Ana en camisón: ella misma no lo nota</t>
+          <t>Ana sin sombrero: ella misma no lo nota</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -37234,7 +37290,7 @@
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>un comentario de Ana con «si: ana:camison»</t>
+          <t>un comentario de Ana con «si: ana:sin_sombrero»</t>
         </is>
       </c>
     </row>
@@ -37246,22 +37302,22 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Situaciones</t>
+          <t>Exploración</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Ana sin sombrero: ella misma no lo nota</t>
+          <t>70 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>en Tejas Verdes, La Cuesta del Huerto, la Hondonada (Sra. Lynde), la casa del Sr. Harrison, la tienda de Lawson, la escuela, la iglesia, la casa parroquial, la aldea (afuera)</t>
+          <t>les falta: Ana no va en la calesa por el camino</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>un comentario de Ana con «si: ana:sin_sombrero»</t>
+          <t>ej.: avenida, newbridge, avenida_petalos, avenida_paso</t>
         </is>
       </c>
     </row>
@@ -37278,17 +37334,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>70 escena(s) que no pasaron en 4 días</t>
+          <t>56 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>les falta: Ana no va en la calesa por el camino</t>
+          <t>les falta: podía pasar (no tocó)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>ej.: avenida, newbridge, avenida_petalos, avenida_paso</t>
+          <t>ej.: primera_gwin, primera_mirror, primera_armario, primera_stairs</t>
         </is>
       </c>
     </row>
@@ -37305,17 +37361,17 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>56 escena(s) que no pasaron en 4 días</t>
+          <t>38 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>les falta: podía pasar (no tocó)</t>
+          <t>les falta: cuando se encuentran</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>ej.: primera_gwin, primera_mirror, primera_armario, primera_stairs</t>
+          <t>ej.: diana_por_casualidad, par:ana+diana:0, par:ana+diana:1, par:ana+diana:2</t>
         </is>
       </c>
     </row>
@@ -37332,17 +37388,17 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>38 escena(s) que no pasaron en 4 días</t>
+          <t>19 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando se encuentran</t>
+          <t>les falta: cuando Ana usa gwin</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>ej.: diana_por_casualidad, par:ana+diana:0, par:ana+diana:1, par:ana+diana:2</t>
+          <t>ej.: ventana_primavera_manana, ventana_primavera_tarde, ventana_verano_manana, ventana_verano_noche</t>
         </is>
       </c>
     </row>
@@ -37359,17 +37415,17 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>19 escena(s) que no pasaron en 4 días</t>
+          <t>13 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana usa gwin</t>
+          <t>les falta: cuando Ana conversa con diana</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>ej.: ventana_primavera_manana, ventana_primavera_tarde, ventana_verano_manana, ventana_verano_noche</t>
+          <t>ej.: conv_diana_pelo, conv_diana_minnie, conv_diana_nombres, conv_diana_escuela</t>
         </is>
       </c>
     </row>
@@ -37386,17 +37442,17 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>13 escena(s) que no pasaron en 4 días</t>
+          <t>8 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana conversa con diana</t>
+          <t>les falta: ana no está en gg</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>ej.: conv_diana_pelo, conv_diana_minnie, conv_diana_nombres, conv_diana_escuela</t>
+          <t>ej.: quiere_amiga, broche, prohibida, invita_allan</t>
         </is>
       </c>
     </row>
@@ -37413,17 +37469,17 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>8 escena(s) que no pasaron en 4 días</t>
+          <t>7 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>les falta: ana no está en gg</t>
+          <t>les falta: cuando Ana conversa con marilla</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>ej.: quiere_amiga, broche, prohibida, invita_allan</t>
+          <t>ej.: conv_marilla_perdon, conv_marilla_cocina, conv_marilla_diana, conv_marilla_genio</t>
         </is>
       </c>
     </row>
@@ -37440,17 +37496,17 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>7 escena(s) que no pasaron en 4 días</t>
+          <t>6 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana conversa con marilla</t>
+          <t>les falta: cuando Ana usa mirror</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>ej.: conv_marilla_perdon, conv_marilla_cocina, conv_marilla_diana, conv_marilla_genio</t>
+          <t>ej.: espejo_pelo, espejo_cordelia, espejo_tejas_verdes, espejo_zanahorias</t>
         </is>
       </c>
     </row>
@@ -37467,17 +37523,17 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>6 escena(s) que no pasaron en 4 días</t>
+          <t>5 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana usa mirror</t>
+          <t>les falta: cuando Ana conversa con matthew</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>ej.: espejo_pelo, espejo_cordelia, espejo_tejas_verdes, espejo_zanahorias</t>
+          <t>ej.: conv_matthew_nombres, conv_matthew_mangas, conv_matthew_mujeres, conv_matthew_queens</t>
         </is>
       </c>
     </row>
@@ -37494,17 +37550,17 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>5 escena(s) que no pasaron en 4 días</t>
+          <t>4 escena(s) que no pasaron en 4 días</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana conversa con matthew</t>
+          <t>les falta: diana no está en Avonlea</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>ej.: conv_matthew_nombres, conv_matthew_mangas, conv_matthew_mujeres, conv_matthew_queens</t>
+          <t>ej.: conoce_diana, te_grosella, crup_aviso, cama_josephine</t>
         </is>
       </c>
     </row>
@@ -37526,12 +37582,12 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>les falta: diana no está en Avonlea</t>
+          <t>les falta: falta hecho:blewett_duda</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>ej.: conoce_diana, te_grosella, crup_aviso, cama_josephine</t>
+          <t>ej.: duda_matthew, duda_suplica, duda_calla, devuelta_blewett</t>
         </is>
       </c>
     </row>
@@ -37553,12 +37609,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>les falta: falta hecho:blewett_duda</t>
+          <t>les falta: cuando Ana usa faro</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>ej.: duda_matthew, duda_suplica, duda_calla, devuelta_blewett</t>
+          <t>ej.: faro_verano, faro_invierno, faro_manana, faro_queens</t>
         </is>
       </c>
     </row>
@@ -37570,22 +37626,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Exploración</t>
+          <t>Noticias</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>4 escena(s) que no pasaron en 4 días</t>
+          <t>«huerfano»: los Cuthbert van a traer un niño del orfanato</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>les falta: cuando Ana usa faro</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>ej.: faro_verano, faro_invierno, faro_manana, faro_queens</t>
+          <t>una escena o una frase con «sabe:quien:huerfano» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37602,7 +37658,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>«huerfano»: los Cuthbert van a traer un niño del orfanato</t>
+          <t>«cerdo_pye»: a los Pye se les escapó otra vez el cerdo</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -37612,7 +37668,7 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:huerfano» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:cerdo_pye» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37629,7 +37685,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>«cerdo_pye»: a los Pye se les escapó otra vez el cerdo</t>
+          <t>«maestra_plumas»: la maestra nueva usa sombrero con plumas</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -37639,7 +37695,7 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:cerdo_pye» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:maestra_plumas» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37656,7 +37712,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>«maestra_plumas»: la maestra nueva usa sombrero con plumas</t>
+          <t>«loro_harrison»: el loro del Sr. Harrison dice cosas terribles</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -37666,7 +37722,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:maestra_plumas» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:loro_harrison» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37683,7 +37739,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>«loro_harrison»: el loro del Sr. Harrison dice cosas terribles</t>
+          <t>«rastrillo_matthew»: Matthew Cuthbert compró un rastrillo en invierno</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -37693,7 +37749,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:loro_harrison» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:rastrillo_matthew» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37710,17 +37766,17 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>«rastrillo_matthew»: Matthew Cuthbert compró un rastrillo en invierno</t>
+          <t>«ana_lengua»</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>es de Ana y no tiene versión exagerada</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:rastrillo_matthew» (alguien que se entera y hace o dice algo)</t>
+          <t>una línea «exagerada:» (los chismosos la agrandan)</t>
         </is>
       </c>
     </row>
@@ -37737,17 +37793,17 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>«ana_lengua»</t>
+          <t>«pastor_nuevo»: llegó un pastor nuevo, el Sr. Allan, con su esposa</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>es de Ana y no tiene versión exagerada</t>
+          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>una línea «exagerada:» (los chismosos la agrandan)</t>
+          <t>una escena o una frase con «sabe:quien:pastor_nuevo» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37764,7 +37820,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>«pastor_nuevo»: llegó un pastor nuevo, el Sr. Allan, con su esposa</t>
+          <t>«tia_josephine»: la tía Josephine de los Barry vino de Charlottetown</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -37774,7 +37830,7 @@
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:pastor_nuevo» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:tia_josephine» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37791,7 +37847,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>«tia_josephine»: la tía Josephine de los Barry vino de Charlottetown</t>
+          <t>«se_va_phillips»: el Sr. Phillips se va de la escuela de Avonlea</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -37801,7 +37857,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:tia_josephine» (alguien que se entera y hace o dice algo)</t>
+          <t>una escena o una frase con «sabe:quien:se_va_phillips» (alguien que se entera y hace o dice algo)</t>
         </is>
       </c>
     </row>
@@ -37813,22 +37869,22 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Noticias</t>
+          <t>Llegadas</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>«se_va_phillips»: el Sr. Phillips se va de la escuela de Avonlea</t>
+          <t>Prissy Andrews se va</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>nadie reacciona a ella (solo se cuenta); es un chisme del pueblo: puede bastar</t>
+          <t>nadie lo nota</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>una escena o una frase con «sabe:quien:se_va_phillips» (alguien que se entera y hace o dice algo)</t>
+          <t>una noticia o una escena con «hecho:se_fue_prissy»</t>
         </is>
       </c>
     </row>
@@ -37845,17 +37901,17 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Prissy Andrews se va</t>
+          <t>el buhonero llega (de visita)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota</t>
+          <t>nadie lo nota (solo queda en el diario)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>una noticia o una escena con «hecho:se_fue_prissy»</t>
+          <t>una noticia «saben si hecho:llego_buhonero: …» o una escena «si: hecho:llego_buhonero»</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37928,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>el buhonero llega (de visita)</t>
+          <t>una veraneante del hotel llega (de visita)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -37882,7 +37938,7 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_buhonero: …» o una escena «si: hecho:llego_buhonero»</t>
+          <t>una noticia «saben si hecho:llego_veraneante: …» o una escena «si: hecho:llego_veraneante»</t>
         </is>
       </c>
     </row>
@@ -37894,22 +37950,22 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Llegadas</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>una veraneante del hotel llega (de visita)</t>
+          <t>Presentación propia (cómo se presenta la primera vez)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>nadie lo nota (solo queda en el diario)</t>
+          <t>32 usan la de siempre: Diana, el Sr. Shearer, el buhonero, el Sr. Phillips, el reverendo Allan, la Sra. Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King, Jasper Dale, Alec King, Janet King…</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>una noticia «saben si hecho:llego_veraneante: …» o una escena «si: hecho:llego_veraneante»</t>
+          <t>«presentacion» en personajes.json, o «presenta» en src/js/56-gente-de-avonlea.js, con su voz</t>
         </is>
       </c>
     </row>
@@ -37926,17 +37982,17 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Presentación propia (cómo se presenta la primera vez)</t>
+          <t>el buhonero</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>32 usan la de siempre: Diana, el Sr. Shearer, el buhonero, el Sr. Phillips, el reverendo Allan, la Sra. Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King, Jasper Dale, Alec King, Janet King…</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>«presentacion» en personajes.json, o «presenta» en src/js/56-gente-de-avonlea.js, con su voz</t>
+          <t>unas frases más en la hoja «Frases»</t>
         </is>
       </c>
     </row>
@@ -37953,7 +38009,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>el buhonero</t>
+          <t>Jane Andrews</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -37980,7 +38036,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Jane Andrews</t>
+          <t>Prissy Andrews</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -38007,7 +38063,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Prissy Andrews</t>
+          <t>Charlie Sloane</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -38034,7 +38090,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Charlie Sloane</t>
+          <t>Moody Spurgeon</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
@@ -38061,7 +38117,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Moody Spurgeon</t>
+          <t>Tillie Boulter</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
@@ -38088,7 +38144,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Tillie Boulter</t>
+          <t>Felicity King</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
@@ -38115,7 +38171,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Felicity King</t>
+          <t>Felix King</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -38142,7 +38198,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Felix King</t>
+          <t>Cecily King</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
@@ -38169,7 +38225,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Cecily King</t>
+          <t>Sara Stanley</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -38196,7 +38252,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Sara Stanley</t>
+          <t>el Sr. Lawson</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -38223,7 +38279,7 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Lawson</t>
+          <t>el herrero</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -38250,7 +38306,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>el herrero</t>
+          <t>el editor de La Crónica</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -38277,7 +38333,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>el editor de La Crónica</t>
+          <t>la Srta. Hetty King</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -38304,7 +38360,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>la Srta. Hetty King</t>
+          <t>Olivia King</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
@@ -38331,7 +38387,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Olivia King</t>
+          <t>Jasper Dale</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
@@ -38358,7 +38414,7 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Jasper Dale</t>
+          <t>Alec King</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
@@ -38385,7 +38441,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Alec King</t>
+          <t>Janet King</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
@@ -38412,7 +38468,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Janet King</t>
+          <t>la Sra. Pye</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -38439,12 +38495,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Pye</t>
+          <t>el Sr. Sloane</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>tiene 1 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -38466,7 +38522,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Sloane</t>
+          <t>el Sr. Andrews</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -38493,12 +38549,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Andrews</t>
+          <t>Peg Bowen</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -38520,7 +38576,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Peg Bowen</t>
+          <t>el Sr. Barry</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -38547,7 +38603,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Barry</t>
+          <t>Mary Joe</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
@@ -38574,7 +38630,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Mary Joe</t>
+          <t>Jerry Buote</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -38601,7 +38657,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Jerry Buote</t>
+          <t>el médico</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -38628,7 +38684,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>el médico</t>
+          <t>el Sr. Bell</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -38655,7 +38711,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>el Sr. Bell</t>
+          <t>la Sra. Spencer</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -38682,7 +38738,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Spencer</t>
+          <t>la Sra. Blewett</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -38709,7 +38765,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>la Sra. Blewett</t>
+          <t>Carrie Sloane</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
@@ -38736,7 +38792,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Carrie Sloane</t>
+          <t>el jefe de estación</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -38763,12 +38819,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>el jefe de estación</t>
+          <t>Thomas Lynde</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>tiene 1 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -38790,12 +38846,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Thomas Lynde</t>
+          <t>una veraneante del hotel</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>tiene 2 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -38817,12 +38873,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>una veraneante del hotel</t>
+          <t>un pescador</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>tiene 2 frase(s) suelta(s)</t>
+          <t>tiene 1 frase(s) suelta(s)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -38844,17 +38900,17 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>un pescador</t>
+          <t>Sin ninguna escena</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>tiene 1 frase(s) suelta(s)</t>
+          <t>36 de la gente del pueblo solo tienen frases sueltas: el buhonero, Gertie Pye, Prissy Andrews, Charlie Sloane, Moody Spurgeon, Tillie Boulter, Felicity King, Felix King, Cecily King, Sara Stanley, el reverendo Allan, el Sr. Lawson, el herrero, el editor de La Crónica, la Srta. Hetty King, Olivia King…</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>unas frases más en la hoja «Frases»</t>
+          <t>una escena pequeña para los que importan en el libro</t>
         </is>
       </c>
     </row>
@@ -38866,22 +38922,22 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Hechos</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Sin ninguna escena</t>
+          <t>«ana_admite_gilbert»</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>40 de la gente del pueblo solo tienen frases sueltas: el buhonero, Josie Pye, Gertie Pye, Ruby Gillis, Jane Andrews, Prissy Andrews, Charlie Sloane, Moody Spurgeon, Tillie Boulter, Felicity King, Felix King, Cecily King, Sara Stanley, el reverendo Allan, el Sr. Lawson, el herrero…</t>
+          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>una escena pequeña para los que importan en el libro</t>
+          <t>una escena, una frase o una noticia que lo recuerde</t>
         </is>
       </c>
     </row>
@@ -38898,7 +38954,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>«ana_admite_gilbert»</t>
+          <t>«blewett_orgullo»</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
@@ -38925,7 +38981,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>«blewett_orgullo»</t>
+          <t>«marilla_doblo_ropa»</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
@@ -38952,7 +39008,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>«marilla_doblo_ropa»</t>
+          <t>«queens_primera»</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
@@ -38966,36 +39022,9 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Hechos</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>«queens_primera»</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr">
-        <is>
-          <t>se deja y nadie lo lee: algo pasó y no tiene consecuencias</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>una escena, una frase o una noticia que lo recuerde</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E110"/>
-  <conditionalFormatting sqref="A2:A110">
+  <autoFilter ref="A1:E109"/>
+  <conditionalFormatting sqref="A2:A109">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>A2="alta"</formula>
     </cfRule>
@@ -49492,7 +49521,7 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>hora:9.2-12, no_hoy:clase</t>
+          <t>hora:9.2-12, no_hoy:clase, hecho:llego_stacy</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
@@ -49551,7 +49580,7 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>hora:9.2-12, no_hoy:clase</t>
+          <t>hora:9.2-12, no_hoy:clase, hecho:llego_stacy</t>
         </is>
       </c>
       <c r="I62" s="9" t="inlineStr">

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -23,14 +23,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frases'!$A$1:$J$2000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modelo'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$E$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Personas'!$A$1:$H$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Escenas'!$A$1:$Q$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Noticias'!$A$1:$K$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Llegadas'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Diálogos'!$A$1:$C$828</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Hechos'!$A$1:$D$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-19 12:50 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-19 21:29 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C483" s="11" t="inlineStr">
         <is>
-          <t>Perdón, Marilla. Se me olvidó por completo: estaba ocupadísima imaginando.</t>
+          <t>Perdón, Marilla. Ahora mismo me visto. Se me olvidó por completo: estaba ocupadísima imaginando.</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15811,17 +15811,13 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>diana_borracha</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>escena te_grosella</t>
-        </is>
-      </c>
+          <t>diana</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida, meta perdon_barry, hito amistad_a_prueba</t>
+          <t>meta conocer_diana (pista)</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -15829,17 +15825,17 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>disculpa_lynde</t>
+          <t>diana_borracha</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_disculpa</t>
+          <t>escena te_grosella</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>hito humillada, hito pedir_perdon</t>
+          <t>escena prohibida, meta perdon_barry, hito amistad_a_prueba</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
@@ -15847,13 +15843,17 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr"/>
+          <t>disculpa_lynde</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_disculpa</t>
+        </is>
+      </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>una frase de gertie</t>
+          <t>hito humillada, hito pedir_perdon</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr"/>
@@ -15861,17 +15861,13 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>examen</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>escena examen_primera, escena examen_entra, escena examen_no</t>
-        </is>
-      </c>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr"/>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>meta queens (pista)</t>
+          <t>una frase de gertie</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
@@ -15879,17 +15875,17 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>historia_</t>
+          <t>examen</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena examen_primera, escena examen_entra, escena examen_no</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>meta queens (pista)</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
@@ -15897,21 +15893,25 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>historia_a_prueba</t>
+          <t>historia_</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>hitos</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="D46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>historia_a_prueba_cerrado</t>
+          <t>historia_a_prueba</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -15925,7 +15925,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma</t>
+          <t>historia_a_prueba_cerrado</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -15939,7 +15939,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_cerrado</t>
+          <t>historia_amiga_del_alma</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -15953,7 +15953,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_juran</t>
+          <t>historia_amiga_del_alma_cerrado</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -15967,7 +15967,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_no_juran</t>
+          <t>historia_amiga_del_alma_juran</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -15981,7 +15981,7 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba</t>
+          <t>historia_amiga_del_alma_no_juran</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -15995,7 +15995,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba_cerrado</t>
+          <t>historia_amistad_a_prueba</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -16009,7 +16009,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba_la_recupera</t>
+          <t>historia_amistad_a_prueba_cerrado</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -16023,7 +16023,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla</t>
+          <t>historia_amistad_a_prueba_la_recupera</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -16037,7 +16037,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_cerrado</t>
+          <t>historia_confianza_marilla</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -16051,7 +16051,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_confiesa_en_falso</t>
+          <t>historia_confianza_marilla_cerrado</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -16065,7 +16065,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_dice_la_verdad</t>
+          <t>historia_confianza_marilla_confiesa_en_falso</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -16079,7 +16079,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>historia_decision</t>
+          <t>historia_confianza_marilla_dice_la_verdad</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -16093,7 +16093,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>historia_decision_cerrado</t>
+          <t>historia_decision</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -16107,7 +16107,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>historia_decision_devuelta</t>
+          <t>historia_decision_cerrado</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -16121,7 +16121,7 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>historia_decision_se_queda</t>
+          <t>historia_decision_devuelta</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -16135,7 +16135,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada</t>
+          <t>historia_decision_se_queda</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -16149,7 +16149,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_cerrado</t>
+          <t>historia_humillada</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -16163,7 +16163,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_estalla</t>
+          <t>historia_humillada_cerrado</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -16177,7 +16177,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_llora</t>
+          <t>historia_humillada_estalla</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -16191,7 +16191,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>historia_humillada_se_contiene</t>
+          <t>historia_humillada_llora</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -16205,7 +16205,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>historia_llegada</t>
+          <t>historia_humillada_se_contiene</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -16219,7 +16219,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>historia_llegada_cerrado</t>
+          <t>historia_llegada</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -16233,7 +16233,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>historia_matthew_aliado</t>
+          <t>historia_llegada_cerrado</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -16247,7 +16247,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>historia_matthew_aliado_cerrado</t>
+          <t>historia_matthew_aliado</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -16261,7 +16261,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon</t>
+          <t>historia_matthew_aliado_cerrado</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -16275,7 +16275,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon_a_lo_grande</t>
+          <t>historia_pedir_perdon</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -16289,7 +16289,7 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon_cerrado</t>
+          <t>historia_pedir_perdon_a_lo_grande</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -16303,7 +16303,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>historia_rival</t>
+          <t>historia_pedir_perdon_cerrado</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -16317,7 +16317,7 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_cerrado</t>
+          <t>historia_rival</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -16331,7 +16331,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_le_contesta</t>
+          <t>historia_rival_cerrado</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -16345,7 +16345,7 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_lo_ignora</t>
+          <t>historia_rival_le_contesta</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -16359,7 +16359,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>historia_rival_pizarra</t>
+          <t>historia_rival_lo_ignora</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -16373,7 +16373,7 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>historia_sombrero_iglesia</t>
+          <t>historia_rival_pizarra</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -16387,7 +16387,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>historia_sombrero_iglesia_cerrado</t>
+          <t>historia_sombrero_iglesia</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
@@ -16401,12 +16401,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_20</t>
+          <t>historia_sombrero_iglesia_cerrado</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>habilidad estudio</t>
+          <t>hitos</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr"/>
@@ -16415,7 +16415,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_50</t>
+          <t>hito_estudio_20</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
@@ -16429,7 +16429,7 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>hito_estudio_85</t>
+          <t>hito_estudio_50</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
@@ -16443,12 +16443,12 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_10</t>
+          <t>hito_estudio_85</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>habilidad granja</t>
+          <t>habilidad estudio</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr"/>
@@ -16457,7 +16457,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_40</t>
+          <t>hito_granja_10</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
@@ -16471,7 +16471,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>hito_granja_80</t>
+          <t>hito_granja_40</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
@@ -16485,12 +16485,12 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_10</t>
+          <t>hito_granja_80</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>habilidad letras</t>
+          <t>habilidad granja</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr"/>
@@ -16499,7 +16499,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_30</t>
+          <t>hito_letras_10</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -16513,7 +16513,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>hito_letras_60</t>
+          <t>hito_letras_30</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -16527,12 +16527,12 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_cocina_2</t>
+          <t>hito_letras_60</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>habilidad mano_cocina</t>
+          <t>habilidad letras</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr"/>
@@ -16541,7 +16541,7 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_cocina_7</t>
+          <t>hito_mano_cocina_2</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -16555,12 +16555,12 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_leche_3</t>
+          <t>hito_mano_cocina_7</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>habilidad mano_leche</t>
+          <t>habilidad mano_cocina</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr"/>
@@ -16569,7 +16569,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>hito_mano_leche_7</t>
+          <t>hito_mano_leche_3</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -16583,12 +16583,12 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>hito_paciencia_4</t>
+          <t>hito_mano_leche_7</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>habilidad paciencia</t>
+          <t>habilidad mano_leche</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr"/>
@@ -16597,31 +16597,31 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>inicio_juego</t>
+          <t>hito_paciencia_4</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>habilidad paciencia</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr"/>
       <c r="D96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>invierno</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr"/>
+          <t>inicio_juego</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild, escena conv_matthew_huerta</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr"/>
@@ -16629,17 +16629,13 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>llamada_almuerzo</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
-        </is>
-      </c>
+          <t>invierno</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr"/>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
+          <t>escena banco_lago_atardecer, escena lugar_bosque_manana, escena lugar_puente, escena lugar_lago_niebla, escena lugar_campo_rosado, escena lugar_playa, escena lugar_rio_escuela, escena lugar_granero, escena lugar_iglesia, escena lugar_corral_idlewild, escena conv_matthew_huerta</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr"/>
@@ -16647,17 +16643,17 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>llegada_tv</t>
+          <t>llamada_almuerzo</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>escena llegada, escena inicio_llegada</t>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche, escena desayuno_prueba, escena lugar_aldea, una frase de lawson, una frase de vecino, llegadas de diana, hito llegada</t>
+          <t>escena llamar_almuerzo, escena llamar_almuerzo_afuera</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr"/>
@@ -16665,17 +16661,17 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>llegaron</t>
+          <t>llegada_tv</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena llegada, escena inicio_llegada</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>escena llegada</t>
+          <t>escena primera_noche, escena desayuno_prueba, escena lugar_aldea, una frase de lawson, una frase de vecino, llegadas de diana, hito llegada</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr"/>
@@ -16683,7 +16679,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>llego_</t>
+          <t>llegaron</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -16693,7 +16689,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena llegada</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr"/>
@@ -16701,17 +16697,17 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>llego_allan</t>
+          <t>llego_</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>noticia pastor_nuevo</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr"/>
@@ -16719,7 +16715,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>llego_buhonero</t>
+          <t>llego_allan</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -16727,13 +16723,17 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C103" s="11" t="inlineStr"/>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>noticia pastor_nuevo</t>
+        </is>
+      </c>
       <c r="D103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>llego_diana</t>
+          <t>llego_buhonero</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -16747,7 +16747,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>llego_gilbert</t>
+          <t>llego_diana</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -16755,17 +16755,13 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>charla par:ana+diana:5</t>
-        </is>
-      </c>
+      <c r="C105" s="11" t="inlineStr"/>
       <c r="D105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>llego_josephine</t>
+          <t>llego_gilbert</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -16775,7 +16771,7 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>llegadas de phillips</t>
+          <t>escena conv_diana_gilbert_contesta, escena conv_gilbert_caramelo, escena conv_gilbert_estudiar, charla par:ana+diana:5</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr"/>
@@ -16783,7 +16779,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>llego_sraallan</t>
+          <t>llego_josephine</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -16791,13 +16787,17 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C107" s="11" t="inlineStr"/>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>llegadas de phillips</t>
+        </is>
+      </c>
       <c r="D107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>llego_stacy</t>
+          <t>llego_sraallan</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -16805,17 +16805,13 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>charla par:lynde+marilla:3, una frase de carrie, noticia maestra_plumas</t>
-        </is>
-      </c>
+      <c r="C108" s="11" t="inlineStr"/>
       <c r="D108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>llego_veraneante</t>
+          <t>llego_stacy</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -16823,37 +16819,37 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C109" s="11" t="inlineStr"/>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>escena clase_composicion_stacy, escena clase_botanica_stacy, escena conv_stacy_queens, escena conv_stacy_escribir, charla par:lynde+marilla:3, una frase de carrie, noticia maestra_plumas</t>
+        </is>
+      </c>
       <c r="D109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>lynde</t>
-        </is>
-      </c>
-      <c r="B110" s="11" t="inlineStr"/>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
-        </is>
-      </c>
+          <t>llego_veraneante</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr"/>
       <c r="D110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>lynde_contenida</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_visita (una opción)</t>
-        </is>
-      </c>
+          <t>lynde</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr"/>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>hito humillada</t>
+          <t>escena lynde_se_entera, escena camison_lynde, una frase de lynde</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr"/>
@@ -16861,7 +16857,7 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>lynde_llanto</t>
+          <t>lynde_contenida</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -16871,7 +16867,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>escena resp_spencer_lynde_llanto, hito humillada</t>
+          <t>hito humillada</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr"/>
@@ -16879,17 +16875,17 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>lynde_llanto</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita</t>
+          <t>escena lynde_visita (una opción)</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>charla par:lynde+marilla:0, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua, hito humillada</t>
+          <t>escena resp_spencer_lynde_llanto, hito humillada</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr"/>
@@ -16897,13 +16893,17 @@
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>marilla</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr"/>
+          <t>lynde_visita</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_visita</t>
+        </is>
+      </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza, escena geranio_sola</t>
+          <t>charla par:lynde+marilla:0, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua, hito humillada</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr"/>
@@ -16911,49 +16911,45 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>marilla_doblo_ropa</t>
-        </is>
-      </c>
-      <c r="B115" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr"/>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>marilla</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr"/>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>escena marilla_sabe_camison, escena marilla_sabe_camison_descalza, escena geranio_sola</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>marilla_sabe_camison</t>
-        </is>
-      </c>
-      <c r="B116" s="11" t="inlineStr"/>
-      <c r="C116" s="11" t="inlineStr">
-        <is>
-          <t>escena marilla_sabe_camison_descalza</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr"/>
+          <t>marilla_doblo_ropa</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr"/>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>matthew_en_estacion</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
+          <t>marilla_sabe_camison</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr"/>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>escena estacion</t>
+          <t>escena marilla_sabe_camison_descalza</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr"/>
@@ -16961,7 +16957,7 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>matthew_llego_casa</t>
+          <t>matthew_en_estacion</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -16971,7 +16967,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>escena tejas_verdes (alternativa)</t>
+          <t>escena estacion</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr"/>
@@ -16979,13 +16975,17 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>nombra_avenida</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr"/>
+          <t>matthew_llego_casa</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>escena conv_matthew_nombres</t>
+          <t>escena tejas_verdes (alternativa)</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr"/>
@@ -16993,25 +16993,21 @@
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>nombre_propio_</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
-        </is>
-      </c>
-      <c r="C120" s="11" t="inlineStr"/>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>nombra_avenida</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr"/>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>escena conv_matthew_nombres</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>nombro_</t>
+          <t>nombre_propio_</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -17029,48 +17025,48 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>nombro_avenida</t>
+          <t>nombro_</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>escena nombra_avenida</t>
-        </is>
-      </c>
-      <c r="C122" s="11" t="inlineStr">
-        <is>
-          <t>escena conv_matthew_nombres</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr"/>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr"/>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>nombro_burbuja</t>
+          <t>nombro_avenida</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr"/>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena nombra_avenida</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>escena conv_matthew_nombres</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>nombro_cerezo</t>
+          <t>nombro_burbuja</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>escena primera_gwin</t>
+          <t>escena conv_diana_nombres</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr"/>
@@ -17083,35 +17079,35 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>nombro_geranio</t>
+          <t>nombro_cerezo</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>escena primera_geranio, escena geranio_sola</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr">
-        <is>
-          <t>escena geranio_sola</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr"/>
+          <t>escena primera_gwin</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr"/>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>nombro_lago</t>
+          <t>nombro_geranio</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>escena lago</t>
+          <t>escena primera_geranio, escena geranio_sola</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>escena conv_matthew_nombres</t>
+          <t>escena geranio_sola</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr"/>
@@ -17119,49 +17115,53 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>nombro_senda</t>
+          <t>nombro_lago</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_nombres</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr"/>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena lago</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>escena conv_matthew_nombres</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>nombro_senda</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_visita (una opción)</t>
-        </is>
-      </c>
-      <c r="C128" s="11" t="inlineStr">
-        <is>
-          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua</t>
-        </is>
-      </c>
-      <c r="D128" s="8" t="inlineStr"/>
+          <t>escena conv_diana_nombres</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr"/>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>paces</t>
-        </is>
-      </c>
-      <c r="B129" s="11" t="inlineStr"/>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>escena lynde_visita (una opción)</t>
+        </is>
+      </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>escena conv_gilbert_caramelo</t>
+          <t>escena lynde_disculpa, escena conv_lynde_ventana, escena conv_lynde_pelo, escena conv_lynde_queens, charla par:ana+lynde:0, charla par:ana+lynde:1, charla par:ana+lynde+marilla:0, una frase de lynde, noticia ana_lengua</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr"/>
@@ -17169,17 +17169,13 @@
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>pastel_linimento</t>
-        </is>
-      </c>
-      <c r="B130" s="11" t="inlineStr">
-        <is>
-          <t>escena pastel_linimento</t>
-        </is>
-      </c>
+          <t>paces</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr"/>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>meta allan</t>
+          <t>escena conv_gilbert_caramelo</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr"/>
@@ -17187,17 +17183,17 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>perdon_pedido</t>
+          <t>pastel_linimento</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_perdon_marilla</t>
+          <t>escena pastel_linimento</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>escena lynde_perdon_marilla</t>
+          <t>meta allan</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr"/>
@@ -17205,17 +17201,17 @@
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>perdon_pedido</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>escena crup_salva</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico, hito amistad_a_prueba</t>
+          <t>escena lynde_perdon_marilla</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr"/>
@@ -17223,17 +17219,17 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>pide_amiga</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena crup_salva</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena ventana_perdonada, escena conv_barry_cordial, una frase de barry, una frase de minnie, una frase de maryjoe, una frase de medico, hito amistad_a_prueba</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr"/>
@@ -17241,13 +17237,17 @@
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>primera_bed</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr"/>
+          <t>pide_amiga</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>código</t>
+        </is>
+      </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche_sube</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr"/>
@@ -17255,17 +17255,13 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>primera_noche</t>
-        </is>
-      </c>
-      <c r="B135" s="11" t="inlineStr">
-        <is>
-          <t>escena inicio_llegada, escena primera_noche</t>
-        </is>
-      </c>
+          <t>primera_bed</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr"/>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche</t>
+          <t>escena primera_noche_sube</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr"/>
@@ -17273,17 +17269,17 @@
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>primera_noche</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida</t>
+          <t>escena inicio_llegada, escena primera_noche</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>escena prohibida, escena crup_salva, escena cama_josephine, escena ventana_diana, escena banco_lago_diana, escena pupitre_diana, escena lugar_puente_diana, escena conv_marilla_diana, escena conv_diana_pelo, escena conv_diana_minnie, escena conv_diana_nombres, escena conv_diana_escuela, escena conv_diana_bosque, escena conv_diana_vestidos, escena conv_diana_club, escena conv_diana_gilbert, escena conv_diana_gilbert_contesta, escena conv_diana_tia, escena conv_diana_secreto, escena conv_diana_futuro, escena conv_diana_casarse, escena conv_diana_vela, escena conv_barry_diana, charla par:ana+diana+marilla:1, dichos de paseo_fin_tarde, dichos de paseo_fin, dichos de paseo_si, dichos de mira:diana:flores, dichos de mira:diana:lago, dichos de te_diana:primera, dichos de te_diana_otra_vez, dichos de te_diana_cordial, una frase de diana, una frase de barry, meta picnic, meta te_diana, meta josephine, meta club, meta remo, meta techo, código</t>
+          <t>escena primera_noche</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr"/>
@@ -17291,17 +17287,17 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>queens</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera, escena examen_entra</t>
+          <t>escena prohibida</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_queens, escena faro_queens, charla par:ana+gilbert:1</t>
+          <t>escena prohibida, escena crup_salva, escena cama_josephine, escena ventana_diana, escena banco_lago_diana, escena pupitre_diana, escena lugar_puente_diana, escena conv_marilla_diana, escena conv_diana_pelo, escena conv_diana_minnie, escena conv_diana_nombres, escena conv_diana_escuela, escena conv_diana_bosque, escena conv_diana_vestidos, escena conv_diana_club, escena conv_diana_gilbert, escena conv_diana_gilbert_contesta, escena conv_diana_tia, escena conv_diana_secreto, escena conv_diana_futuro, escena conv_diana_casarse, escena conv_diana_vela, escena conv_barry_diana, charla par:ana+diana+marilla:1, dichos de paseo_fin_tarde, dichos de paseo_fin, dichos de paseo_si, dichos de mira:diana:flores, dichos de mira:diana:lago, dichos de te_diana:primera, dichos de te_diana_otra_vez, dichos de te_diana_cordial, una frase de diana, una frase de barry, meta picnic, meta te_diana, meta josephine, meta club, meta remo, meta techo, código</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr"/>
@@ -17309,53 +17305,53 @@
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>queens_primera</t>
+          <t>queens</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>escena examen_primera</t>
-        </is>
-      </c>
-      <c r="C138" s="11" t="inlineStr"/>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>nadie lo lee</t>
-        </is>
-      </c>
+          <t>escena examen_primera, escena examen_entra</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>escena ventana_queens, escena faro_queens, charla par:ana+gilbert:1</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>quiere_amiga</t>
+          <t>queens_primera</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>escena quiere_amiga</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr">
-        <is>
-          <t>escena aviso_barry, escena barry_recibe, meta conocer_diana (pista)</t>
-        </is>
-      </c>
-      <c r="D139" s="8" t="inlineStr"/>
+          <t>escena examen_primera</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr"/>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>nadie lo lee</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>rachel_en_casa_bell</t>
+          <t>quiere_amiga</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>escena quiere_amiga</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_bell</t>
+          <t>escena aviso_barry, escena barry_recibe, meta conocer_diana (pista)</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr"/>
@@ -17363,7 +17359,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>rachel_llego_tejas_verdes</t>
+          <t>rachel_en_casa_bell</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -17373,7 +17369,7 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>escena rachel_marilla</t>
+          <t>escena rachel_bell</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr"/>
@@ -17381,17 +17377,17 @@
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>rachel_lo_sabe</t>
+          <t>rachel_llego_tejas_verdes</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
+          <t>código</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
           <t>escena rachel_marilla</t>
-        </is>
-      </c>
-      <c r="C142" s="11" t="inlineStr">
-        <is>
-          <t>código</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr"/>
@@ -17399,17 +17395,17 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>regado</t>
+          <t>rachel_lo_sabe</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
+          <t>escena rachel_marilla</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
           <t>código</t>
-        </is>
-      </c>
-      <c r="C143" s="11" t="inlineStr">
-        <is>
-          <t>una frase de marilla</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr"/>
@@ -17417,7 +17413,7 @@
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>ropa_arrugada</t>
+          <t>regado</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -17435,7 +17431,7 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>ropa_ordenada</t>
+          <t>ropa_arrugada</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
@@ -17445,7 +17441,7 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>una frase de marilla, código</t>
+          <t>una frase de marilla</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr"/>
@@ -17453,7 +17449,7 @@
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>ropa_tirada_otra</t>
+          <t>ropa_ordenada</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
@@ -17463,7 +17459,7 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>escena falta_ropa (una opción), código</t>
+          <t>una frase de marilla, código</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr"/>
@@ -17471,7 +17467,7 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>se_fue_</t>
+          <t>ropa_tirada_otra</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
@@ -17479,18 +17475,22 @@
           <t>código</t>
         </is>
       </c>
-      <c r="C147" s="11" t="inlineStr"/>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>escena falta_ropa (una opción), código</t>
+        </is>
+      </c>
       <c r="D147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>se_fue_buhonero</t>
+          <t>se_fue_</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>llegadas</t>
+          <t>código</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr"/>
@@ -17499,7 +17499,7 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>se_fue_josephine</t>
+          <t>se_fue_buhonero</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
@@ -17507,17 +17507,13 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C149" s="11" t="inlineStr">
-        <is>
-          <t>llegadas de allan, llegadas de sraallan</t>
-        </is>
-      </c>
+      <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>se_fue_phillips</t>
+          <t>se_fue_josephine</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
@@ -17527,7 +17523,7 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
+          <t>llegadas de allan, llegadas de sraallan</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr"/>
@@ -17535,7 +17531,7 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>se_fue_prissy</t>
+          <t>se_fue_phillips</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
@@ -17543,13 +17539,17 @@
           <t>llegadas</t>
         </is>
       </c>
-      <c r="C151" s="11" t="inlineStr"/>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>noticia se_va_phillips, llegadas de prissy, llegadas de stacy</t>
+        </is>
+      </c>
       <c r="D151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>se_fue_veraneante</t>
+          <t>se_fue_prissy</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
@@ -17563,31 +17563,31 @@
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>se_fue_veraneante</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>escena se_queda</t>
-        </is>
-      </c>
-      <c r="C153" s="11" t="inlineStr">
-        <is>
-          <t>escena carta_spencer_1, escena resp_spencer_prueba_quedo, escena resp_spencer_conocidas_diana, escena resp_spencer_zanahorias_pizarra, escena resp_spencer_zanahorias_contesta, escena resp_spencer_zanahorias_ignora, escena resp_spencer_ofendio_lynde, escena resp_spencer_lynde_llanto, escena resp_spencer_prohibida, escena resp_spencer_1, escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, escena conv_marilla_por_que, un comentario de espejo, charla par:ana+matthew:2, charla par:lynde+marilla:0, charla par:marilla+matthew:1, charla par:marilla+matthew:2, charla par:ana+marilla+matthew:0, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana, hito decision</t>
-        </is>
-      </c>
+          <t>llegadas</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>undefined</t>
-        </is>
-      </c>
-      <c r="B154" s="11" t="inlineStr"/>
+          <t>se_queda</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>escena se_queda</t>
+        </is>
+      </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>escena primera_noche, un comentario de sueno_1, un comentario de sueno_2</t>
+          <t>escena carta_spencer_1, escena resp_spencer_prueba_quedo, escena resp_spencer_conocidas_diana, escena resp_spencer_zanahorias_pizarra, escena resp_spencer_zanahorias_contesta, escena resp_spencer_zanahorias_ignora, escena resp_spencer_ofendio_lynde, escena resp_spencer_lynde_llanto, escena resp_spencer_prohibida, escena resp_spencer_1, escena lynde_visita, escena ventana_se_queda, escena espejo_tejas_verdes, escena armario_vestidos, escena lugar_camino_blanco_flor, escena lugar_primera_nieve, escena conv_marilla_por_que, un comentario de espejo, charla par:ana+matthew:2, charla par:lynde+marilla:0, charla par:marilla+matthew:1, charla par:marilla+matthew:2, charla par:ana+marilla+matthew:0, una frase de matthew, una frase de marilla, una frase de lynde, una frase de tillie, una frase de allan, una frase de srbell, meta conocer_diana, hito decision</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr"/>
@@ -17595,13 +17595,13 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>undefined</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr"/>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>charla par:ana+diana:5, una frase de phillips</t>
+          <t>escena primera_noche, un comentario de sueno_1, un comentario de sueno_2</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr"/>
@@ -17609,13 +17609,13 @@
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr"/>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>charla par:ana+diana:5, una frase de phillips</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr"/>
@@ -17623,17 +17623,13 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>escena zanahorias</t>
-        </is>
-      </c>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr"/>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, escena conv_gilbert_caramelo, un comentario de pupitre, un comentario de pizarra, charla par:ana+gilbert:0, una frase de gilbert, meta paces, hito rival</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr"/>
@@ -17641,17 +17637,17 @@
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>zanahorias_contesta</t>
+          <t>zanahorias</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>escena zanahorias (una opción)</t>
+          <t>escena zanahorias</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>escena conv_diana_gilbert</t>
+          <t>escena ventana_zanahorias, escena espejo_zanahorias, escena pizarra_zanahorias, escena pupitre_gilbert, escena conv_marilla_john, escena conv_diana_gilbert, escena conv_gilbert_caramelo, un comentario de pupitre, un comentario de pizarra, charla par:ana+gilbert:0, una frase de gilbert, meta paces, hito rival</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr"/>
@@ -17659,7 +17655,7 @@
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>zanahorias_ignora</t>
+          <t>zanahorias_contesta</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -17669,7 +17665,7 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>escena resp_spencer_zanahorias_ignora, hito rival</t>
+          <t>escena conv_diana_gilbert</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr"/>
@@ -17677,7 +17673,7 @@
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>zanahorias_pizarra</t>
+          <t>zanahorias_ignora</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -17687,7 +17683,7 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>escena resp_spencer_zanahorias_pizarra, hito rival</t>
+          <t>escena resp_spencer_zanahorias_ignora, hito rival</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr"/>
@@ -17695,21 +17691,39 @@
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
+          <t>zanahorias_pizarra</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>escena zanahorias (una opción)</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>escena resp_spencer_zanahorias_pizarra, hito rival</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
           <t>{k}</t>
         </is>
       </c>
-      <c r="B161" s="11" t="inlineStr"/>
-      <c r="C161" s="11" t="inlineStr">
+      <c r="B162" s="11" t="inlineStr"/>
+      <c r="C162" s="11" t="inlineStr">
         <is>
           <t>una frase de niños</t>
         </is>
       </c>
-      <c r="D161" s="8" t="inlineStr"/>
+      <c r="D162" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <autoFilter ref="A1:D161"/>
-  <conditionalFormatting sqref="D2:D161">
+  <autoFilter ref="A1:D162"/>
+  <conditionalFormatting sqref="D2:D162">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(D2,5)="nunca"</formula>
     </cfRule>
@@ -19423,7 +19437,7 @@
       <c r="I26" s="7" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>afecto:marilla:ana&gt;=3</t>
+          <t>afecto:marilla:ana&gt;=3, hora:17-22</t>
         </is>
       </c>
     </row>
@@ -20106,15 +20120,15 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Ana Shirley, siempre es un gusto verte por aquí. Pórtate bien, ¿eh?</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr"/>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>barry_presenta</t>
-        </is>
-      </c>
+          <t>¿Cómo estás, Ana? Abrígate bien, que el viento de la isla es traicionero.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -20141,13 +20155,13 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Diana habla de ti todo el día, ¿sabes?</t>
+          <t>Ana Shirley, siempre es un gusto verte por aquí. Pórtate bien, ¿eh?</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>conocidas_diana</t>
+          <t>barry_presenta</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
@@ -20178,17 +20192,23 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Esta vez el cordial de frambuesa está bien etiquetado, te lo aseguro.</t>
+          <t>Diana habla de ti todo el día, ¿sabes?</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>perdonada</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="inlineStr"/>
+          <t>conocidas_diana</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="9" t="inlineStr"/>
     </row>
@@ -20209,21 +20229,17 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Buenas tardes. (La Sra. Barry no la invita a pasar.)</t>
+          <t>Esta vez el cordial de frambuesa está bien etiquetado, te lo aseguro.</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="H50" s="7" t="inlineStr"/>
       <c r="I50" s="7" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr"/>
     </row>
@@ -20244,23 +20260,23 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Saluda a Marilla de mi parte.</t>
+          <t>Buenas tardes. (La Sra. Barry no la invita a pasar.)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
-      <c r="F51" s="7" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>prohibida</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>!donde:ana:tejas</t>
-        </is>
-      </c>
+      <c r="J51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -20279,23 +20295,23 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Buenos días, niña. ¿Y Marilla, cómo está? Hace tiempo que no la veo.</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>Saluda a Marilla de mi parte.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>barry_presenta</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="9" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>!donde:ana:tejas</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -20309,24 +20325,24 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Buenos días, Ana. Diana está deseando verte.</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>barry_presenta</t>
-        </is>
-      </c>
+          <t>Buenos días, niña. ¿Y Marilla, cómo está? Hace tiempo que no la veo.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>barry_presenta</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr"/>
@@ -20344,12 +20360,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Qué calor, ¿verdad? Hay limonada en la despensa.</t>
+          <t>Buenos días, Ana. Diana está deseando verte.</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -20379,12 +20395,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Diana me ayudó con las manzanas. Llévale algunas a Marilla.</t>
+          <t>Qué calor, ¿verdad? Hay limonada en la despensa.</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
@@ -20414,12 +20430,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Pasa, pasa, que hace un frío terrible. Diana está junto al fuego.</t>
+          <t>Diana me ayudó con las manzanas. Llévale algunas a Marilla.</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr"/>
@@ -20435,16 +20451,12 @@
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>escena_ana:os</t>
-        </is>
-      </c>
+      <c r="J56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>lynde</t>
+          <t>barry</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -20453,30 +20465,30 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>¿Así que tú eres la huérfana de Tejas Verdes? Ya iré a verte con calma, ya.</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr"/>
+          <t>Pasa, pasa, que hace un frío terrible. Diana está junto al fuego.</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>barry_presenta</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>prohibida</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>sabe:lynde:nina_cuthbert</t>
+          <t>escena_ana:os</t>
         </is>
       </c>
     </row>
@@ -20497,23 +20509,27 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Hmpf. No tengo nada que hablar contigo, niña malcriada.</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>ofendio_lynde</t>
-        </is>
-      </c>
+          <t>¿Así que tú eres la huérfana de Tejas Verdes? Ya iré a verte con calma, ya.</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>disculpa_lynde</t>
+          <t>lynde_visita</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr"/>
-      <c r="J58" s="9" t="inlineStr"/>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>sabe:lynde:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -20532,15 +20548,19 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Desde mi ventana veo todo el camino: no se me escapa nadie. Lo digo sin mala intención, ¿eh?</t>
+          <t>Hmpf. No tengo nada que hablar contigo, niña malcriada.</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr"/>
-      <c r="F59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>disculpa_lynde</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr"/>
@@ -20563,7 +20583,7 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Llevo cincuenta y dos cubrecamas de retazos, ¡cincuenta y dos! Y no pienso parar.</t>
+          <t>Desde mi ventana veo todo el camino: no se me escapa nadie. Lo digo sin mala intención, ¿eh?</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
@@ -20594,15 +20614,11 @@
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Marilla hizo bien en quedarse contigo, y lo digo yo, que nunca me callo lo que pienso.</t>
+          <t>Llevo cincuenta y dos cubrecamas de retazos, ¡cincuenta y dos! Y no pienso parar.</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>se_queda</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -20610,11 +20626,7 @@
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>hecho:lynde_visita</t>
-        </is>
-      </c>
+      <c r="J61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -20633,13 +20645,13 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>A una niña hay que enseñarle a ser útil. Pero, bueno, tú vas por buen camino.</t>
+          <t>Marilla hizo bien en quedarse contigo, y lo digo yo, que nunca me callo lo que pienso.</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>se_queda</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
@@ -20649,7 +20661,11 @@
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>hecho:lynde_visita</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -20668,7 +20684,7 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Ana Shirley, hablas más que un molino... pero tienes buen corazón, eso lo reconozco.</t>
+          <t>A una niña hay que enseñarle a ser útil. Pero, bueno, tú vas por buen camino.</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
@@ -20698,12 +20714,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>¡Vaya, vaya, ya brotó todo! Ya es hora de limpiar la casa, digo yo.</t>
+          <t>Ana Shirley, hablas más que un molino... pero tienes buen corazón, eso lo reconozco.</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
@@ -20733,12 +20749,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Con este calor no hay quien teja... ¡pero yo tejo, claro que tejo!</t>
+          <t>¡Vaya, vaya, ya brotó todo! Ya es hora de limpiar la casa, digo yo.</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr"/>
@@ -20768,12 +20784,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>El otoño siempre me hace pensar en los cubrecamas. Este año haré uno rojo y dorado.</t>
+          <t>Con este calor no hay quien teja... ¡pero yo tejo, claro que tejo!</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
@@ -20803,12 +20819,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Pasa, niña, que hace un frío de mil demonios... perdón, de los que dan escalofríos.</t>
+          <t>El otoño siempre me hace pensar en los cubrecamas. Este año haré uno rojo y dorado.</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
@@ -20824,16 +20840,12 @@
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>escena_ana:rl</t>
-        </is>
-      </c>
+      <c r="J67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>harrison</t>
+          <t>lynde</t>
         </is>
       </c>
       <c r="B68" s="8">
@@ -20842,22 +20854,30 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>¡Hmpf! ¡En camisón! Ni Ginger anda tan mal vestido, muchacha.</t>
+          <t>Pasa, niña, que hace un frío de mil demonios... perdón, de los que dan escalofríos.</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>lynde_visita</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>ofendio_lynde</t>
+        </is>
+      </c>
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas</t>
+          <t>escena_ana:rl</t>
         </is>
       </c>
     </row>
@@ -20878,7 +20898,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>¿Tú, a esta hora? Vete a casa antes de que te confunda con un zorro.</t>
+          <t>¡Hmpf! ¡En camisón! Ni Ginger anda tan mal vestido, muchacha.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
@@ -20888,7 +20908,7 @@
       <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>hora:21-26, !donde:ana:tejas</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20929,7 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Hmpf. Buenos días... si es que son buenos.</t>
+          <t>¿Tú, a esta hora? Vete a casa antes de que te confunda con un zorro.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
@@ -20917,7 +20937,11 @@
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="inlineStr"/>
       <c r="I70" s="7" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>hora:21-26, !donde:ana:tejas</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -20936,18 +20960,12 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>¿Esa vaca tuya se ha portado bien hoy? Más le vale.</t>
+          <t>Hmpf. Buenos días... si es que son buenos.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>conoce_harrison</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="9" t="inlineStr"/>
@@ -20969,12 +20987,18 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>No me mires la casa, que el desorden es mío.</t>
+          <t>¿Esa vaca tuya se ha portado bien hoy? Más le vale.</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
-      <c r="F72" s="7" t="inlineStr"/>
-      <c r="G72" s="7" t="n"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>conoce_harrison</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr"/>
       <c r="J72" s="9" t="inlineStr"/>
@@ -20996,7 +21020,7 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Ginger, ¡silencio!... No le hagas caso, muchacha.</t>
+          <t>No me mires la casa, que el desorden es mío.</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
@@ -21018,12 +21042,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>La avena ya asoma. Que nadie la pise, ¿eh?</t>
+          <t>Ginger, ¡silencio!... No le hagas caso, muchacha.</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr"/>
@@ -21045,12 +21069,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Calor de mil demonios para segar... con perdón.</t>
+          <t>La avena ya asoma. Que nadie la pise, ¿eh?</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr"/>
@@ -21072,12 +21096,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Buena cosecha este año, aunque no lo diga mucho.</t>
+          <t>Calor de mil demonios para segar... con perdón.</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr"/>
@@ -21099,12 +21123,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Con este frío, ni Ginger quiere hablar. Bueno, sí quiere.</t>
+          <t>Buena cosecha este año, aunque no lo diga mucho.</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr"/>
@@ -21117,7 +21141,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>shearer</t>
+          <t>harrison</t>
         </is>
       </c>
       <c r="B78" s="8">
@@ -21126,12 +21150,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Buen día, señorita. ¿Algún animal para vender?</t>
+          <t>Con este frío, ni Ginger quiere hablar. Bueno, sí quiere.</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr"/>
@@ -21158,7 +21182,7 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Ando apurado: me esperan en Carmody.</t>
+          <t>Buen día, señorita. ¿Algún animal para vender?</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr"/>
@@ -21185,7 +21209,7 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Buena tierra la de por aquí, sí señor.</t>
+          <t>Ando apurado: me esperan en Carmody.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr"/>
@@ -21207,12 +21231,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>primavera</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Primavera: buen tiempo para comprar terneros.</t>
+          <t>Buena tierra la de por aquí, sí señor.</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr"/>
@@ -21234,12 +21258,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>primavera</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Con este calor las vacas dan menos leche, ¿sabía?</t>
+          <t>Primavera: buen tiempo para comprar terneros.</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr"/>
@@ -21261,12 +21285,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>otoño</t>
+          <t>verano</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>En otoño se vende bien el ganado.</t>
+          <t>Con este calor las vacas dan menos leche, ¿sabía?</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr"/>
@@ -21288,12 +21312,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>En invierno casi no salgo, pero hoy hacía falta.</t>
+          <t>En otoño se vende bien el ganado.</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr"/>
@@ -21306,7 +21330,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>gilbert</t>
+          <t>shearer</t>
         </is>
       </c>
       <c r="B85" s="8">
@@ -21315,20 +21339,16 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>invierno</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>¡Buenos días, Zanahorias!... Perdón, perdón. Era una broma, Ana.</t>
+          <t>En invierno casi no salgo, pero hoy hacía falta.</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr"/>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
+      <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr"/>
@@ -21351,7 +21371,7 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>¿Me vas a hablar algún día, Ana Shirley?</t>
+          <t>¡Buenos días, Zanahorias!... Perdón, perdón. Era una broma, Ana.</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr"/>
@@ -21382,18 +21402,16 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Te gané en ortografía. Pero en composición... bueno, ahí ganas tú.</t>
+          <t>¿Me vas a hablar algún día, Ana Shirley?</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>3</v>
-      </c>
+          <t>zanahorias</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="9" t="inlineStr"/>
@@ -21415,16 +21433,18 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>¿Quieres que te ayude a cruzar el arroyo? ¿No? Bueno...</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="n"/>
+          <t>Te gané en ortografía. Pero en composición... bueno, ahí ganas tú.</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="7" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr"/>
@@ -21441,20 +21461,20 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Hmpf.</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr"/>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>zanahorias</t>
-        </is>
-      </c>
+          <t>¿Quieres que te ayude a cruzar el arroyo? ¿No? Bueno...</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr"/>
@@ -21477,7 +21497,7 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>No le hablo a Gilbert Blythe. Nunca jamás.</t>
+          <t>Hmpf.</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr"/>
@@ -21508,7 +21528,7 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>(Ana sigue de largo con la nariz en alto.)</t>
+          <t>No le hablo a Gilbert Blythe. Nunca jamás.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
@@ -21525,7 +21545,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>buhonero</t>
+          <t>gilbert</t>
         </is>
       </c>
       <c r="B92" s="8">
@@ -21534,16 +21554,20 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>¡Cintas, botones, peinetas, tinte para el pelo! ¡Todo lo que una señorita necesita!</t>
+          <t>(Ana sigue de largo con la nariz en alto.)</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr"/>
-      <c r="F92" s="7" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>zanahorias</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr"/>
@@ -21566,7 +21590,7 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Un tinte que deja el pelo negro azabache, señorita. Garantizado.</t>
+          <t>¡Cintas, botones, peinetas, tinte para el pelo! ¡Todo lo que una señorita necesita!</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr"/>
@@ -21579,7 +21603,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>josie</t>
+          <t>buhonero</t>
         </is>
       </c>
       <c r="B94" s="8">
@@ -21593,7 +21617,7 @@
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>¿Ese vestido es nuevo, Ana? Ah, no... es el de siempre.</t>
+          <t>Un tinte que deja el pelo negro azabache, señorita. Garantizado.</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr"/>
@@ -21620,7 +21644,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Te apuesto a que no te atreves a caminar por el techo de la casa de los Barry.</t>
+          <t>¿Ese vestido es nuevo, Ana? Ah, no... es el de siempre.</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr"/>
@@ -21647,7 +21671,7 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá dice que las pelirrojas tienen mal genio. ¿Es verdad?</t>
+          <t>Te apuesto a que no te atreves a caminar por el techo de la casa de los Barry.</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr"/>
@@ -21669,12 +21693,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Josie Pye, eres... ¡eres una Pye!</t>
+          <t>Mi mamá dice que las pelirrojas tienen mal genio. ¿Es verdad?</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr"/>
@@ -21701,7 +21725,7 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>No pienso contestarte eso.</t>
+          <t>Josie Pye, eres... ¡eres una Pye!</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
@@ -21714,7 +21738,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>gertie</t>
+          <t>josie</t>
         </is>
       </c>
       <c r="B99" s="8">
@@ -21723,28 +21747,20 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Josie dice que tú hablas como un libro. ¿Es verdad? Di algo difícil.</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>No pienso contestarte eso.</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr"/>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>!dias_desde:escuela:3</t>
-        </is>
-      </c>
+      <c r="J99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -21763,21 +21779,23 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Josie dice que tú inventas palabras difíciles para lucirte.</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="n">
-        <v>3</v>
-      </c>
+          <t>Josie dice que tú hablas como un libro. ¿Es verdad? Di algo difícil.</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr"/>
-      <c r="J100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>!dias_desde:escuela:3</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -21796,7 +21814,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>¿Me prestas tu lápiz? El mío se perdió... otra vez.</t>
+          <t>Josie dice que tú inventas palabras difíciles para lucirte.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr"/>
@@ -21815,7 +21833,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>gertie</t>
         </is>
       </c>
       <c r="B102" s="8">
@@ -21829,12 +21847,18 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>¡Ay, Ana! ¿Viste cómo me miró Charlie Sloane?</t>
+          <t>¿Me prestas tu lápiz? El mío se perdió... otra vez.</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr"/>
-      <c r="F102" s="7" t="inlineStr"/>
-      <c r="G102" s="7" t="n"/>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H102" s="7" t="inlineStr"/>
       <c r="I102" s="7" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr"/>
@@ -21856,7 +21880,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Mi hermana tiene un pretendiente nuevo. ¡Es tan romántico!</t>
+          <t>¡Ay, Ana! ¿Viste cómo me miró Charlie Sloane?</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr"/>
@@ -21883,7 +21907,7 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>¿Vamos a ver las botellas de leche en el río? La mía tiene una cinta azul.</t>
+          <t>Mi hermana tiene un pretendiente nuevo. ¡Es tan romántico!</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr"/>
@@ -21896,7 +21920,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="B105" s="8">
@@ -21910,18 +21934,12 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>¿Hiciste los problemas de aritmética? Yo los hice dos veces, por si acaso.</t>
+          <t>¿Vamos a ver las botellas de leche en el río? La mía tiene una cinta azul.</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="n"/>
       <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
       <c r="J105" s="9" t="inlineStr"/>
@@ -21943,16 +21961,18 @@
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá dice que eres muy imaginativa. No sé si lo dice como algo bueno.</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="7" t="n"/>
+          <t>¿Hiciste los problemas de aritmética? Yo los hice dos veces, por si acaso.</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
       <c r="J106" s="9" t="inlineStr"/>
@@ -21960,7 +21980,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>prissy</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="B107" s="8">
@@ -21974,10 +21994,14 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>El año que viene voy a estudiar para entrar a Queen's.</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr"/>
+          <t>Mi mamá dice que eres muy imaginativa. No sé si lo dice como algo bueno.</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="inlineStr"/>
@@ -22001,7 +22025,7 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Ya tengo dieciséis años, ¿sabes? Casi una señorita.</t>
+          <t>El año que viene voy a estudiar para entrar a Queen's.</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr"/>
@@ -22014,7 +22038,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>charlie</t>
+          <t>prissy</t>
         </is>
       </c>
       <c r="B109" s="8">
@@ -22028,18 +22052,12 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Ana, ¿quieres... quieres usar mi pizarra nueva? Prestada, digo.</t>
+          <t>Ya tengo dieciséis años, ¿sabes? Casi una señorita.</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr"/>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="n"/>
       <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="7" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
@@ -22061,16 +22079,18 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá hizo tarta de grosellas. Te guardé un pedazo... si quieres.</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr"/>
-      <c r="G110" s="7" t="n"/>
+          <t>Ana, ¿quieres... quieres usar mi pizarra nueva? Prestada, digo.</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr"/>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="9" t="inlineStr"/>
@@ -22078,7 +22098,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>moody</t>
+          <t>charlie</t>
         </is>
       </c>
       <c r="B111" s="8">
@@ -22092,10 +22112,14 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Voy a ser pastor cuando sea grande. Ya practico los sermones con las vacas.</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr"/>
+          <t>Mi mamá hizo tarta de grosellas. Te guardé un pedazo... si quieres.</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F111" s="7" t="inlineStr"/>
       <c r="G111" s="7" t="n"/>
       <c r="H111" s="7" t="inlineStr"/>
@@ -22119,7 +22143,7 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Ayer el maestro me dejó sin recreo. Fue injusto, aunque sí me reí en la oración.</t>
+          <t>Voy a ser pastor cuando sea grande. Ya practico los sermones con las vacas.</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr"/>
@@ -22132,7 +22156,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>tillie</t>
+          <t>moody</t>
         </is>
       </c>
       <c r="B113" s="8">
@@ -22146,7 +22170,7 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>¿Juegas a la mancha? ¡Tú la llevas!</t>
+          <t>Ayer el maestro me dejó sin recreo. Fue injusto, aunque sí me reí en la oración.</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr"/>
@@ -22173,15 +22197,11 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Encontré un nido de petirrojos detrás de la escuela. ¡No le digas a nadie!</t>
+          <t>¿Juegas a la mancha? ¡Tú la llevas!</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>se_queda</t>
-        </is>
-      </c>
+      <c r="F114" s="7" t="inlineStr"/>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
@@ -22190,7 +22210,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>felicity</t>
+          <t>tillie</t>
         </is>
       </c>
       <c r="B115" s="8">
@@ -22204,11 +22224,15 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Mi madre dice que una señorita nunca corre. Pero yo corro si llego tarde.</t>
+          <t>Encontré un nido de petirrojos detrás de la escuela. ¡No le digas a nadie!</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr"/>
-      <c r="F115" s="7" t="inlineStr"/>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
       <c r="G115" s="7" t="n"/>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
@@ -22231,7 +22255,7 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Esta mañana hice pan yo solita. Bueno, casi solita.</t>
+          <t>Mi madre dice que una señorita nunca corre. Pero yo corro si llego tarde.</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
@@ -22244,7 +22268,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>felix</t>
+          <t>felicity</t>
         </is>
       </c>
       <c r="B117" s="8">
@@ -22258,7 +22282,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>¿Sabías que en el bosque de Peg Bowen vive una bruja de verdad?</t>
+          <t>Esta mañana hice pan yo solita. Bueno, casi solita.</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr"/>
@@ -22285,7 +22309,7 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Estoy juntando valor para tocar la puerta de Peg Bowen. Mañana. O pasado.</t>
+          <t>¿Sabías que en el bosque de Peg Bowen vive una bruja de verdad?</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr"/>
@@ -22298,7 +22322,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>cecily</t>
+          <t>felix</t>
         </is>
       </c>
       <c r="B119" s="8">
@@ -22312,18 +22336,12 @@
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>¿Me enseñas a recitar como tú? Cuando tú recitas, me dan escalofríos.</t>
+          <t>Estoy juntando valor para tocar la puerta de Peg Bowen. Mañana. O pasado.</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr"/>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F119" s="7" t="inlineStr"/>
+      <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="inlineStr"/>
       <c r="I119" s="7" t="inlineStr"/>
       <c r="J119" s="9" t="inlineStr"/>
@@ -22345,24 +22363,26 @@
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>¿Tú eres la niña de Tejas Verdes? Dicen que hablas como en los libros.</t>
+          <t>¿Me enseñas a recitar como tú? Cuando tú recitas, me dan escalofríos.</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr"/>
-      <c r="F120" s="7" t="inlineStr"/>
-      <c r="G120" s="7" t="n"/>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H120" s="7" t="inlineStr"/>
       <c r="I120" s="7" t="inlineStr"/>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>sabe:cecily:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>sara</t>
+          <t>cecily</t>
         </is>
       </c>
       <c r="B121" s="8">
@@ -22376,7 +22396,7 @@
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>¿Te cuento una historia? Es de un barco fantasma que se ve desde el faro las noches de niebla.</t>
+          <t>¿Tú eres la niña de Tejas Verdes? Dicen que hablas como en los libros.</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr"/>
@@ -22384,7 +22404,11 @@
       <c r="G121" s="7" t="n"/>
       <c r="H121" s="7" t="inlineStr"/>
       <c r="I121" s="7" t="inlineStr"/>
-      <c r="J121" s="9" t="inlineStr"/>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>sabe:cecily:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
@@ -22403,14 +22427,10 @@
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>La tía Hetty dice que hablo demasiado. Tú también, ¿no? ¡Qué bien!</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>¿Te cuento una historia? Es de un barco fantasma que se ve desde el faro las noches de niebla.</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr"/>
       <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="inlineStr"/>
@@ -22420,7 +22440,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>phillips</t>
+          <t>sara</t>
         </is>
       </c>
       <c r="B123" s="8">
@@ -22434,18 +22454,18 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>¡Vacaciones, por fin! Hasta los maestros las necesitamos, señorita.</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr"/>
+          <t>La tía Hetty dice que hablo demasiado. Tú también, ¿no? ¡Qué bien!</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F123" s="7" t="inlineStr"/>
       <c r="G123" s="7" t="n"/>
       <c r="H123" s="7" t="inlineStr"/>
-      <c r="I123" s="7" t="inlineStr">
-        <is>
-          <t>verano</t>
-        </is>
-      </c>
+      <c r="I123" s="7" t="inlineStr"/>
       <c r="J123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
@@ -22465,25 +22485,19 @@
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Señorita Shirley, ¿no debería estar repasando su ortografía?</t>
+          <t>¡Vacaciones, por fin! Hasta los maestros las necesitamos, señorita.</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="n"/>
       <c r="H124" s="7" t="inlineStr"/>
-      <c r="I124" s="7" t="inlineStr"/>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>!estacion:verano</t>
-        </is>
-      </c>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t>verano</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
@@ -22502,12 +22516,18 @@
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Mañana hay examen de geometría. Que nadie lo olvide.</t>
+          <t>Señorita Shirley, ¿no debería estar repasando su ortografía?</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr"/>
-      <c r="F125" s="7" t="inlineStr"/>
-      <c r="G125" s="7" t="n"/>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="7" t="inlineStr"/>
       <c r="J125" s="9" t="inlineStr">
@@ -22519,7 +22539,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>allan</t>
+          <t>phillips</t>
         </is>
       </c>
       <c r="B126" s="8">
@@ -22533,7 +22553,7 @@
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>(El reverendo carraspea.) Ana… quizás deberías volver a casa a vestirte.</t>
+          <t>Mañana hay examen de geometría. Que nadie lo olvide.</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr"/>
@@ -22543,7 +22563,7 @@
       <c r="I126" s="7" t="inlineStr"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas</t>
+          <t>!estacion:verano</t>
         </is>
       </c>
     </row>
@@ -22564,7 +22584,7 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Bienvenida, Ana. El Señor no mira los sombreros… pero la Sra. Lynde sí.</t>
+          <t>(El reverendo carraspea.) Ana… quizás deberías volver a casa a vestirte.</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
@@ -22574,7 +22594,7 @@
       <c r="I127" s="7" t="inlineStr"/>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>ana:sin_sombrero, escena_ana:ig</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -22595,19 +22615,19 @@
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Que Dios te bendiga, Ana. ¿Te veremos el domingo en la escuela dominical?</t>
+          <t>Bienvenida, Ana. El Señor no mira los sombreros… pero la Sra. Lynde sí.</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr"/>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>se_queda</t>
-        </is>
-      </c>
+      <c r="F128" s="7" t="inlineStr"/>
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="inlineStr"/>
       <c r="I128" s="7" t="inlineStr"/>
-      <c r="J128" s="9" t="inlineStr"/>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>ana:sin_sombrero, escena_ana:ig</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
@@ -22626,11 +22646,15 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Hermoso día para dar gracias, ¿no te parece?</t>
+          <t>Que Dios te bendiga, Ana. ¿Te veremos el domingo en la escuela dominical?</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr"/>
-      <c r="F129" s="7" t="inlineStr"/>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
       <c r="G129" s="7" t="n"/>
       <c r="H129" s="7" t="inlineStr"/>
       <c r="I129" s="7" t="inlineStr"/>
@@ -22639,7 +22663,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>sraallan</t>
+          <t>allan</t>
         </is>
       </c>
       <c r="B130" s="8">
@@ -22653,7 +22677,7 @@
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>¡Ana! Ven, ven, que te vas a resfriar. ¿Pasó algo en casa?</t>
+          <t>Hermoso día para dar gracias, ¿no te parece?</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr"/>
@@ -22661,11 +22685,7 @@
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="7" t="inlineStr"/>
       <c r="I130" s="7" t="inlineStr"/>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>ana:camison, !donde:ana:tejas</t>
-        </is>
-      </c>
+      <c r="J130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
@@ -22684,7 +22704,7 @@
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>(La Sra. Allan le sonríe, y le alisa el pelo con la mano.) Así estás bien, querida.</t>
+          <t>¡Ana! Ven, ven, que te vas a resfriar. ¿Pasó algo en casa?</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr"/>
@@ -22694,7 +22714,7 @@
       <c r="I131" s="7" t="inlineStr"/>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>ana:sin_sombrero, escena_ana:ig</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -22715,7 +22735,7 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>¡Ana, querida! ¡Qué gusto verte! ¿Cómo van tus estudios?</t>
+          <t>(La Sra. Allan le sonríe, y le alisa el pelo con la mano.) Así estás bien, querida.</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr"/>
@@ -22723,7 +22743,11 @@
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="7" t="inlineStr"/>
-      <c r="J132" s="9" t="inlineStr"/>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>ana:sin_sombrero, escena_ana:ig</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -22742,15 +22766,11 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Me encantó tu recitación. Tienes un don, Ana.</t>
+          <t>¡Ana, querida! ¡Qué gusto verte! ¿Cómo van tus estudios?</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr"/>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>escuela_dominical</t>
-        </is>
-      </c>
+      <c r="F133" s="7" t="inlineStr"/>
       <c r="G133" s="7" t="n"/>
       <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="7" t="inlineStr"/>
@@ -22773,11 +22793,15 @@
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Qué tarde tan linda para pasear, ¿verdad?</t>
+          <t>Me encantó tu recitación. Tienes un don, Ana.</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
-      <c r="F134" s="7" t="inlineStr"/>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>escuela_dominical</t>
+        </is>
+      </c>
       <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="7" t="inlineStr"/>
@@ -22795,19 +22819,15 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>¡Oh, Sra. Allan! Usted es mi espíritu afín.</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>Qué tarde tan linda para pasear, ¿verdad?</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="7" t="inlineStr"/>
       <c r="G135" s="7" t="n"/>
       <c r="H135" s="7" t="inlineStr"/>
@@ -22817,7 +22837,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>lawson</t>
+          <t>sraallan</t>
         </is>
       </c>
       <c r="B136" s="8">
@@ -22826,15 +22846,19 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>¡Buenos días, Ana! Llegaron caramelos de menta y cintas nuevas.</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
+          <t>¡Oh, Sra. Allan! Usted es mi espíritu afín.</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="n"/>
       <c r="H136" s="7" t="inlineStr"/>
@@ -22858,22 +22882,12 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>¿Qué te manda Marilla hoy? ¿Azúcar? ¿Hilo?</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>llegada_tv</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="n">
-        <v>7</v>
-      </c>
+          <t>¡Buenos días, Ana! Llegaron caramelos de menta y cintas nuevas.</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr"/>
+      <c r="F137" s="7" t="inlineStr"/>
+      <c r="G137" s="7" t="n"/>
       <c r="H137" s="7" t="inlineStr"/>
       <c r="I137" s="7" t="inlineStr"/>
       <c r="J137" s="9" t="inlineStr"/>
@@ -22881,7 +22895,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>herrero</t>
+          <t>lawson</t>
         </is>
       </c>
       <c r="B138" s="8">
@@ -22895,12 +22909,22 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>¡Cuidado con las chispas, niña!</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr"/>
-      <c r="F138" s="7" t="inlineStr"/>
-      <c r="G138" s="7" t="n"/>
+          <t>¿Qué te manda Marilla hoy? ¿Azúcar? ¿Hilo?</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>llegada_tv</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="n">
+        <v>7</v>
+      </c>
       <c r="H138" s="7" t="inlineStr"/>
       <c r="I138" s="7" t="inlineStr"/>
       <c r="J138" s="9" t="inlineStr"/>
@@ -22922,7 +22946,7 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>El caballo del Sr. Barry perdió una herradura. Otra vez.</t>
+          <t>¡Cuidado con las chispas, niña!</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
@@ -22935,7 +22959,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>herrero</t>
         </is>
       </c>
       <c r="B140" s="8">
@@ -22949,7 +22973,7 @@
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>¿Tienes alguna noticia para La Crónica, Ana? Se me acabaron las historias.</t>
+          <t>El caballo del Sr. Barry perdió una herradura. Otra vez.</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr"/>
@@ -22976,7 +23000,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Si escribes un cuento bonito, te lo publico. Palabra de editor.</t>
+          <t>¿Tienes alguna noticia para La Crónica, Ana? Se me acabaron las historias.</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
@@ -22989,7 +23013,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>hetty</t>
+          <t>editor</t>
         </is>
       </c>
       <c r="B142" s="8">
@@ -23003,7 +23027,7 @@
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Los niños de hoy no saben estarse quietos. En mis tiempos...</t>
+          <t>Si escribes un cuento bonito, te lo publico. Palabra de editor.</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
@@ -23030,7 +23054,7 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Señorita, no se corre por la calle principal. ¡Y menos con el sombrero torcido!</t>
+          <t>Los niños de hoy no saben estarse quietos. En mis tiempos...</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
@@ -23043,7 +23067,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>olivia</t>
+          <t>hetty</t>
         </is>
       </c>
       <c r="B144" s="8">
@@ -23057,7 +23081,7 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>¡Hola, Ana! ¿No es un día perfecto para un picnic?</t>
+          <t>Señorita, no se corre por la calle principal. ¡Y menos con el sombrero torcido!</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
@@ -23084,7 +23108,7 @@
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Jasper Dale me saludó esta mañana. Bueno... casi me saludó.</t>
+          <t>¡Hola, Ana! ¿No es un día perfecto para un picnic?</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
@@ -23097,7 +23121,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>jasper</t>
+          <t>olivia</t>
         </is>
       </c>
       <c r="B146" s="8">
@@ -23111,7 +23135,7 @@
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>B-buenos días. Estoy... estoy probando un invento. Para la lluvia.</t>
+          <t>Jasper Dale me saludó esta mañana. Bueno... casi me saludó.</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr"/>
@@ -23138,7 +23162,7 @@
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Si ves a la Srta. Olivia... no, nada. No le digas nada.</t>
+          <t>B-buenos días. Estoy... estoy probando un invento. Para la lluvia.</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
@@ -23151,7 +23175,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>alec</t>
+          <t>jasper</t>
         </is>
       </c>
       <c r="B148" s="8">
@@ -23165,7 +23189,7 @@
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Buen día para la siega, Ana. ¡Si no llueve!</t>
+          <t>Si ves a la Srta. Olivia... no, nada. No le digas nada.</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr"/>
@@ -23192,7 +23216,7 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Saluda a Matthew de mi parte. Hace tiempo que no conversamos.</t>
+          <t>Buen día para la siega, Ana. ¡Si no llueve!</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr"/>
@@ -23205,7 +23229,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>alec</t>
         </is>
       </c>
       <c r="B150" s="8">
@@ -23219,7 +23243,7 @@
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>¿Has visto a Felix? Tendría que estar trayendo leña.</t>
+          <t>Saluda a Matthew de mi parte. Hace tiempo que no conversamos.</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
@@ -23246,7 +23270,7 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Dile a Marilla que le devuelvo la fuente el sábado.</t>
+          <t>¿Has visto a Felix? Tendría que estar trayendo leña.</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr"/>
@@ -23259,7 +23283,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>srapye</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B152" s="8">
@@ -23273,7 +23297,7 @@
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>¿Ya supiste lo del Sr. Harrison? Dicen que su loro dice cosas terribles.</t>
+          <t>Dile a Marilla que le devuelvo la fuente el sábado.</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
@@ -23300,7 +23324,7 @@
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Pelo rojo, genio vivo, como dice el refrán.</t>
+          <t>¿Ya supiste lo del Sr. Harrison? Dicen que su loro dice cosas terribles.</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
@@ -23313,7 +23337,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>sloane</t>
+          <t>srapye</t>
         </is>
       </c>
       <c r="B154" s="8">
@@ -23327,7 +23351,7 @@
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Las papas vienen buenas este año. Ya lo verás.</t>
+          <t>Pelo rojo, genio vivo, como dice el refrán.</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr"/>
@@ -23340,7 +23364,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>andrews</t>
+          <t>sloane</t>
         </is>
       </c>
       <c r="B155" s="8">
@@ -23354,7 +23378,7 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>Buenas tardes. ¿Va todo bien en Tejas Verdes?</t>
+          <t>Las papas vienen buenas este año. Ya lo verás.</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
@@ -23367,7 +23391,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>peg</t>
+          <t>andrews</t>
         </is>
       </c>
       <c r="B156" s="8">
@@ -23381,7 +23405,7 @@
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>Je, je. ¿Tú eres la pelirroja de los Cuthbert? Dile a Marilla que Peg Bowen la saluda.</t>
+          <t>Buenas tardes. ¿Va todo bien en Tejas Verdes?</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
@@ -23408,7 +23432,7 @@
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>En el bosque no hay brujas, niña. Solo estoy yo... je, je.</t>
+          <t>Je, je. ¿Tú eres la pelirroja de los Cuthbert? Dile a Marilla que Peg Bowen la saluda.</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
@@ -23430,12 +23454,12 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>(¡Es Peg Bowen! Felix dice que es una bruja...)</t>
+          <t>En el bosque no hay brujas, niña. Solo estoy yo... je, je.</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
@@ -23448,7 +23472,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>farero</t>
+          <t>peg</t>
         </is>
       </c>
       <c r="B159" s="8">
@@ -23457,12 +23481,12 @@
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>Ese faro lleva cuarenta años encendido, y yo con él. Las noches de tormenta son las más hermosas.</t>
+          <t>(¡Es Peg Bowen! Felix dice que es una bruja...)</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
@@ -23489,7 +23513,7 @@
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>¿Ves esa vela allá lejos? Va a Charlottetown. Antes yo navegaba hasta las Antillas.</t>
+          <t>Ese faro lleva cuarenta años encendido, y yo con él. Las noches de tormenta son las más hermosas.</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr"/>
@@ -23516,7 +23540,7 @@
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Si subes al faro al atardecer, el mar se pone de oro. Pregúntale a cualquier gaviota.</t>
+          <t>¿Ves esa vela allá lejos? Va a Charlottetown. Antes yo navegaba hasta las Antillas.</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
@@ -23538,12 +23562,12 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>¡Capitán Jim, cuénteme una historia del mar!</t>
+          <t>Si subes al faro al atardecer, el mar se pone de oro. Pregúntale a cualquier gaviota.</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
@@ -23570,7 +23594,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>¡Qué vida tan romántica la de un farero!</t>
+          <t>¡Capitán Jim, cuénteme una historia del mar!</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
@@ -23583,7 +23607,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>stacy</t>
+          <t>farero</t>
         </is>
       </c>
       <c r="B164" s="8">
@@ -23592,12 +23616,12 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>Señorita Shirley, ¿una nueva moda? Me temo que Avonlea no está preparada. A casa, a vestirse.</t>
+          <t>¡Qué vida tan romántica la de un farero!</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
@@ -23605,11 +23629,7 @@
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="7" t="inlineStr"/>
       <c r="I164" s="7" t="inlineStr"/>
-      <c r="J164" s="9" t="inlineStr">
-        <is>
-          <t>ana:camison, !donde:ana:tejas</t>
-        </is>
-      </c>
+      <c r="J164" s="9" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
@@ -23628,7 +23648,7 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>¿Estudiando las estrellas, Ana? Mejor desde la ventana de tu cuarto. Buenas noches.</t>
+          <t>Señorita Shirley, ¿una nueva moda? Me temo que Avonlea no está preparada. A casa, a vestirse.</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
@@ -23638,7 +23658,7 @@
       <c r="I165" s="7" t="inlineStr"/>
       <c r="J165" s="9" t="inlineStr">
         <is>
-          <t>hora:21-26, !donde:ana:tejas</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -23659,21 +23679,19 @@
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>Ana, tu composición fue la mejor de la clase. Pero cuidado con los adjetivos: ¡no hacen falta tantos!</t>
+          <t>¿Estudiando las estrellas, Ana? Mejor desde la ventana de tu cuarto. Buenas noches.</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F166" s="7" t="inlineStr"/>
+      <c r="G166" s="7" t="n"/>
       <c r="H166" s="7" t="inlineStr"/>
       <c r="I166" s="7" t="inlineStr"/>
-      <c r="J166" s="9" t="inlineStr"/>
+      <c r="J166" s="9" t="inlineStr">
+        <is>
+          <t>hora:21-26, !donde:ana:tejas</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
@@ -23692,12 +23710,18 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>El viernes por la tarde salimos al bosque a estudiar botánica. ¿Te apuntas?</t>
+          <t>Ana, tu composición fue la mejor de la clase. Pero cuidado con los adjetivos: ¡no hacen falta tantos!</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
-      <c r="F167" s="7" t="inlineStr"/>
-      <c r="G167" s="7" t="n"/>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="7" t="inlineStr"/>
       <c r="J167" s="9" t="inlineStr"/>
@@ -23719,7 +23743,7 @@
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Este año preparamos a los mejores para el examen de Queen's. Tú puedes, Ana.</t>
+          <t>El viernes por la tarde salimos al bosque a estudiar botánica. ¿Te apuntas?</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
@@ -23727,11 +23751,7 @@
       <c r="G168" s="7" t="n"/>
       <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="7" t="inlineStr"/>
-      <c r="J168" s="9" t="inlineStr">
-        <is>
-          <t>estudio:ana&gt;=20</t>
-        </is>
-      </c>
+      <c r="J168" s="9" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -23745,29 +23765,29 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>¡Srta. Stacy! Usted es mi espíritu afín, ¿lo sabía?</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+          <t>Este año preparamos a los mejores para el examen de Queen's. Tú puedes, Ana.</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="7" t="inlineStr"/>
       <c r="G169" s="7" t="n"/>
       <c r="H169" s="7" t="inlineStr"/>
       <c r="I169" s="7" t="inlineStr"/>
-      <c r="J169" s="9" t="inlineStr"/>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>estudio:ana&gt;=20</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>minnie</t>
+          <t>stacy</t>
         </is>
       </c>
       <c r="B170" s="8">
@@ -23776,12 +23796,12 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>¡Ana! ¿Me cuentas un cuento de hadas? Diana dice que tú inventas los mejores.</t>
+          <t>¡Srta. Stacy! Usted es mi espíritu afín, ¿lo sabía?</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
@@ -23812,7 +23832,7 @@
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Diana no me deja jugar con sus muñecas. ¿Tú me dejas?</t>
+          <t>¡Ana! ¿Me cuentas un cuento de hadas? Diana dice que tú inventas los mejores.</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
@@ -23843,19 +23863,19 @@
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>¿Tú eres la niña nueva de Tejas Verdes? Mamá dice que eres pelirroja. ¡Y es verdad!</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr"/>
+          <t>Diana no me deja jugar con sus muñecas. ¿Tú me dejas?</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="F172" s="7" t="inlineStr"/>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="7" t="inlineStr"/>
       <c r="I172" s="7" t="inlineStr"/>
-      <c r="J172" s="9" t="inlineStr">
-        <is>
-          <t>sabe:minnie:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J172" s="9" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
@@ -23874,24 +23894,24 @@
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Ya no tengo tos. ¡Mamá dice que tú me salvaste!</t>
+          <t>¿Tú eres la niña nueva de Tejas Verdes? Mamá dice que eres pelirroja. ¡Y es verdad!</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="F173" s="7" t="inlineStr"/>
       <c r="G173" s="7" t="n"/>
       <c r="H173" s="7" t="inlineStr"/>
       <c r="I173" s="7" t="inlineStr"/>
-      <c r="J173" s="9" t="inlineStr"/>
+      <c r="J173" s="9" t="inlineStr">
+        <is>
+          <t>sabe:minnie:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>srbarry</t>
+          <t>minnie</t>
         </is>
       </c>
       <c r="B174" s="8">
@@ -23905,11 +23925,15 @@
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Buenas, Ana. Diana está en la casa, creo. O en el huerto.</t>
+          <t>Ya no tengo tos. ¡Mamá dice que tú me salvaste!</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
-      <c r="F174" s="7" t="inlineStr"/>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>perdonada</t>
+        </is>
+      </c>
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="inlineStr"/>
       <c r="I174" s="7" t="inlineStr"/>
@@ -23932,7 +23956,7 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>El heno está listo para entrar. Si no llueve, mañana lo cargamos.</t>
+          <t>Buenas, Ana. Diana está en la casa, creo. O en el huerto.</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr"/>
@@ -23945,7 +23969,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>maryjoe</t>
+          <t>srbarry</t>
         </is>
       </c>
       <c r="B176" s="8">
@@ -23959,15 +23983,11 @@
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>¡Ay, señorita Ana! Yo no sé nada de enfermedades, menos mal que usted vino aquella noche.</t>
+          <t>El heno está listo para entrar. Si no llueve, mañana lo cargamos.</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr"/>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="F176" s="7" t="inlineStr"/>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="7" t="inlineStr"/>
@@ -23990,11 +24010,15 @@
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>La señora Barry dice que tienda la ropa antes de que se nuble.</t>
+          <t>¡Ay, señorita Ana! Yo no sé nada de enfermedades, menos mal que usted vino aquella noche.</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
-      <c r="F177" s="7" t="inlineStr"/>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>perdonada</t>
+        </is>
+      </c>
       <c r="G177" s="7" t="n"/>
       <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="7" t="inlineStr"/>
@@ -24003,7 +24027,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>jerry</t>
+          <t>maryjoe</t>
         </is>
       </c>
       <c r="B178" s="8">
@@ -24017,7 +24041,7 @@
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>El Sr. Cuthbert me pidió que entrara la leña antes de la cena.</t>
+          <t>La señora Barry dice que tienda la ropa antes de que se nuble.</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
@@ -24044,7 +24068,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Oui, oui... ya voy, ya voy. ¡Esa vaca no se quiere mover!</t>
+          <t>El Sr. Cuthbert me pidió que entrara la leña antes de la cena.</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr"/>
@@ -24057,7 +24081,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>medico</t>
+          <t>jerry</t>
         </is>
       </c>
       <c r="B180" s="8">
@@ -24071,7 +24095,7 @@
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>¿Alguien enfermo en Tejas Verdes? Espero que no.</t>
+          <t>Oui, oui... ya voy, ya voy. ¡Esa vaca no se quiere mover!</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr"/>
@@ -24098,15 +24122,11 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Esa niña Shirley tiene buena cabeza: salvó a la pequeña Barry del crup antes de que yo llegara.</t>
+          <t>¿Alguien enfermo en Tejas Verdes? Espero que no.</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr"/>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>perdonada</t>
-        </is>
-      </c>
+      <c r="F181" s="7" t="inlineStr"/>
       <c r="G181" s="7" t="n"/>
       <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="7" t="inlineStr"/>
@@ -24115,7 +24135,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>srbell</t>
+          <t>medico</t>
         </is>
       </c>
       <c r="B182" s="8">
@@ -24129,13 +24149,13 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>Te esperamos el domingo en la escuela dominical, Ana. Y apréndete el versículo.</t>
+          <t>Esa niña Shirley tiene buena cabeza: salvó a la pequeña Barry del crup antes de que yo llegara.</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr"/>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>perdonada</t>
         </is>
       </c>
       <c r="G182" s="7" t="n"/>
@@ -24160,11 +24180,15 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>Una oración larga no es mejor que una sincera, niña.</t>
+          <t>Te esperamos el domingo en la escuela dominical, Ana. Y apréndete el versículo.</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr"/>
-      <c r="F183" s="7" t="inlineStr"/>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>se_queda</t>
+        </is>
+      </c>
       <c r="G183" s="7" t="n"/>
       <c r="H183" s="7" t="inlineStr"/>
       <c r="I183" s="7" t="inlineStr"/>
@@ -24173,7 +24197,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>srbell</t>
         </is>
       </c>
       <c r="B184" s="8">
@@ -24187,7 +24211,7 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>Así que tú eres la niña de Tejas Verdes. Hmm. Ya veremos qué clase de niña eres.</t>
+          <t>Una oración larga no es mejor que una sincera, niña.</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr"/>
@@ -24195,11 +24219,7 @@
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="inlineStr"/>
       <c r="I184" s="7" t="inlineStr"/>
-      <c r="J184" s="9" t="inlineStr">
-        <is>
-          <t>sabe:josephine:nina_cuthbert</t>
-        </is>
-      </c>
+      <c r="J184" s="9" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
@@ -24218,19 +24238,19 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>¡La niña Ana! Desde que me saltaste encima en la cama, no me había reído tanto en años.</t>
+          <t>Así que tú eres la niña de Tejas Verdes. Hmm. Ya veremos qué clase de niña eres.</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr"/>
-      <c r="F185" s="7" t="inlineStr">
-        <is>
-          <t>cama_josephine</t>
-        </is>
-      </c>
+      <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="n"/>
       <c r="H185" s="7" t="inlineStr"/>
       <c r="I185" s="7" t="inlineStr"/>
-      <c r="J185" s="9" t="inlineStr"/>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>sabe:josephine:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
@@ -24249,7 +24269,7 @@
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>Cuando vengas a Charlottetown, te alojas en mi casa. Te llevo a la exposición.</t>
+          <t>¡La niña Ana! Desde que me saltaste encima en la cama, no me había reído tanto en años.</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr"/>
@@ -24275,16 +24295,20 @@
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>¡Srta. Barry! Usted es un espíritu afín, aunque no lo parezca a primera vista.</t>
+          <t>Cuando vengas a Charlottetown, te alojas en mi casa. Te llevo a la exposición.</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr"/>
-      <c r="F187" s="7" t="inlineStr"/>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>cama_josephine</t>
+        </is>
+      </c>
       <c r="G187" s="7" t="n"/>
       <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
@@ -24293,7 +24317,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>spencer</t>
+          <t>josephine</t>
         </is>
       </c>
       <c r="B188" s="8">
@@ -24302,12 +24326,12 @@
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>¡Ana! Qué bien te ves. Y yo que creí que los Cuthbert querían una niña… ¡qué enredo!</t>
+          <t>¡Srta. Barry! Usted es un espíritu afín, aunque no lo parezca a primera vista.</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr"/>
@@ -24334,7 +24358,7 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>Mi Lily estuvo enferma, por eso no pude llevarte yo a Tejas Verdes.</t>
+          <t>¡Ana! Qué bien te ves. Y yo que creí que los Cuthbert querían una niña… ¡qué enredo!</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr"/>
@@ -24347,7 +24371,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>blewett</t>
+          <t>spencer</t>
         </is>
       </c>
       <c r="B190" s="8">
@@ -24361,15 +24385,11 @@
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>Así que te quedaste con los Cuthbert. Hmm. Yo te habría hecho trabajar de verdad.</t>
+          <t>Mi Lily estuvo enferma, por eso no pude llevarte yo a Tejas Verdes.</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>a_prueba</t>
-        </is>
-      </c>
+      <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="n"/>
       <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
@@ -24392,11 +24412,15 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>Hmm. Flacucha. En mi casa no hay tiempo para mirar las nubes, ¿sabes?</t>
+          <t>Así que te quedaste con los Cuthbert. Hmm. Yo te habría hecho trabajar de verdad.</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr"/>
-      <c r="F191" s="7" t="inlineStr"/>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>a_prueba</t>
+        </is>
+      </c>
       <c r="G191" s="7" t="n"/>
       <c r="H191" s="7" t="inlineStr"/>
       <c r="I191" s="7" t="inlineStr"/>
@@ -24414,20 +24438,16 @@
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>(Ana se esconde detrás de un árbol. ¡Menos mal que Marilla no la dejó irse con ella!)</t>
+          <t>Hmm. Flacucha. En mi casa no hay tiempo para mirar las nubes, ¿sabes?</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr"/>
-      <c r="F192" s="7" t="inlineStr">
-        <is>
-          <t>a_prueba</t>
-        </is>
-      </c>
+      <c r="F192" s="7" t="inlineStr"/>
       <c r="G192" s="7" t="n"/>
       <c r="H192" s="7" t="inlineStr"/>
       <c r="I192" s="7" t="inlineStr"/>
@@ -24436,7 +24456,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>carrie</t>
+          <t>blewett</t>
         </is>
       </c>
       <c r="B193" s="8">
@@ -24445,30 +24465,24 @@
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>¿Viste la composición de Ana? ¡La señorita Stacy la leyó en voz alta!</t>
+          <t>(Ana se esconde detrás de un árbol. ¡Menos mal que Marilla no la dejó irse con ella!)</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr"/>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>escuela</t>
-        </is>
-      </c>
-      <c r="G193" s="7" t="n">
-        <v>3</v>
-      </c>
+          <t>a_prueba</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="n"/>
       <c r="H193" s="7" t="inlineStr"/>
       <c r="I193" s="7" t="inlineStr"/>
-      <c r="J193" s="9" t="inlineStr">
-        <is>
-          <t>hecho:llego_stacy</t>
-        </is>
-      </c>
+      <c r="J193" s="9" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
@@ -24487,24 +24501,30 @@
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>Mi mamá dice que en Tejas Verdes hay una niña nueva. ¿Eres tú?</t>
+          <t>¿Viste la composición de Ana? ¡La señorita Stacy la leyó en voz alta!</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr"/>
-      <c r="F194" s="7" t="inlineStr"/>
-      <c r="G194" s="7" t="n"/>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>escuela</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H194" s="7" t="inlineStr"/>
       <c r="I194" s="7" t="inlineStr"/>
       <c r="J194" s="9" t="inlineStr">
         <is>
-          <t>sabe:carrie:nina_cuthbert</t>
+          <t>hecho:llego_stacy</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>jefe</t>
+          <t>carrie</t>
         </is>
       </c>
       <c r="B195" s="8">
@@ -24518,7 +24538,7 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>El tren de las cinco y media ya pasó, ¿sabe? Hoy no viene otro.</t>
+          <t>Mi mamá dice que en Tejas Verdes hay una niña nueva. ¿Eres tú?</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr"/>
@@ -24526,7 +24546,11 @@
       <c r="G195" s="7" t="n"/>
       <c r="H195" s="7" t="inlineStr"/>
       <c r="I195" s="7" t="inlineStr"/>
-      <c r="J195" s="9" t="inlineStr"/>
+      <c r="J195" s="9" t="inlineStr">
+        <is>
+          <t>sabe:carrie:nina_cuthbert</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -24545,7 +24569,7 @@
       </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>Esa niñita de pelo rojo... se sentó en las tejuelas a imaginar cosas. Todo un caso.</t>
+          <t>El tren de las cinco y media ya pasó, ¿sabe? Hoy no viene otro.</t>
         </is>
       </c>
       <c r="E196" s="7" t="inlineStr"/>
@@ -24558,7 +24582,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>thomas</t>
+          <t>jefe</t>
         </is>
       </c>
       <c r="B197" s="8">
@@ -24572,7 +24596,7 @@
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>Buenas. Rachel está adentro. Ella habla por los dos, ¿sabes?</t>
+          <t>Esa niñita de pelo rojo... se sentó en las tejuelas a imaginar cosas. Todo un caso.</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr"/>
@@ -24585,7 +24609,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>veraneante</t>
+          <t>thomas</t>
         </is>
       </c>
       <c r="B198" s="8">
@@ -24599,7 +24623,7 @@
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>¡Qué playa tan encantadora! En Boston no hay nada parecido.</t>
+          <t>Buenas. Rachel está adentro. Ella habla por los dos, ¿sabes?</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr"/>
@@ -24626,7 +24650,7 @@
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>¿Eres de aquí, niña? ¡Qué suerte vivir en un lugar así!</t>
+          <t>¡Qué playa tan encantadora! En Boston no hay nada parecido.</t>
         </is>
       </c>
       <c r="E199" s="7" t="inlineStr"/>
@@ -24639,7 +24663,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>pescador</t>
+          <t>veraneante</t>
         </is>
       </c>
       <c r="B200" s="8">
@@ -24653,7 +24677,7 @@
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>Hoy vienen buenas las caballas. Si Marilla quiere pescado, que mande a Matthew.</t>
+          <t>¿Eres de aquí, niña? ¡Qué suerte vivir en un lugar así!</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr"/>
@@ -24666,7 +24690,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>vecino</t>
+          <t>pescador</t>
         </is>
       </c>
       <c r="B201" s="8">
@@ -24680,18 +24704,12 @@
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>¡Buenos días, Ana! ¿Cómo están Matthew y Marilla?</t>
+          <t>Hoy vienen buenas las caballas. Si Marilla quiere pescado, que mande a Matthew.</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr"/>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>llegada_tv</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="n">
-        <v>14</v>
-      </c>
+      <c r="F201" s="7" t="inlineStr"/>
+      <c r="G201" s="7" t="n"/>
       <c r="H201" s="7" t="inlineStr"/>
       <c r="I201" s="7" t="inlineStr"/>
       <c r="J201" s="9" t="inlineStr"/>
@@ -24713,12 +24731,18 @@
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>Lindo día, ¿verdad? Dicen que mañana llueve.</t>
+          <t>¡Buenos días, Ana! ¿Cómo están Matthew y Marilla?</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr"/>
-      <c r="F202" s="7" t="inlineStr"/>
-      <c r="G202" s="7" t="n"/>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>llegada_tv</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="n">
+        <v>14</v>
+      </c>
       <c r="H202" s="7" t="inlineStr"/>
       <c r="I202" s="7" t="inlineStr"/>
       <c r="J202" s="9" t="inlineStr"/>
@@ -24740,25 +24764,15 @@
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>¡Qué grande estás, niña! Saludos a Marilla.</t>
+          <t>Lindo día, ¿verdad? Dicen que mañana llueve.</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr"/>
-      <c r="F203" s="7" t="inlineStr">
-        <is>
-          <t>llegada_tv</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="n">
-        <v>56</v>
-      </c>
+      <c r="F203" s="7" t="inlineStr"/>
+      <c r="G203" s="7" t="n"/>
       <c r="H203" s="7" t="inlineStr"/>
       <c r="I203" s="7" t="inlineStr"/>
-      <c r="J203" s="9" t="inlineStr">
-        <is>
-          <t>!donde:ana:tejas</t>
-        </is>
-      </c>
+      <c r="J203" s="9" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -24777,17 +24791,23 @@
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>Buenas. Tú no eres de por aquí, ¿no?</t>
+          <t>¡Qué grande estás, niña! Saludos a Marilla.</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr"/>
-      <c r="F204" s="7" t="inlineStr"/>
-      <c r="G204" s="7" t="n"/>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>llegada_tv</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="n">
+        <v>56</v>
+      </c>
       <c r="H204" s="7" t="inlineStr"/>
       <c r="I204" s="7" t="inlineStr"/>
       <c r="J204" s="9" t="inlineStr">
         <is>
-          <t>!dias_desde:llegada_tv:14</t>
+          <t>!donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -24808,7 +24828,7 @@
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>¿Vas para la aldea? Yo vengo de la tienda de Lawson.</t>
+          <t>Buenas. Tú no eres de por aquí, ¿no?</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr"/>
@@ -24816,7 +24836,11 @@
       <c r="G205" s="7" t="n"/>
       <c r="H205" s="7" t="inlineStr"/>
       <c r="I205" s="7" t="inlineStr"/>
-      <c r="J205" s="9" t="inlineStr"/>
+      <c r="J205" s="9" t="inlineStr">
+        <is>
+          <t>!dias_desde:llegada_tv:14</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
@@ -24835,7 +24859,7 @@
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>Buenas, buenas. No te entretengas, que se hace tarde.</t>
+          <t>¿Vas para la aldea? Yo vengo de la tienda de Lawson.</t>
         </is>
       </c>
       <c r="E206" s="7" t="inlineStr"/>
@@ -24862,7 +24886,7 @@
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>Mira qué cielo. Así da gusto salir.</t>
+          <t>Buenas, buenas. No te entretengas, que se hace tarde.</t>
         </is>
       </c>
       <c r="E207" s="7" t="inlineStr"/>
@@ -24875,7 +24899,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>niño</t>
+          <t>vecino</t>
         </is>
       </c>
       <c r="B208" s="8">
@@ -24889,7 +24913,7 @@
       </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
-          <t>¿Tú eres Ana? ¡Tienes el pelo como una zanahoria!... ¡Es bonito!</t>
+          <t>Mira qué cielo. Así da gusto salir.</t>
         </is>
       </c>
       <c r="E208" s="7" t="inlineStr"/>
@@ -24916,7 +24940,7 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>¡Mira, encontré una piedra que brilla!</t>
+          <t>¿Tú eres Ana? ¡Tienes el pelo como una zanahoria!... ¡Es bonito!</t>
         </is>
       </c>
       <c r="E209" s="7" t="inlineStr"/>
@@ -24943,7 +24967,7 @@
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>¿Jugamos? Yo me escondo y tú cuentas hasta cien.</t>
+          <t>¡Mira, encontré una piedra que brilla!</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr"/>
@@ -24956,7 +24980,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>adultos</t>
+          <t>niño</t>
         </is>
       </c>
       <c r="B211" s="8">
@@ -24970,7 +24994,7 @@
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>¡Niña! ¿Andas en camisón por la calle? ¡Qué va a decir la gente!</t>
+          <t>¿Jugamos? Yo me escondo y tú cuentas hasta cien.</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr"/>
@@ -24978,11 +25002,7 @@
       <c r="G211" s="7" t="n"/>
       <c r="H211" s="7" t="inlineStr"/>
       <c r="I211" s="7" t="inlineStr"/>
-      <c r="J211" s="9" t="inlineStr">
-        <is>
-          <t>ana:camison, !donde:ana:tejas</t>
-        </is>
-      </c>
+      <c r="J211" s="9" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
@@ -25001,7 +25021,7 @@
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>¡Válgame Dios! La niña de los Cuthbert, en camisón… Ya verás cuando lo sepa Marilla.</t>
+          <t>¡Niña! ¿Andas en camisón por la calle? ¡Qué va a decir la gente!</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr"/>
@@ -25011,7 +25031,7 @@
       <c r="I212" s="7" t="inlineStr"/>
       <c r="J212" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas, sabe:{k}:nina_cuthbert</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -25032,7 +25052,7 @@
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>(Se le queda mirando, con la boca abierta, sin saber qué decir.)</t>
+          <t>¡Válgame Dios! La niña de los Cuthbert, en camisón… Ya verás cuando lo sepa Marilla.</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr"/>
@@ -25042,7 +25062,7 @@
       <c r="I213" s="7" t="inlineStr"/>
       <c r="J213" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas</t>
+          <t>ana:camison, !donde:ana:tejas, sabe:{k}:nina_cuthbert</t>
         </is>
       </c>
     </row>
@@ -25063,7 +25083,7 @@
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>¿Qué haces sola a estas horas, niña? Vete derechito a tu casa.</t>
+          <t>(Se le queda mirando, con la boca abierta, sin saber qué decir.)</t>
         </is>
       </c>
       <c r="E214" s="7" t="inlineStr"/>
@@ -25073,7 +25093,7 @@
       <c r="I214" s="7" t="inlineStr"/>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>hora:21-26, !donde:ana:tejas</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25114,7 @@
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>¡A esta hora, por el camino! ¿Saben los Cuthbert dónde andas?</t>
+          <t>¿Qué haces sola a estas horas, niña? Vete derechito a tu casa.</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr"/>
@@ -25125,7 +25145,7 @@
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>(Mira a Ana de arriba abajo.) ¿A la iglesia sin sombrero? En mis tiempos, eso no se veía.</t>
+          <t>¡A esta hora, por el camino! ¿Saben los Cuthbert dónde andas?</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr"/>
@@ -25135,7 +25155,7 @@
       <c r="I216" s="7" t="inlineStr"/>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>ana:sin_sombrero, escena_ana:ig</t>
+          <t>hora:21-26, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -25156,7 +25176,7 @@
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>Hmm. Sin sombrero, en la casa del Señor… Alguien tendría que decírselo a Marilla.</t>
+          <t>(Mira a Ana de arriba abajo.) ¿A la iglesia sin sombrero? En mis tiempos, eso no se veía.</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr"/>
@@ -25173,7 +25193,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>niños</t>
+          <t>adultos</t>
         </is>
       </c>
       <c r="B218" s="8">
@@ -25187,7 +25207,7 @@
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>¡Miren a la de Tejas Verdes! ¡Anda en camisón! (Se ríe tapándose la boca.)</t>
+          <t>Hmm. Sin sombrero, en la casa del Señor… Alguien tendría que decírselo a Marilla.</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr"/>
@@ -25197,7 +25217,7 @@
       <c r="I218" s="7" t="inlineStr"/>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas, !afecto:{k}:ana&gt;=3, sabe:{k}:nina_cuthbert</t>
+          <t>ana:sin_sombrero, escena_ana:ig</t>
         </is>
       </c>
     </row>
@@ -25218,7 +25238,7 @@
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>¿Saliste en camisón? ¡Mi mamá me mataría!</t>
+          <t>¡Miren a la de Tejas Verdes! ¡Anda en camisón! (Se ríe tapándose la boca.)</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr"/>
@@ -25228,7 +25248,7 @@
       <c r="I219" s="7" t="inlineStr"/>
       <c r="J219" s="9" t="inlineStr">
         <is>
-          <t>ana:camison, !donde:ana:tejas</t>
+          <t>ana:camison, !donde:ana:tejas, !afecto:{k}:ana&gt;=3, sabe:{k}:nina_cuthbert</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25269,7 @@
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>¿Tú puedes andar afuera a esta hora? A mí no me dejan.</t>
+          <t>¿Saliste en camisón? ¡Mi mamá me mataría!</t>
         </is>
       </c>
       <c r="E220" s="7" t="inlineStr"/>
@@ -25259,7 +25279,7 @@
       <c r="I220" s="7" t="inlineStr"/>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>hora:21-26, !donde:ana:tejas</t>
+          <t>ana:camison, !donde:ana:tejas</t>
         </is>
       </c>
     </row>
@@ -25280,7 +25300,7 @@
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>(Le susurra a la de al lado, mirando a Ana sin sombrero, y las dos se ríen.)</t>
+          <t>¿Tú puedes andar afuera a esta hora? A mí no me dejan.</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr"/>
@@ -25290,14 +25310,39 @@
       <c r="I221" s="7" t="inlineStr"/>
       <c r="J221" s="9" t="inlineStr">
         <is>
+          <t>hora:21-26, !donde:ana:tejas</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>niños</t>
+        </is>
+      </c>
+      <c r="B222" s="8">
+        <f>IFERROR(INDEX(Personas!$B:$B,MATCH(A222,Personas!$A:$A,0)),"(¿quién?)")</f>
+        <v/>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr">
+        <is>
+          <t>(Le susurra a la de al lado, mirando a Ana sin sombrero, y las dos se ríen.)</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr"/>
+      <c r="F222" s="7" t="inlineStr"/>
+      <c r="G222" s="7" t="n"/>
+      <c r="H222" s="7" t="inlineStr"/>
+      <c r="I222" s="7" t="inlineStr"/>
+      <c r="J222" s="9" t="inlineStr">
+        <is>
           <t>ana:sin_sombrero, escena_ana:ig, !afecto:{k}:ana&gt;=3</t>
         </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="B222" s="10">
-        <f>IF(A222="","",IFERROR(INDEX(Personas!$B:$B,MATCH(A222,Personas!$A:$A,0)),"(¿quién?)"))</f>
-        <v/>
       </c>
     </row>
     <row r="223">
@@ -35991,10 +36036,10 @@
       <formula1>=Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="No es un hecho ni una meta que exista (¿está bien escrito?)." type="list" errorStyle="warning">
-      <formula1>=Listas!$E$2:$E$170</formula1>
+      <formula1>=Listas!$E$2:$E$171</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="No es un hecho ni una meta que exista (¿está bien escrito?)." type="list" errorStyle="warning">
-      <formula1>=Listas!$E$2:$E$170</formula1>
+      <formula1>=Listas!$E$2:$E$171</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Avonlea" error="primavera, verano, otoño o invierno." type="list" errorStyle="stop">
       <formula1>=Listas!$D$2:$D$5</formula1>
@@ -36014,7 +36059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36057,8 +36102,43 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>hueco</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>algo que decirle</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>la Sra. Barry</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>día: 46 · estación: invierno · hora: 6:00 · Ana en: el patio de Tejas Verdes · conoce a la Sra. Barry: sí</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>ana:camison (4); !conoce:barry (2); hecho:prohibida (2); hora:21-26 (2); ana:sin_sombrero (2); !hecho:conocidas_diana (2)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F2"/>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>A2="incoherencia"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39452,19 +39532,19 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>1</v>
@@ -39476,25 +39556,25 @@
         <v>2</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" s="19" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" s="19" t="n">
         <v>1</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="19" t="n">
         <v>2</v>
       </c>
       <c r="R9" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -42984,7 +43064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43406,7 +43486,7 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>diana_borracha</t>
+          <t>diana</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43498,7 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>disculpa_lynde</t>
+          <t>diana_borracha</t>
         </is>
       </c>
     </row>
@@ -43430,7 +43510,7 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>escuela</t>
+          <t>disculpa_lynde</t>
         </is>
       </c>
     </row>
@@ -43442,7 +43522,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>escuela_dominical</t>
+          <t>escuela</t>
         </is>
       </c>
     </row>
@@ -43454,7 +43534,7 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>examen</t>
+          <t>escuela_dominical</t>
         </is>
       </c>
     </row>
@@ -43466,7 +43546,7 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>historia_</t>
+          <t>examen</t>
         </is>
       </c>
     </row>
@@ -43478,7 +43558,7 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>historia_a_prueba</t>
+          <t>historia_</t>
         </is>
       </c>
     </row>
@@ -43490,7 +43570,7 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>historia_a_prueba_cerrado</t>
+          <t>historia_a_prueba</t>
         </is>
       </c>
     </row>
@@ -43502,7 +43582,7 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma</t>
+          <t>historia_a_prueba_cerrado</t>
         </is>
       </c>
     </row>
@@ -43514,7 +43594,7 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_cerrado</t>
+          <t>historia_amiga_del_alma</t>
         </is>
       </c>
     </row>
@@ -43526,7 +43606,7 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_juran</t>
+          <t>historia_amiga_del_alma_cerrado</t>
         </is>
       </c>
     </row>
@@ -43538,7 +43618,7 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>historia_amiga_del_alma_no_juran</t>
+          <t>historia_amiga_del_alma_juran</t>
         </is>
       </c>
     </row>
@@ -43550,7 +43630,7 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba</t>
+          <t>historia_amiga_del_alma_no_juran</t>
         </is>
       </c>
     </row>
@@ -43562,7 +43642,7 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba_cerrado</t>
+          <t>historia_amistad_a_prueba</t>
         </is>
       </c>
     </row>
@@ -43574,7 +43654,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>historia_amistad_a_prueba_la_recupera</t>
+          <t>historia_amistad_a_prueba_cerrado</t>
         </is>
       </c>
     </row>
@@ -43586,7 +43666,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla</t>
+          <t>historia_amistad_a_prueba_la_recupera</t>
         </is>
       </c>
     </row>
@@ -43598,7 +43678,7 @@
       </c>
       <c r="E45" s="17" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_cerrado</t>
+          <t>historia_confianza_marilla</t>
         </is>
       </c>
     </row>
@@ -43610,7 +43690,7 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_confiesa_en_falso</t>
+          <t>historia_confianza_marilla_cerrado</t>
         </is>
       </c>
     </row>
@@ -43622,7 +43702,7 @@
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>historia_confianza_marilla_dice_la_verdad</t>
+          <t>historia_confianza_marilla_confiesa_en_falso</t>
         </is>
       </c>
     </row>
@@ -43634,7 +43714,7 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>historia_decision</t>
+          <t>historia_confianza_marilla_dice_la_verdad</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43726,7 @@
       </c>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>historia_decision_cerrado</t>
+          <t>historia_decision</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43738,7 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>historia_decision_devuelta</t>
+          <t>historia_decision_cerrado</t>
         </is>
       </c>
     </row>
@@ -43670,7 +43750,7 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>historia_decision_se_queda</t>
+          <t>historia_decision_devuelta</t>
         </is>
       </c>
     </row>
@@ -43682,7 +43762,7 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>historia_humillada</t>
+          <t>historia_decision_se_queda</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43774,7 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>historia_humillada_cerrado</t>
+          <t>historia_humillada</t>
         </is>
       </c>
     </row>
@@ -43706,7 +43786,7 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>historia_humillada_estalla</t>
+          <t>historia_humillada_cerrado</t>
         </is>
       </c>
     </row>
@@ -43718,7 +43798,7 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>historia_humillada_llora</t>
+          <t>historia_humillada_estalla</t>
         </is>
       </c>
     </row>
@@ -43730,7 +43810,7 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>historia_humillada_se_contiene</t>
+          <t>historia_humillada_llora</t>
         </is>
       </c>
     </row>
@@ -43742,796 +43822,803 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>historia_llegada</t>
+          <t>historia_humillada_se_contiene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>historia_llegada_cerrado</t>
+          <t>historia_llegada</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>historia_matthew_aliado</t>
+          <t>historia_llegada_cerrado</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>historia_matthew_aliado_cerrado</t>
+          <t>historia_matthew_aliado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon</t>
+          <t>historia_matthew_aliado_cerrado</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon_a_lo_grande</t>
+          <t>historia_pedir_perdon</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>historia_pedir_perdon_cerrado</t>
+          <t>historia_pedir_perdon_a_lo_grande</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>historia_rival</t>
+          <t>historia_pedir_perdon_cerrado</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>historia_rival_cerrado</t>
+          <t>historia_rival</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>historia_rival_le_contesta</t>
+          <t>historia_rival_cerrado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>historia_rival_lo_ignora</t>
+          <t>historia_rival_le_contesta</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>historia_rival_pizarra</t>
+          <t>historia_rival_lo_ignora</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>historia_sombrero_iglesia</t>
+          <t>historia_rival_pizarra</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>historia_sombrero_iglesia_cerrado</t>
+          <t>historia_sombrero_iglesia</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>hito_estudio_20</t>
+          <t>historia_sombrero_iglesia_cerrado</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>hito_estudio_50</t>
+          <t>hito_estudio_20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>hito_estudio_85</t>
+          <t>hito_estudio_50</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>hito_granja_10</t>
+          <t>hito_estudio_85</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>hito_granja_40</t>
+          <t>hito_granja_10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>hito_granja_80</t>
+          <t>hito_granja_40</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>hito_letras_10</t>
+          <t>hito_granja_80</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>hito_letras_30</t>
+          <t>hito_letras_10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>hito_letras_60</t>
+          <t>hito_letras_30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>hito_mano_cocina_2</t>
+          <t>hito_letras_60</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>hito_mano_cocina_7</t>
+          <t>hito_mano_cocina_2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>hito_mano_leche_3</t>
+          <t>hito_mano_cocina_7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>hito_mano_leche_7</t>
+          <t>hito_mano_leche_3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>hito_paciencia_4</t>
+          <t>hito_mano_leche_7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>huerta</t>
+          <t>hito_paciencia_4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>inicio_juego</t>
+          <t>huerta</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>invierno</t>
+          <t>inicio_juego</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>josephine</t>
+          <t>invierno</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>leido</t>
+          <t>josephine</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>llamada_almuerzo</t>
+          <t>leido</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>llegada_tv</t>
+          <t>llamada_almuerzo</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>llegaron</t>
+          <t>llegada_tv</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>llego_</t>
+          <t>llegaron</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>llego_allan</t>
+          <t>llego_</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>llego_buhonero</t>
+          <t>llego_allan</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>llego_diana</t>
+          <t>llego_buhonero</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>llego_gilbert</t>
+          <t>llego_diana</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>llego_josephine</t>
+          <t>llego_gilbert</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>llego_sraallan</t>
+          <t>llego_josephine</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>llego_stacy</t>
+          <t>llego_sraallan</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>llego_veraneante</t>
+          <t>llego_stacy</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>lynde</t>
+          <t>llego_veraneante</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>lynde_contenida</t>
+          <t>lynde</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>lynde_llanto</t>
+          <t>lynde_contenida</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>lynde_visita</t>
+          <t>lynde_llanto</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>marilla</t>
+          <t>lynde_visita</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>marilla_doblo_ropa</t>
+          <t>marilla</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>marilla_sabe_camison</t>
+          <t>marilla_doblo_ropa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>matthew_en_estacion</t>
+          <t>marilla_sabe_camison</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>matthew_llego_casa</t>
+          <t>matthew_en_estacion</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="E111" s="17" t="inlineStr">
         <is>
-          <t>nombra_avenida</t>
+          <t>matthew_llego_casa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>nombre_propio_</t>
+          <t>nombra_avenida</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>nombres</t>
+          <t>nombre_propio_</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>nombro_</t>
+          <t>nombres</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>nombro_avenida</t>
+          <t>nombro_</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>nombro_burbuja</t>
+          <t>nombro_avenida</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>nombro_cerezo</t>
+          <t>nombro_burbuja</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>nombro_geranio</t>
+          <t>nombro_cerezo</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="E119" s="17" t="inlineStr">
         <is>
-          <t>nombro_lago</t>
+          <t>nombro_geranio</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>nombro_senda</t>
+          <t>nombro_lago</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="E121" s="17" t="inlineStr">
         <is>
-          <t>ofendio_lynde</t>
+          <t>nombro_senda</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>paces</t>
+          <t>ofendio_lynde</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>pastel_linimento</t>
+          <t>paces</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>patinar</t>
+          <t>pastel_linimento</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>pelo_corto</t>
+          <t>patinar</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>perdon_barry</t>
+          <t>pelo_corto</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>perdon_pedido</t>
+          <t>perdon_barry</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>perdonada</t>
+          <t>perdon_pedido</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>picnic</t>
+          <t>perdonada</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>pide_amiga</t>
+          <t>picnic</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="E131" s="17" t="inlineStr">
         <is>
-          <t>primera_bed</t>
+          <t>pide_amiga</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>primera_noche</t>
+          <t>primera_bed</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>prohibida</t>
+          <t>primera_noche</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>quedarse</t>
+          <t>prohibida</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>queens</t>
+          <t>quedarse</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>queens_primera</t>
+          <t>queens</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>quehaceres</t>
+          <t>queens_primera</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>quiere_amiga</t>
+          <t>quehaceres</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="E139" s="17" t="inlineStr">
         <is>
-          <t>rachel_en_casa_bell</t>
+          <t>quiere_amiga</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>rachel_llego_tejas_verdes</t>
+          <t>rachel_en_casa_bell</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>rachel_lo_sabe</t>
+          <t>rachel_llego_tejas_verdes</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>recito</t>
+          <t>rachel_lo_sabe</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="E143" s="17" t="inlineStr">
         <is>
-          <t>regado</t>
+          <t>recito</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>regalo</t>
+          <t>regado</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="E145" s="17" t="inlineStr">
         <is>
-          <t>remo</t>
+          <t>regalo</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>rezo</t>
+          <t>remo</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="E147" s="17" t="inlineStr">
         <is>
-          <t>ropa_arrugada</t>
+          <t>rezo</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>ropa_ordenada</t>
+          <t>ropa_arrugada</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="E149" s="17" t="inlineStr">
         <is>
-          <t>ropa_tirada_otra</t>
+          <t>ropa_ordenada</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>sala</t>
+          <t>ropa_tirada_otra</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="E151" s="17" t="inlineStr">
         <is>
-          <t>se_fue_</t>
+          <t>sala</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>se_fue_buhonero</t>
+          <t>se_fue_</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="E153" s="17" t="inlineStr">
         <is>
-          <t>se_fue_josephine</t>
+          <t>se_fue_buhonero</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>se_fue_phillips</t>
+          <t>se_fue_josephine</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="E155" s="17" t="inlineStr">
         <is>
-          <t>se_fue_prissy</t>
+          <t>se_fue_phillips</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>se_fue_veraneante</t>
+          <t>se_fue_prissy</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="E157" s="17" t="inlineStr">
         <is>
-          <t>se_queda</t>
+          <t>se_fue_veraneante</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>sombrero</t>
+          <t>se_queda</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="E159" s="17" t="inlineStr">
         <is>
-          <t>te_diana</t>
+          <t>sombrero</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>techo</t>
+          <t>te_diana</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="E161" s="17" t="inlineStr">
         <is>
-          <t>tinte</t>
+          <t>techo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>trineo</t>
+          <t>tinte</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="E163" s="17" t="inlineStr">
         <is>
-          <t>undefined</t>
+          <t>trineo</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="E164" s="17" t="inlineStr">
         <is>
-          <t>verano</t>
+          <t>undefined</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="E165" s="17" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>verano</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="E166" s="17" t="inlineStr">
         <is>
-          <t>zanahorias</t>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="E167" s="17" t="inlineStr">
         <is>
-          <t>zanahorias_contesta</t>
+          <t>zanahorias</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="E168" s="17" t="inlineStr">
         <is>
-          <t>zanahorias_ignora</t>
+          <t>zanahorias_contesta</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="E169" s="17" t="inlineStr">
         <is>
-          <t>zanahorias_pizarra</t>
+          <t>zanahorias_ignora</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="E170" s="17" t="inlineStr">
+        <is>
+          <t>zanahorias_pizarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="E171" s="17" t="inlineStr">
         <is>
           <t>{k}</t>
         </is>
@@ -56119,7 +56206,7 @@
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
-          <t>!estacion:invierno</t>
+          <t>!estacion:invierno, hecho:conocidas_diana</t>
         </is>
       </c>
       <c r="I191" s="9" t="n"/>

--- a/planilla/avonlea.xlsx
+++ b/planilla/avonlea.xlsx
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generada el 2026-10-25 16:29 desde los datos del juego (node tools/planilla.js).</t>
+          <t>Generada el 2026-10-25 17:03 desde los datos del juego (node tools/planilla.js).</t>
         </is>
       </c>
     </row>
@@ -58489,7 +58489,11 @@
           <t>hecho:primera_noche, !hecho:desayuno_prueba, ana_en_tv&lt;se_queda</t>
         </is>
       </c>
-      <c r="I147" s="9" t="n"/>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>ana=ga</t>
+        </is>
+      </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
           <t>marilla</t>
@@ -58502,7 +58506,8 @@
         <is>
           <t>resumen: Ana en la pieza del alero, la primera noche: llora hasta dormirse.
 objeto: bed
-paso: 1</t>
+paso: 1
+sola: sí</t>
         </is>
       </c>
       <c r="O147" s="22" t="inlineStr">
